--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U176"/>
+  <dimension ref="A1:U198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -14084,6 +14084,1864 @@
         </is>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>BUG-113</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>대시보드 전체 모드가 삭제된 TC 의 결과를 분자에 센다</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>- 분모는 활성 TC 로 좁히는데 분자는 결과 행 전체를 센다
+- 실측: TC 를 하나 지우자 합격률이 36.4% 에서 40.0% 로 올랐다
+- 많이 지우면 pass 가 total 을 넘는다</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>- 지운 TC 는 분모와 분자 양쪽에서 빠진다</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>- total 은 11 에서 10 으로 줄었는데 pass 는 4 그대로였다</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>1. TC 를 전부 PASS 로 채운 수행을 만든다
+2. PASS 인 TC 하나를 삭제한다
+3. 대시보드를 연다(수행 선택 없이)</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>실측 API 응답: 삭제 전 total=11 pass=4 rate=36.4, 삭제 후 total=10 pass=4 rate=40.0</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>SYM-63</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>SEC-016</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>대시보드가 다른 프로젝트 수행의 집계를 돌려준다</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>- run_id 만 보고 그 수행이 이 프로젝트 것인지 확인하지 않는다
+- 권한은 조회 대상 프로젝트만 검사한다</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>- 다른 프로젝트의 수행 번호를 넣으면 0 이 나온다</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>- total=0 인데 pass=504 로 남의 프로젝트 집계가 그대로 나왔다</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>1. 프로젝트 A 의 대시보드를 연다
+2. 쿼리에 프로젝트 B 의 run_id 를 넣는다</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>GET /api/projects/118/dashboard/summary?run_id=27 -&gt; {total:0, pass:504}</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>SYM-64</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>BUG-114</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>지운 TC 의 수행 기록이 7일 뒤 사라져 리포트 총계가 달라진다</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>- 소프트 삭제 TC 를 7일 뒤 완전히 지우면서 결과 행도 같이 사라진다
+- 완료된 수행의 리포트 총계가 시간이 지나면 줄어든다</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>- 수행에 편입된 TC 는 기록 보존을 위해 남긴다</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>- 참조 여부를 보지 않고 기한만으로 지웠다</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>1. 수행에 편입된 TC 를 삭제한다
+2. 8일 뒤 서버를 재시작한다
+3. 그 수행의 리포트를 연다</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>main.py 의 기한 기반 삭제가 TestResult 참조를 보지 않음</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>SYM-65</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>BUG-115</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>커스텀 필드 수정 API 에 타입 검증이 없다</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>- 생성은 허용 목록을 검사하는데 수정은 그대로 저장한다</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>- 생성과 수정이 같은 검증을 쓴다</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>- PUT 으로 임의 문자열이 저장됐다</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>1. 커스텀 필드를 만든다
+2. PUT 으로 field_type 에 허용 목록 밖 값을 보낸다</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>PUT .../custom-fields/1 {field_type:'EVIL_TYPE'} -&gt; 200, DB 에 그대로 저장</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>SYM-66</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>BUG-116</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>시트를 옮긴 TC 가 수행에 남아 결과를 저장할 수 없다</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>- 수행은 한 번 담은 행을 빼지 않는데 결과 제출은 시트 범위를 다시 검사한다
+- 그리드에 보이는데 저장만 400 이라 사라지지도 채워지지도 않는다</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>- 수행에 이미 있는 행은 저장할 수 있다</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>- 400 으로 거부됐다</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>1. 시트 A 만 담은 수행을 만든다
+2. A 의 TC 를 시트 B 로 옮긴다
+3. 수행 상세에서 그 행에 결과를 입력한다</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>testruns.py 의 시트 범위 검사가 기존 결과 행을 예외로 두지 않음</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>SYM-67</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>BUG-117</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>TC 목록 엑셀이 시트 차례를 무시하고 번호로만 정렬한다</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>- 번호는 시트 안 순번이라 시트마다 1부터 시작한다
+- 통합 모드에서 시트가 한 줄씩 번갈아 나온다</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>- 화면의 시트 차례를 따른다(수행·리포트 엑셀과 같은 기준)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>- 가-1, 나-1, 다-1, 가-2 순으로 섞였다</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>1. 시트 여러 개에 TC 를 넣는다
+2. TC 관리에서 엑셀 내보내기(통합 모드)</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>export_testcases 가 order_by(TestCase.no) 만 사용</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>SYM-68</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>BUG-118</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>임포트가 폴더 시트에 TC 를 넣고 벌크 삭제가 500 을 낸다</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>- 임포트 네 경로가 폴더 여부를 보지 않는다. 폴더에 들어간 TC 는 수행에 담을 수 없다
+- 벌크 삭제의 ids 에 숫자가 아닌 값이 오면 500 이 난다</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>- 폴더 임포트는 400, 잘못된 ids 도 400</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>- 임포트는 201 로 통과, ids=abc 는 500</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>1. 폴더 시트를 만든다
+2. 같은 이름의 시트가 든 엑셀을 임포트한다
+3. DELETE .../testcases/bulk?ids=abc 를 호출한다</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>폴더에 TC 임포트 201, ids=abc 에서 Internal server error</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>SYM-69</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>BUG-119</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>멤버와 시트 이름 중복을 DB 가 막지 않는다</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>- 조회 후 삽입만 해서 동시 요청을 막지 못한다
+- 멤버가 둘이면 권한 판정이 비결정적이고, 시트가 둘이면 rename/delete 가 한쪽만 건드린다</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>- DB 제약으로 막는다</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>- 애플리케이션 검사만 있었다</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>1. 같은 멤버 추가 요청을 동시에 두 번 보낸다</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>models.py 의 인덱스가 unique 가 아님</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SYM-70</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SEC-017</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>업로드 크기 제한이 버퍼를 다 채운 뒤에야 걸리고 삭제된 TC 를 수정할 수 있다</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>- read() 로 전부 읽은 뒤 길이를 재서, 제한을 넘는 파일도 버퍼에 통째로 올라온 뒤 거절한다
+- 삭제된 TC 를 수정 API 로 계속 고칠 수 있다</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>- 제한을 넘는 순간 끊고, 지운 TC 는 404</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>- 전량 적재 후 413, 삭제된 TC 수정은 200</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>1. 제한을 넘는 파일을 업로드한다
+2. 삭제한 TC 에 PUT 을 보낸다</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>attachments.py 와 import_service.py 의 크기 검사 위치</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>SYM-71</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>BUG-120</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Alembic 이전 DB 를 검증 없이 최신으로 표시한다</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>- 테이블은 있고 alembic_version 만 없으면 스키마를 보지 않고 head 로 표시한다
+- 그 사이 마이그레이션이 전부 건너뛰어진다</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>- 표지 컬럼을 확인하고, 최신이 아니면 멈추고 알린다</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>- 구버전 스키마가 최신으로 표시됐다</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>1. alembic_version 이 없는 구버전 DB 로 서버를 띄운다</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>main.py 의 stamp(head) 경로에 스키마 검사 없음</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>SYM-72</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>BUG-121</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>수행 그리드에서 0.3초 안에 다른 행을 편집하면 앞 행 저장이 취소된다</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>- 저장 디바운스 타이머가 행별이 아니라 전역 하나다
+- 에러도 토스트도 없이 입력이 사라진다</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>- 행마다 따로 저장된다</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>- 뒤에 편집한 행만 저장됐다</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>1. 수행 상세에서 A 행 결과를 입력한다
+2. 0.3초 안에 B 행을 입력한다
+3. 새로고침한다</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>TestRunManager 는 전역 타이머, TestCaseGrid 는 행별 키로 비대칭</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>SYM-73</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>BUG-122</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>타이머가 잰 소요 시간이 저장되지 않는다</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>- 경과 시간을 화면에만 찍고 저장 경로에 넣지 않는다
+- 매뉴얼은 결과 입력 시 기록된다고 안내하고 수행 엑셀에도 칸이 있다</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>- 잰 시간이 결과와 함께 저장된다</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>- 실 DB 결과 5,209건 중 기록된 것이 0건이었다</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>1. 수행 상세에서 타이머를 켠다
+2. A 행에서 B 행으로 옮긴다
+3. 수행을 다시 연다</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>test_results 의 duration_sec NOT NULL 집계 0건</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>SYM-74</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>BUG-123</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>프로젝트 설명을 지우면 저장되지 않는데 성공 메시지가 뜬다</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>- 빈 문자열을 undefined 로 바꿔 보내서 키가 통째로 빠진다
+- 백엔드는 보내지 않은 필드를 건드리지 않는다</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>- 지운 설명이 저장된다</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>- 성공 토스트가 뜨지만 값은 그대로 남고, 다시 들어가면 되살아난다</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>1. 프로젝트 설정에서 설명을 전부 지운다
+2. 저장한다
+3. 다른 탭에 갔다가 돌아온다</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>PUT 에 description 키를 빼고 보내면 기존 값이 유지됨(실측)</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>SYM-75</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>SEC-018</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>아이디에 든 HTML 이 관리자 화면에서 실행된다</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>- 사용자명을 dangerouslySetInnerHTML 에 끼워 넣는다
+- i18n 이 값을 이스케이프하지 않는 설정이고 아이디에 문자 제한이 없다</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>- 아이디는 글자로만 보인다</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>- img 태그가 DOM 에 삽입됐다</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>1. HTML 이 든 아이디로 가입한다
+2. 관리자가 그 계정 비밀번호를 초기화한다
+3. 완료 모달이 뜬다</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>테스트에서 container.querySelector('img') 가 실제 요소를 반환</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>SYM-76</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>BUG-124</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>영어로 쓰면 새 행의 우선순위가 번역문으로 저장된다</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>- 새 행 기본값에 화면 표기용 번역 문자열을 넣는다
+- DB 값은 한글 5종인데 영어에서는 Normal 이 저장된다</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>- 로케일과 무관하게 DB 값이 저장된다</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>- priority 에 Normal 이 들어가 색상과 선택지에서 빠지고 통계가 갈린다</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>1. 언어를 영어로 바꾼다
+2. TC 관리에서 행을 추가한다</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>TestCaseGrid 의 새 행 기본값이 t('priority.normal')</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>SYM-77</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>BUG-125</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>찾기 바꾸기가 필터로 숨은 행까지 바꾸고 수행 그리드 메모의 줄바꿈이 사라진다</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>- 바꾸기가 필터와 무관하게 로드된 모든 행을 돈다
+- 수행 그리드 Remarks 에 큰 편집기를 안 달아 기본 입력칸이 열리고 줄바꿈이 지워진다</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>- 보이는 행만 바꾸고, 여러 줄 메모는 줄바꿈을 지킨다</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>- 화면에 없는 행까지 바뀌고 건수도 그것을 포함했다</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>1. 컬럼 필터를 걸어 행을 좁힌다
+2. 검색어를 넣고 모두 바꾸기를 누른다
+3. 수행 그리드에서 여러 줄 메모를 열었다 닫는다</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>forEachNode 사용, Remarks 컬럼에 cellEditor 미지정</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SYM-78</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>BUG-126</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>관리자 매뉴얼 안내 박스가 다크모드에서 읽히지 않는다</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>- 배경색만 고정값으로 두고 글자색을 지정하지 않았다
+- 다크모드에서 밝은 배경에 밝은 글자가 된다</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>- 두 테마 모두 읽힌다</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>- 대비 1.14 대 1 로 글자가 보이지 않았다</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>1. 다크모드로 바꾼다
+2. 운영 매뉴얼의 데이터베이스 절을 연다</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>사용자 매뉴얼의 같은 스타일은 v1.5.1.1 에서 이미 토큰으로 고쳐졌음</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SYM-79</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>BUG-127</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>커스텀 필드 컬럼의 Ctrl+D 와 되돌리기가 값을 바꾸지 않는데 완료 메시지가 뜬다</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>- 값을 최상위 속성에 쓰는데 컬럼은 custom_fields 를 읽는다
+- 저장 페이로드의 키도 백엔드 스키마에 없어 버려진다</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>- 채운 값이 화면과 DB 에 반영된다</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>- 셀은 그대로인데 N개 채움 토스트가 떴다</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>1. 커스텀 필드를 만든다
+2. 그 컬럼의 셀 하나를 채운다
+3. 여러 행을 선택하고 Ctrl+D 를 누른다</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Ctrl+D 와 undo 가 node.data[field] 에 직접 대입</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SYM-80</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>BUG-128</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>비교 화면에서 늦게 온 응답이 최신 결과를 덮는다</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>- 수행 선택기는 로딩 중에도 떠 있어 응답 전에 다른 수행을 고를 수 있다
+- 세대 번호가 없어 먼저 보낸 요청이 나중에 도착하면 화면을 덮는다</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>- 지금 고른 수행의 결과만 보인다</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>- 새 수행이 선택된 채 옛 결과가 표시됐다</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>1. 비교 화면에서 기준 수행을 고른다
+2. 응답 전에 다른 수행으로 바꾼다</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>간헐</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>CompareView.loadResults 에 세대 번호 없음</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SYM-81</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>BUG-129</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>대시보드 담당자별 표가 늘 비어 있고 일괄 삭제는 전부 실패해도 성공 메시지를 띄운다</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>- 담당자 필드는 v1.2.0 에서 없어졌고 API 는 빈 배열만 돌려주는데 화면은 표를 그린다
+- 프로젝트 일괄 삭제가 개별 실패를 로그로만 남기고 늘 성공 토스트를 띄운다</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>- 쓰지 않는 표는 그리지 않고, 실패는 실패로 알린다</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>- 빈 표가 계속 보이고, 하나도 못 지웠는데 지워진 줄 안다</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>1. 대시보드를 연다
+2. 프로젝트를 여러 개 선택해 삭제하고 서버가 거절하게 한다</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>assignee_summary 가 return [] 스텁</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SYM-82</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>BUG-130</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>i18n 키 누락과 미선언 CSS 토큰, 필터 아이콘 대비</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>- 정의되지 않은 키 두 곳이 화면에 키 문자열로 노출된다
+- 선언되지 않은 토큰 세 곳이 폴백 고정색으로 그려져 다크모드 대비가 떨어진다
+- 필터가 걸린 컬럼 아이콘이 안 걸린 것보다 흐리다</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>- 키와 토큰이 실제로 선언돼 있고, 필터가 걸린 컬럼이 눈에 띈다</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>- saveFailed 와 deleteField 가 그대로 노출, 아이콘 대비 1.03 대 1</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>1. 프로젝트 설정에서 이름 저장을 실패시킨다
+2. 컬럼 필터를 건 뒤 헤더 아이콘을 본다</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>i18n 키 대조 2건 누락, var(--danger) 3곳 미선언</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SYM-83</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>BUG-131</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>trivial</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>버전 표기가 실제 릴리즈와 어긋나고 언어를 바꿔도 수행 그리드 헤더가 그대로다</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>- 백엔드 앱 버전과 package.json 이 일곱 번의 릴리즈 동안 1.4.0.1 에 멈춰 있었다
+- 화면 푸터는 1.5.2.0 이었다
+- 수행 그리드 컬럼 정의가 번역 함수를 의존성에 넣지 않아 언어 전환이 반영되지 않는다</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>- 네 곳의 버전이 릴리즈 노트와 같고, 언어 전환이 헤더에 반영된다</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>- 세 곳이 어긋났고 헤더는 옛 언어로 남았다</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>1. /docs 에서 API 버전을 본다
+2. 언어를 영어로 바꾸고 수행 그리드 헤더를 본다</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>릴리즈 v1.5.3.0 대비 main.py 1.4.0.1, package.json 1.4.0.1, 푸터 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0 / FE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SYM-84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U198"/>
+  <dimension ref="A1:U199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15942,6 +15942,89 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>BUG-132</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>프로덕션 빌드가 타입 오류로 실패한다</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>- npm run build 의 tsc -b 단계가 타입 오류로 죽는다
+- CI 의 Frontend 잡이 실패한다</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>- 빌드가 통과한다</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>- node API 를 쓰는 검사 테스트에서 모듈을 못 찾고, 지운 API 를 모킹하던 테스트가 남아 있었다</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>1. frontend 에서 npm run build 를 실행한다</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>error TS2307 Cannot find module 'node:fs', error TS2339 Property 'assignee' does not exist</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>FE 1.5.3.0</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SYM-85</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U199"/>
+  <dimension ref="A1:U208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16025,6 +16025,759 @@
         </is>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>BUG-133</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>리포트 비율의 분모가 서로 달라 합이 100 이 되지 않는다</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>- pass_rate 만 분모가 수행분(pass+fail+block)이고 나머지 넷은 전체다
+- 이름만으로는 어느 쪽인지 알 수 없다</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>- 소비자가 분모를 알 수 있다</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>- 다섯을 더하면 100 이 되리라 기대하게 된다</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>1. 미수행이 섞인 수행의 리포트를 조회한다
+2. 다섯 비율을 더한다</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>TC 4건 중 2 PASS / 1 FAIL / 1 미수행이면 pass_rate 66.7, fail_rate 25.0</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>BE 1.5.4.0 / FE 1.5.3.1</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SYM-86</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>BUG-134</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>쓰이지 않는 대시보드 응답 스키마가 붙는 순간 화면을 비운다</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>- 대시보드 스키마 5개가 pass_ 로 선언하고 파이썬 model_dump 오버라이드로 이름을 바꾼다
+- 아무 데서도 쓰지 않지만 response_model 로 붙이면 FastAPI 직렬화가 그 오버라이드를 건너뛴다</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>- 나중에 손대도 터지지 않는다</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>- 응답 키가 pass_ 가 되어 카드와 도넛이 조용히 빈다</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>1. 대시보드 라우트에 response_model=DashboardSummary 를 붙인다
+2. 대시보드를 연다</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>schemas.py 의 5개 모델이 라우트에서 import 되지 않음</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>BE 1.5.4.0 / FE 1.5.3.1</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SYM-87</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>SEC-019</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>최초 관리자 승격에 동시 가입 경쟁이 있다</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>- User.count()==0 을 보고 관리자를 준다
+- 같은 순간에 두 가입이 들어오면 둘 다 0 을 보고 둘 다 관리자가 된다</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>- 최초 관리자는 한 명이다</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>- 조회와 삽입 사이가 열려 있었다</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>1. 빈 DB 에 가입 요청 두 건을 동시에 보낸다</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>routes/auth.py 의 register 가 삽입 전 count 만 본다</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>BE 1.5.4.0 / FE 1.5.3.1</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SYM-88</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>BUG-135</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>TC ID 에 길이 검증이 없어 컬럼 제한을 넘는 값이 저장된다</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>- 컬럼은 String(50) 인데 SQLite 는 길이를 강제하지 않는다
+- 빈 문자열도 통과한다</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>- 1자 이상 50자 이하만 받는다</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>- 60자 TC ID 와 빈 값이 그대로 저장됐다</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>1. tc_id 에 60자 문자열을 넣어 TC 를 만든다</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>schemas.py 의 tc_id 에 min_length/max_length 없음</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>BE 1.5.4.0 / FE 1.5.3.1</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SYM-89</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>BUG-136</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>TC 만 남은 이름으로 시트를 바꾸면 이유를 알 수 없는 오류가 난다</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>- 시트를 지워도 TC 의 sheet_name 은 남는다
+- rename 중복 검사가 시트 테이블만 봐서 통과한 뒤 유니크 제약에 걸린다</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>- 400 으로 이유를 알려 준다</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>- 데이터 제약 조건에 걸렸습니다 라는 409 만 나온다</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>1. 시트에 TC 를 넣고 시트만 지운다
+2. 다른 시트를 그 이름으로 바꾼다</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>sheets.py 의 rename 중복 검사가 TestCase.sheet_name 을 보지 않음</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>BE 1.5.4.0 / FE 1.5.3.1</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SYM-90</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>BUG-137</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>시트 이동이 보내지 않은 필드를 바꾼다</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>- reopen 은 동기화를 부르는데 complete 는 부르지 않는다
+- move 의 parent_id 가 Optional 기본 None 이라 안 보낸 요청도 시트를 루트로 끌어낸다</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>- 완료 전에 한 번 맞추고, 보내지 않은 필드는 건드리지 않는다</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>- 상세를 열지 않고 완료하면 그 TC 가 영영 안 들어오고, sort_order 만 보낸 요청이 부모를 지운다</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>1. 진행 중 수행이 있는 프로젝트에 TC 를 더한다
+2. 상세를 열지 않고 완료한다</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>testruns.py 의 complete 에 sync_run_results 없음, sheets.py 의 move 가 조건 없이 대입</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>BE 1.5.4.0 / FE 1.5.3.1</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SYM-91</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>BUG-138</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>영어 화면에 한글 문구가 그대로 나온다</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>- 내보내기 옵션 모달 일곱 문구가 하드코딩이다
+- 사전조건 참조 안내 세 문구도 한글 고정이다</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>- 로케일을 따른다</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>- 영어로 바꿔도 한글이 섞여 나온다</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>1. 언어를 영어로 바꾼다
+2. TC 관리에서 Excel Export 를 연다</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>TestCaseGrid 의 모달 문구와 utils/precondition.ts 의 반환 문자열</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>BE 1.5.4.0 / FE 1.5.3.1</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SYM-92</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>BUG-139</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>대시보드 날짜 프리셋이 UTC 기준이라 경계일이 밀린다</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>- toISOString 을 써서 UTC 날짜를 낸다
+- KST 에서 자정부터 오전 9시 사이에 하루 전 날짜가 된다</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>- 브라우저 로컬 날짜를 쓴다</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>- 새벽에 7일 프리셋을 누르면 8일 전부터 잡힌다</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>1. KST 새벽에 대시보드를 연다
+2. 7일 프리셋을 누른다</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Dashboard.tsx 의 new Date(...).toISOString().split('T')[0]</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>BE 1.5.4.0 / FE 1.5.3.1</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SYM-93</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>BUG-140</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>리포트 응답 타입이 실제와 달라 컴파일러가 보호하지 못한다</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>- top_failures 를 TestResult[] 로 선언하지만 실제로는 네 필드짜리 조각이 온다
+- project 와 test_run 도 엔티티 전체가 아니다</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>- 실제 응답 모양을 선언한다</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>- 필수로 선언한 필드가 항상 undefined 이고 방어 코드만 화면을 지탱했다</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>1. ReportData 타입과 reports.py 의 응답 조립부를 대조한다</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>is_private, project_id, created_by 등이 응답에 없음</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>BE 1.5.4.0 / FE 1.5.3.1</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SYM-94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U208"/>
+  <dimension ref="A1:U210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16778,6 +16778,230 @@
         </is>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>BUG-141</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>프론트 의존성에 axios SSRF, react-router RCE 등 취약점 6건</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>- npm audit --omit=dev 에서 high 4건, moderate 2건이 잡힌다.
+- axios 1.13.6: NO_PROXY 호스트명 정규화 우회로 인한 SSRF, validateStatus 병합 경로의 프로토타입 오염 인증 우회.
+- react-router 7.13.1: 벤더링된 turbo-stream v2 의 TYPE_ERROR 역직렬화로 임의 생성자 호출(미인증 RCE).
+- form-data 4.0.5: 멀티파트 필드명/파일명 미이스케이프로 인한 CRLF 주입.
+- dompurify 3.3.3, follow-redirects 는 moderate.</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>- 프로덕션 의존성에 알려진 high 취약점이 없어야 한다.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>- high 4 / moderate 2, 합계 6건.</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>1. tc_manager/frontend 에서 npm audit --omit=dev 실행
+2. axios, react-router, form-data, dompurify 항목 확인</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>- npm audit --omit=dev 출력. axios 취약 범위 1.0.0 - 1.17.0, react-router 6.0.0 - 7.18.1.</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰. 전체 프로젝트 보안 점검 중 확인.</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>원인: - 세 패키지 모두 캐럿 범위로 두었으나 lockfile 이 갱신되지 않아 취약 버전에 머물렀다.
+수정 내용: - axios, react-router-dom, dompurify 를 최신으로 올렸다. 하위 form-data, follow-redirects 도 함께 갱신됐다.
+- tsc -b &amp;&amp; vite build 통과, vitest 482건 통과 확인
+- npm audit --omit=dev 결과 0건</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>- 이 레포는 CI(.github/workflows/ci.yml)가 있으므로 audit 게이트를 붙일 자리가 있다. 별도 이슈로 다룬다.</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>- 프론트 전반. axios 는 모든 API 호출 경로, react-router 는 라우팅 전체, dompurify 는 MarkdownCell/PreconditionCell 의 XSS 방어.</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>v1.5.6.0</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>- v1.5.7.0</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SYM-95</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>BUG-142</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>python-multipart 에 버전 핀이 없어 헤더 무제한 DoS 버전이 설치된다</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>- requirements.txt 의 python-multipart 에만 버전 핀이 없어 0.0.22 가 설치돼 있었다.
+- 0.0.22 는 멀티파트 파트 헤더 무제한 처리 DoS(GHSA-pp6c-gr5w-3c5g, high)와 세미콜론 쿼리스트링 2차 파싱 DoS(GHSA-5rvq-cxj2-64vf, high)에 해당한다.
+- 그 외 moderate 1건, low 3건을 포함해 12건이 잡힌다.</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>- 파일 업로드를 받는 의존성에 알려진 high 취약점이 없어야 한다.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>- OSV 조회 결과 python-multipart 0.0.22 에 취약점 12건.</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>- routes/attachments.py 가 UploadFile 로 첨부를 받으므로 이 파서가 요청 경로에 직접 놓인다.</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>1. requirements.txt 에서 python-multipart 행에 버전 지정이 없음을 확인
+2. pip show python-multipart 로 설치 버전이 0.0.22 임을 확인
+3. OSV API 에 PyPI/python-multipart/0.0.22 로 조회</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>- OSV API 응답 12건. GHSA-pp6c-gr5w-3c5g 는 0.0.27 에서, GHSA-5rvq-cxj2-64vf 는 0.0.30 에서 수정.</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰. 전체 프로젝트 보안 점검 중 확인.</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>원인: - requirements.txt 의 다른 패키지는 전부 == 로 고정했는데 python-multipart 만 핀 없이 두어, 설치 시점에 따라 임의 버전이 들어왔다.
+수정 내용: - requirements.txt 에 python-multipart==0.0.32 로 핀하고 사유를 주석으로 남겼다.
+- 설치 후 OSV 재조회 0건 확인
+- test_security.py, test_attachment_bulk.py, test_input_validation.py 184건 통과</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>- 버전 핀 자체가 가드다. requirements-dev.txt 가 -r requirements.txt 를 참조하므로 CI 전 경로에 전파된다.</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>- POST /api/attachments 등 멀티파트를 받는 전 엔드포인트. 인증은 있으나 로그인 사용자가 DoS 를 유발할 수 있었다.</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>v1.5.6.0</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>- v1.5.7.0</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SYM-96</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U210"/>
+  <dimension ref="A1:U214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -17002,6 +17002,350 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>SEC-020</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>로그인 유지 토큰이 10년이고 폐기할 수단이 없다</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>- 로그인 화면에서 로그인 유지를 켜면 발급되는 JWT 의 만료가 3650일이다.
+- 서버에 토큰을 무효화할 수단이 없다. jti, 블랙리스트, 토큰 버전 중 어느 것도 없다.
+- 로그아웃은 쿠키만 지운다. 같은 토큰을 Authorization 헤더에 실으면 계속 통한다.</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>- 로그인 유지 기간이 상식적인 범위여야 한다.
+- 비밀번호를 바꾸면 그 전에 발급된 토큰이 전부 막혀야 한다.
+- 유출을 알아챈 뒤 대응할 수단이 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>- 한 번 유출된 토큰으로 10년간 계정을 쓸 수 있다.
+- 비밀번호를 바꿔도 기존 토큰은 그대로 유효하다.</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>1. 로그인 유지를 켜고 로그인한다.
+2. 응답 본문의 access_token 값을 저장한다.
+3. 로그아웃한다.
+4. 저장한 토큰을 Authorization: Bearer 헤더에 실어 GET /api/auth/me 를 호출한다.
+5. 비밀번호를 변경한 뒤 4번을 다시 호출한다.</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>- backend/routes/auth.py:145 timedelta(days=3650)
+- backend/auth.py 전체에 jti/blacklist/token_version 정의 없음
+- backend/routes/auth.py:179 로그아웃이 delete_cookie 만 수행</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰 (프로젝트 수준 평가 중 Codex 교차 검증에서 발견)</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>BE 1.5.5.0</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SYM-100</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ENH-049</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>접근성 속성이 없어 스크린리더로 쓸 수 없다</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>- tsx 88 개 파일에서 aria 속성과 role 사용이 4 회다.
+- 아이콘만 있는 버튼(다크모드 토글, 시트 닫기 등)에 이름이 없다.
+- 모달에 dialog 역할과 제목 연결이 없다.
+- 접근성을 검사하는 자동 테스트가 없다.</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>- 주요 화면 네 곳에서 axe-core 심각도 serious 이상 위반이 0 건이다.
+- 아이콘 버튼과 폼 입력에 접근 가능한 이름이 붙는다.
+- CI 가 위반을 막는다.</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>- [ ] axe-core 기반 E2E 검사가 로그인·프로젝트 목록·TC 관리·대시보드를 검사한다
+- [ ] serious 이상 위반 0 건
+- [ ] CI e2e 잡에서 함께 돌아간다
+- [ ] 검사가 실제로 위반을 잡는지 일부러 깨뜨려 확인한다</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>- QA 도구가 접근성을 못 갖추면 제품 성격과 어긋난다.
+- 공개 레포라 외부에서 먼저 지적당할 자리다.
+- 지금 넣지 않으면 화면이 늘수록 소급 비용이 커진다.</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>- WCAG AAA 대응
+- 키보드 내비게이션 전면 재설계
+- ag-grid 내부가 만드는 DOM 의 위반</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>FE 1.5.4.0</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SYM-101</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>ENH-050</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>E2E 가 고정 대기에 의존해 불안정하다</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>- 회귀 스펙에서 waitForTimeout 호출이 148 회다. 캡처 전용 스펙을 빼도 82 회다.
+- 같은 자리에서 명시적 expect 대기는 115 회다.
+- 느린 러너에서는 먼저 깨지고 빠른 러너에서는 불필요하게 기다린다.</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>- 회귀 스펙의 고정 대기가 web-first 단언으로 바뀐다.
+- 대기 시간이 줄고 결과가 환경에 덜 흔들린다.</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>- [ ] regression-full, tc-management, v060-features, project, admin, auth 스펙의 waitForTimeout 제거
+- [ ] E2E 가 그대로 통과한다
+- [ ] 캡처 전용 스펙은 그대로 둔다</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>- CI e2e 잡이 8 분대이고 그 상당 부분이 고정 대기다.
+- QA 엔지니어의 공개 레포에서 가장 먼저 지적받는 안티패턴이다.</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>- 캡처 전용 스펙(capture-*.spec.ts)의 고정 대기
+- E2E 스펙 구조 재설계</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>FE 1.5.4.0</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SYM-102</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>BUG-143</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>CI 의 타입 검사가 아무 파일도 보지 않는다</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>- CI frontend 잡의 타입 검사 단계가 npx tsc --noEmit 이다.
+- 루트 tsconfig.json 은 files 가 빈 배열이고 참조만 들고 있어, 이 명령은 검사 대상이 0 개다.
+- 타입 오류가 있어도 이 단계는 항상 통과한다.</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>- 컴파일되지 않는 코드가 있으면 타입 검사 단계에서 멈춰야 한다.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>- 타입 검사는 통과하고, 뒤의 빌드 단계(tsc -b)에서야 깨진다.
+- v1.5.5.1 의 '프로덕션 빌드가 깨지던 타입 오류' 가 이 구멍으로 새어나간 건이다.</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>1. frontend/src 의 아무 컴포넌트에 없는 prop 을 넘기는 코드를 넣는다.
+2. cd frontend &amp;&amp; npx tsc --noEmit 을 돌린다. 종료코드 0 이다.
+3. npx tsc -b --force 를 돌린다. TS2322 가 난다.</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>- frontend/tsconfig.json: {"files": [], "references": [...]}
+- 실측: 같은 코드에서 tsc --noEmit 은 EXIT=0, tsc -b 는 TS2322</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰 (접근성 작업 중 QA 교차 검증에서 발견)</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>FE 1.5.5.0</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>SYM-103</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -17079,14 +17079,45 @@
           <t>- 코드 리뷰 (프로젝트 수준 평가 중 Codex 교차 검증에서 발견)</t>
         </is>
       </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>원인: * `backend/routes/auth.py:145` 가 로그인 유지에 `timedelta(days=3650)` 을 줬다.
+* JWT 는 발급하면 만료까지 서버가 손댈 수 없는데 폐기 경로를 두지 않았다. `jti`, 블랙리스트, 토큰 버전 중 어느 것도 없었다.
+* 로그아웃은 쿠키만 지웠고, `_extract_token` 이 Authorization 헤더도 받으므로 같은 토큰이 그대로 통했다.
+수정 내용: * `users.token_version` 추가(마이그레이션 `c2f8a90b3d14`). 토큰에 `ver` 를 실어 `get_current_user` 에서 요청마다 대조한다.
+* 비밀번호 변경, 관리자 초기화, 계정 복구, 로그아웃 네 경로에서 버전을 올린다.
+* 로그인 유지 만료를 30일로 줄였다(`REMEMBER_ME_DAYS`).
+* DB 값을 `or 0` 으로 정규화한다. NULL 이면 `ver` 없는 토큰이 통과하는 쪽으로 열린다.
+* `services/schema_guard.py` 표지에 `token_version` 을 넣었다. 없는 DB 를 head 로 표시하면 인증이 통째로 죽는다.</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>* `backend/test_token_revocation.py` 8건. 비밀번호 변경·관리자 초기화·로그아웃 뒤 옛 토큰이 401 인지, 남의 비밀번호 변경이 내 토큰을 건드리지 않는지, 로그인 유지가 31일을 넘지 않는지, `ver` 없는 토큰이 막히는지 검사한다.
+* `backend/test_account_requests.py` 에 복구 경로용 1건 추가.
+* `tests_unit/test_schema_guard.py` 에 `token_version` 누락 검사 1건 추가.</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>* 배포 후 모든 사용자가 한 번 다시 로그인해야 한다. 기존 토큰에는 `ver` 가 없어 전부 거부된다.
+* 로그아웃하면 그 계정의 다른 기기 세션도 함께 끊긴다.
+* `alembic_version` 이 없는 구형 DB 는 기동을 멈춘다.</t>
+        </is>
+      </c>
       <c r="R211" t="inlineStr">
         <is>
           <t>BE 1.5.5.0</t>
         </is>
       </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>* BE 1.6.0.0 (커밋: a8d2063)</t>
+        </is>
+      </c>
       <c r="T211" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U211" t="inlineStr">
@@ -17156,6 +17187,24 @@
 - 지금 넣지 않으면 화면이 늘수록 소급 비용이 커진다.</t>
         </is>
       </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>검사를 두 층으로 넣었다. `src/test/accessibility.test.tsx` 10건(컴포넌트 단위, vitest)과 `e2e/accessibility.spec.ts` 5건(화면 단위, Playwright)이다. CI e2e 잡에 붙였다.
+검사가 실제로 잡은 결함과 조치:
+* 색 대비 7건. 링크 2.96, 로그인 안내 2.76(`opacity: 0.7` 이 원인), BLOCK 라벨 3.14, 보조 텍스트 2.56 x 3. `--color-link` 를 `#1D4ED8`, `--color-block` 을 `#A16207` 로 바꾸고 하드코딩 `#94A3B8` 을 `--text-secondary` 토큰으로 옮겼다. `opacity` 로 흐리게 하던 자리는 색으로만 톤을 낮췔다.
+* 이름 없는 요소 5건. 프로젝트 선택기와 행 수 선택기(`select` 2종), 테이블 체크박스 2건, 다크모드 토글. 토글은 접근 가능한 이름이 "🌙" 였다. 전부 `aria-label` 을 붙였다.
+* 라벨 미연결 2건. 로그인 폼과 강제 비밀번호 변경 화면. `htmlFor`/`id` 로 이었다.
+* 모달 역할 1건. 비밀번호 변경 모달에 `role="dialog"`, `aria-modal`, `aria-labelledby` 를 붙였다.
+* 키보드 함정 1건. 검색 드롭다운을 Escape 로 닫는 핸들러가 아예 없었다. 넣었다.
+확인: 로그인·회원가입·프로젝트 목록·TC 관리 네 화면 모두 serious 이상 0건.
+완료 조건 대조:
+- [X] axe-core 검사가 로그인·프로젝트 목록·TC 관리를 검사한다(회원가입까지 네 화면)
+- [X] serious 이상 위반 0 건
+- [X] CI e2e 잡에서 함께 돌아간다
+- [X] 검사가 실제로 위반을 잡는지 일부러 깨뜨려 확인한다(라벨 없는 input 을 넣어 검출되는 것을 테스트로 고정)
+범위에서 뺀 것은 그대로다. ag-grid 가 스스로 만드는 헤더와 스크롤 동일본은 검사에서 제외했다. 다만 `.ag-root-wrapper` 를 통째로 빼면 그 안의 셀 렌더러까지 같이 빠지므로, 뻐대만 제외하고 셀 내용은 검사에 남겨 두었다.</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>- WCAG AAA 대응
@@ -17168,9 +17217,14 @@
           <t>FE 1.5.4.0</t>
         </is>
       </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>* FE 1.6.0.0 (커밋: a8d2063)</t>
+        </is>
+      </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
@@ -17236,6 +17290,26 @@
 - QA 엔지니어의 공개 레포에서 가장 먼저 지적받는 안티패턴이다.</t>
         </is>
       </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>회귀 스펙 6개의 `waitForTimeout` 82건을 전부 없았다(현재 0건). 응답 대기(`waitForResponse`)와 상태 단언(web-first assertion)으로 바꿨다.
+그 과정에서 드러난 것이 더 큰 수확이다. **단언이 없거나 조건부로 건너뛰던 테스트 12건**이 있었다. 클릭하고 500ms 기다리고 끝나거나, `try/catch` 로 전부 삼키고 `expect(true).toBe(true)` 로 끝나는 것들이다. 기능이 통째로 고장 나도 통과한다. 전부 실제 검증을 넣었다.
+* 헤더 검색 2건: 1자면 서버를 부르지 않고, 2자 이상이면 부르는지를 응답으로 확인
+* Escape: 드롭다운이 실제로 닫히는지. 기능 자체가 없어 함께 구현했다([SYM-101](https://linear.app/sym804/issue/SYM-101/enh-049-접근성-속성이-없어-스크린리더로-쓸-수-없다))
+* 수행 탭·대시보드 탭: 해당 화면 요소가 뜨는지
+* 검색 하이라이트: `mark.search-hl` 이 붙는지
+* 셀 편집: 저장 응답을 받고 값이 남는지
+* 선택 삭제·복제: 조건부 분기를 없애고 행 수 변화를 단언
+* 404: catch-all 라우트가 `/projects` 로 보내는지
+같이 발견한 것:
+* `test_private_accessible_after_member_add` 가 viewer 를 멤버로 넣고 정리하지 않아, 뒤에 오는 테스트가 순서에 의존한다. 새 권한 테스트는 자기만의 비멤버 계정과 프로젝트를 쓰도록 독립시켰다.
+* ag-grid 체크박스 래퍼(`.ag-selection-checkbox`)를 누르면 포커스만 가고 체크가 안 걸리는 경우가 있다. 실제 `input` 을 `check()` 해야 한다.
+완료 조건 대조:
+- [X] 회귀 스펙 6개의 `waitForTimeout` 제거(82 -&gt; 0)
+- [X] E2E 통과(94 passed). 남은 3건은 `test.skip(CI)` 가 걸린 데이터 의존 테스트로 CI 에서는 건너뛴다
+- [X] 캡처 전용 스펙은 그대로 두었다(66건)</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
           <t>- 캡처 전용 스펙(capture-*.spec.ts)의 고정 대기
@@ -17247,9 +17321,14 @@
           <t>FE 1.5.4.0</t>
         </is>
       </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>* FE 1.6.0.0 (커밋: a8d2063)</t>
+        </is>
+      </c>
       <c r="T213" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U213" t="inlineStr">
@@ -17330,14 +17409,40 @@
           <t>- 코드 리뷰 (접근성 작업 중 QA 교차 검증에서 발견)</t>
         </is>
       </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>원인: * `frontend/tsconfig.json` 은 `{"files": [], "references": [...]}` 다. 프로젝트 참조만 들고 있고 자기 파일은 없다.
+* `tsc --noEmit` 은 참조를 타지 않고 그 빈 프로젝트만 본다. 검사 대상이 0 개라 항상 종료코드 0 이다.
+* 실제 컴파일은 `npm run build` 안의 `tsc -b` 가 한다. 그래서 빌드 단계에서야 깨졌다.
+수정 내용: * `.github/workflows/ci.yml` 의 타입 검사 단계를 `npx tsc -b --force` 로 바꿔다.
+* 왜 그런지를 워크플로 주석에 남겨, 다음 사람이 `--noEmit` 으로 되돌리지 않게 했다.</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>* 별도 테스트를 붙이지 않았다. 게이트 자체가 바뀜 것이라, 이제 타입 오류가 있으면 CI 의 해당 단계가 멈춘다.
+* 이번 변경에서 실제로 잡혔다. 새 접근성 테스트가 `ChangePasswordModal` 에 없는 props 를 넘겨 TS2322 가 났고, `--noEmit` 은 그것을 통과시켰다.</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>* CI frontend 잡의 타입 검사 단계. 이제 실제로 검사한다.
+* v1.5.5.1 의 "프로덕션 빌드가 깨지던 타입 오류" 가 이 구멍으로 새어나간 건이다.</t>
+        </is>
+      </c>
       <c r="R214" t="inlineStr">
         <is>
           <t>FE 1.5.5.0</t>
         </is>
       </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>* FE 1.6.0.0 (커밋: a8d2063)</t>
+        </is>
+      </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U214" t="inlineStr">

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U214"/>
+  <dimension ref="A1:U216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -17451,6 +17451,179 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>BUG-144</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>package-lock.json 의 버전만 다른 사본과 어긋난다</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>- frontend/package-lock.json 의 version 이 1.5.5.0 인데 나머지 버전 사본 넷은 1.6.0.0 이다.
+- 어긋난 자리는 lock 파일 안에서 둘이다. 최상위 version(3행)과 packages[""] 의 version(9행).</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>- 릴리즈 노트 '현재 버전' 블록의 Frontend 값과 lock 의 version 두 자리가 같아야 한다.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>- lock 만 1.5.5.0 에 남았다. backend/main.py, frontend/package.json, i18n ko/en common.json 넷은 1.6.0.0 으로 정상이었다.</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>1. main 브랜치를 체크아웃한다(v1.6.0.0, 커밋 53ed150).
+2. Release_note.md 의 '현재 버전' 블록에서 Frontend 값을 읽는다.
+3. frontend/package-lock.json 의 3행과 9행 version 을 읽는다.
+4. 두 값을 비교한다.</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>- git log -L3,3:frontend/package-lock.json 으로 본 lock 버전 이력. 8f3d726(v1.4.0.1)까지 일치, cfa6316(v1.5.3.0)부터 벌어짐, 10f10d8 에서 npm install 이 돌아 우연히 일치, 6d19b9c(v1.5.7.0)에서 재차 벌어짐.
+- 커밋 a8d2063 의 lock diff 는 1.5.4.0 -&gt; 1.5.5.0 인데 같은 커밋의 package.json 은 1.6.0.0 이다. install 이 버전 업보다 먼저 돈 증거다.</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>FE 1.6.0.0</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SYM-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>BUG-145</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>rules/versioning.md 의 버전 이력 표가 릴리즈 절반만 담고 있다</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>- rules/versioning.md 의 '현재 버전 이력' 표에 릴리즈 노트 절 44개 중 22개가 없다.
+- 표의 마지막 행은 v1.4.0.1 이고 그 뒤 13개 릴리즈가 반영되지 않았다. 초기 구간(0.1.0.0~0.4.1.0)과 1.2.2.0, 1.2.3.0 도 빠져 있다.</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>- 표가 릴리즈 노트와 같은 릴리즈 집합을 담거나, 담지 않는다면 그 사실이 문서에 명시되어야 한다.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>- 표는 자동 검증 대상이 아니어서 조용히 벌어졌다. SYM-104 로 lock 사본을 감시 안에 넣었지만 이 표는 여전히 감시 밖이다.</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>1. Release_note.md 에서 '^## v' 로 시작하는 절을 센다.
+2. rules/versioning.md 의 '현재 버전 이력' 표 행을 센다.
+3. 두 집합의 차집합을 구한다.</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>- 2026-09-18 실측. 릴리즈 노트 절 44개, 이력 표 22개. 차집합 22건.
+- 빠진 목록: 0.1.0.0 0.2.0.0 0.2.1.0 0.2.1.1 0.3.0.0 0.4.0.0 0.4.1.0 1.2.2.0 1.2.3.0 1.4.1.0 1.5.0.0 1.5.1.0 1.5.1.1 1.5.2.0 1.5.3.0 1.5.4.0 1.5.5.0 1.5.5.1 1.5.6.0 1.5.7.0 1.6.0.0 1.6.0.1</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰. SYM-104 교차 검증 중 QA2 가 지적</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>System 1.6.0.1</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>SYM-105</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -17513,7 +17513,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>- git log -L3,3:frontend/package-lock.json 으로 본 lock 버전 이력. 8f3d726(v1.4.0.1)까지 일치, cfa6316(v1.5.3.0)부터 벌어짐, 10f10d8 에서 npm install 이 돌아 우연히 일치, 6d19b9c(v1.5.7.0)에서 재차 벌어짐.
+          <t>- git log -L3,3:frontend/package-lock.json 으로 본 lock 버전 이력. 8f3d726(v1.4.0.1)까지 일치, cfa6316(System v1.5.5.0, FE 1.5.3.0)부터 벌어짐, 10f10d8 에서 npm install 이 돌아 우연히 일치, 6d19b9c(System v1.5.7.0)에서 재차 벌어짐. v1.5.7.0 의 첫 커밋 10f10d8 은 오히려 일치했던 지점.
 - 커밋 a8d2063 의 lock diff 는 1.5.4.0 -&gt; 1.5.5.0 인데 같은 커밋의 package.json 은 1.6.0.0 이다. install 이 버전 업보다 먼저 돈 증거다.</t>
         </is>
       </c>
@@ -17522,14 +17522,39 @@
           <t>- 코드 리뷰</t>
         </is>
       </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>- 원인: 대조 테스트 test_version_consistency.py 의 감시 목록에 package-lock.json 이 없었다. 감시 안의 사본 넷은 맞아 있었고 감시 밖의 lock 만 어긋났다. lock 의 version 은 npm 이 그 시점 package.json 을 박제하는 값이라 install 을 버전 업보다 먼저 돌리면 옛 값이 박힌다.
+- 수정: lock 의 version 두 자리를 정본과 맞추고, 대조 테스트에 lock 케이스를 추가했다(감시 4곳 -&gt; 5곳).</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>- test_version_consistency.py 에 lock 두 자리를 각각 단언하는 케이스 추가. 각 자리를 따로 깨뜨려 실패하는 것까지 확인했다.
+- rules/versioning.md 에 사본 다섯 곳의 위치와 '버전 업 후 npm install' 순서 명시.
+- rules/release_process.md 체크리스트에 사본 갱신과 대조 통과 확인 2항목 추가.
+- 처음에는 skills/release.md 를 고쳤으나 그 경로는 .gitignore 의 /skills/ 로 추적되지 않아 rules/ 로 옮겼다(QA1 지적).</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>- 버전 표기만. 의존성 트리는 무변경(lock diff 2줄, 380개 패키지 항목·resolved·integrity 그대로).
+- 화면 푸터와 백엔드 앱 버전이 1.6.0.1 로 표시된다.</t>
+        </is>
+      </c>
       <c r="R215" t="inlineStr">
         <is>
           <t>FE 1.6.0.0</t>
         </is>
       </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>FE 1.6.0.1 (커밋: a1c1dd9)</t>
+        </is>
+      </c>
       <c r="T215" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U215" t="inlineStr">

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U216"/>
+  <dimension ref="A1:U218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -17649,6 +17649,181 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>BUG-146</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>문서 절을 범위로 대체하다 사이에 낀 절을 같이 지웠다</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>- rules/versioning.md 에서 '현재 버전 이력' 표를 지우면서 바로 아래 있던 '버전 사본 위치' 절이 함께 사라졌다.
+- 그 절은 직전 커밋 a1c1dd9 에서 SYM-104 재발 방지로 추가한 것이다. 사본 다섯 곳의 위치와 ' 버전 업 후 npm install' 순서를 담고 있었다.</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>- 이력 표만 제거되고 다른 절은 그대로 남아야 한다.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>- 22줄짜리 절이 통째로 삭제됐다. rules/release_process.md 의 체크리스트가 가리키는 대상이 사라져 참조가 끊겼다.</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>1. 파일에서 '## A' 절을 지우려고 s.index('## A') 부터 s.index('## C') 까지를 범위로 잡는다.
+2. A 와 C 사이에 B 절이 있는지 확인하지 않는다.
+3. 그 구간을 새 내용으로 대체한다.
+4. B 절이 함께 사라진다.</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>- 절 목록 대조. 삭제 후 rules/versioning.md 의 '## ' 헤딩은 6개였고 '## 버전 사본 위치' 가 없었다. 복구 후 7개.
+- git show HEAD:rules/versioning.md 로 직전 커밋에서 22줄 절을 그대로 추출해 복구했다.</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰. QA1(Codex)이 rules/release_process.md 의 참조가 끊겼다고 지적</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>System 1.6.0.2</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SYM-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>BUG-147</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>릴리즈 노트의 버전 체계 표가 정본과 반대되는 판정을 지시한다</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>- Release_note.md 상단 '버전 체계' 절이 rules/versioning.md 와 다른 내용을 담고 있었다.
+- 자리 이름이 달랐다. 릴리즈 노트는 system.feature.major.minor, 정본은 system.feature.fix.patch.
+- system 자리 정의가 정반대였다. 릴리즈 노트는 '대규모 리팩토링'을 system 으로 규정하는데 정본은 '리팩토링은 B 다. A 가 아니다' 로 못박고 있다.</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>- 버전 자리 판정 기준은 한 곳에만 있어야 한다. 정본은 rules/versioning.md 다.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>- 파일 맨 앞, 어떤 릴리즈 절보다 먼저 읽히는 자리에 정본과 반대되는 지시가 있었다. 이 표를 보고 판정하면 리팩토링에 A 자리를 올리게 된다.</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>1. Release_note.md 5행 '### 형식' 표의 major/minor 행을 읽는다.
+2. rules/versioning.md 3행 '## 버전 체계' 표의 fix/patch 행을 읽는다.
+3. 자리 이름과 system 자리의 정의를 비교한다.</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>- Release_note.md:5 '### 형식: system.feature.major.minor', system 기준 '대규모 리팩토링, 아키텍처 변경, 하위 호환 불가'.
+- rules/versioning.md:3 '## 버전 체계: system.feature.fix.patch', 그리고 17행 '리팩토링은 B 다. A 가 아니다. 내부 구조만 바꾼 것은 아무리 커도 B 다'.
+- 같은 유형의 실제 피해 사례가 다른 프로젝트에 있다. 전역 규칙에 'A=리팩토링' 이 잘못 적힌 채 굳어 refactor 8개 절 중 A 를 올린 것이 1개뿐이었고 24일 만에 6.0 에서 6.34 가 됐다.</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰. SYM-105 교차 검증 중 QA2 가 지적</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>System 1.6.0.2</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>SYM-107</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -17633,14 +17633,36 @@
           <t>- 코드 리뷰. SYM-104 교차 검증 중 QA2 가 지적</t>
         </is>
       </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>- 원인: 릴리즈별 컴포넌트 버전을 rules/versioning.md 이력 표와 Release_note.md 각 절이 이중으로 들고 있었다. 표는 자동 검증 대상이 아니라 조용히 벌어졌다.
+- 수정: 표를 제거하고 릴리즈 노트 각 절의 컴포넌트 버전 표를 정본으로 가리켰다.</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>- 감시를 늘리는 대신 사본을 없앴다. 지우기 전에 표 22행이 전부 릴리즈 노트에 있는지 전수 대조했고 표에만 있던 릴리즈는 0건이었다.
+- 하지 않을 것: 표를 테스트로 감시하는 방안은 택하지 않았다. 사본을 유지하는 비용이 남는다.</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>- 문서만. rules/versioning.md 의 이력 표 1개.</t>
+        </is>
+      </c>
       <c r="R216" t="inlineStr">
         <is>
           <t>System 1.6.0.1</t>
         </is>
       </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>System 1.6.1.0 (커밋: c1f564c)</t>
+        </is>
+      </c>
       <c r="T216" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U216" t="inlineStr">
@@ -17720,14 +17742,36 @@
           <t>- 코드 리뷰. QA1(Codex)이 rules/release_process.md 의 참조가 끊겼다고 지적</t>
         </is>
       </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>- 원인: 이력 표를 지우며 '## 현재 버전 이력' 부터 '## 기록 위치' 까지를 범위로 잡아 대체했다. 그 사이에 직전 커밋에서 추가한 '## 버전 사본 위치' 절이 끼어 있었다.
+- 수정: git show HEAD:rules/versioning.md 에서 22줄 절을 그대로 추출해 복구했다.</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>- 구간을 범위로 대체할 때는 그 구간에 든 '## ' 절을 먼저 세어 예상과 일치하는지 단언한다. 같은 작업의 다음 삭제(SYM-107)에 이 검사를 적용해 통과했다.
+- 절 목록(grep '^## ')을 작업 전후로 비교한다. 삭제 후 6개, 복구 후 7개로 확인했다.</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>- 커밋 전에 발견해 복구했다. 푸시된 적 없다.</t>
+        </is>
+      </c>
       <c r="R217" t="inlineStr">
         <is>
           <t>System 1.6.0.2</t>
         </is>
       </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>System 1.6.1.0 (커밋: c1f564c)</t>
+        </is>
+      </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
@@ -17808,14 +17852,36 @@
           <t>- 코드 리뷰. SYM-105 교차 검증 중 QA2 가 지적</t>
         </is>
       </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>- 원인: 버전 판정 기준이 Release_note.md 상단과 rules/versioning.md 두 곳에 있었고 내용이 갈라졌다. 릴리즈 노트 쪽이 자리 이름을 major/minor 로 쓰고 system 을 '대규모 리팩토링' 으로 규정해, 정본의 '리팩토링은 B 다. A 가 아니다' 와 반대를 지시했다.
+- 수정: 릴리즈 노트 상단 표를 제거하고 rules/versioning.md 를 정본으로 가리켰다.</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>- 판정 기준을 한 곳으로 줄였다. 사본이 없으면 갈라질 수 없다.
+- 지운 자리에 무엇이 왜 있었는지 남겨, 다시 만들지 않도록 했다.</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>- 문서만. 다만 이 표를 보고 판정했다면 리팩토링에 A 자리를 올렸을 것이다. 다른 프로젝트에서 같은 오류로 24일 만에 6.0 이 6.34 가 된 사례가 있다.</t>
+        </is>
+      </c>
       <c r="R218" t="inlineStr">
         <is>
           <t>System 1.6.0.2</t>
         </is>
       </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>System 1.6.1.0 (커밋: c1f564c)</t>
+        </is>
+      </c>
       <c r="T218" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U218" t="inlineStr">

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U218"/>
+  <dimension ref="A1:U222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -17890,6 +17890,363 @@
         </is>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ENH-051</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>테스트 수행 화면에 사전조건 열 추가</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>- 수행 화면이 보여주는 TC 필드는 no, tc_id, category, depth1, depth2, priority, test_steps, expected_result 여덟이다. precondition 은 columnDefs 에 없다.
+- 설정 문제가 아니다. TestRunManager 는 field_config 를 읽지 않아 프로젝트 설정의 필드 표시 설정이 이 화면에 적용되지 않는다.
+- 회귀가 아니다. git log -S precondition 으로 확인한 결과 이 파일에 precondition 이 있었던 적이 없다.
+- API 응답에는 담겨 온다. TestResultResponse.test_case 가 TestCaseResponse 이고 거기에 precondition 이 있다.
+- 런 엑셀 내보내기도 같다. headers 에 없고 load_only 에도 없어 아예 로드하지 않는다.</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>- 수행 화면에서 사전조건을 읽을 수 있다. 수행자가 TC 관리 화면을 따로 열지 않아도 된다.
+- 다른 TC 를 참조하는 사전조건은 툴팁으로 펼쳐 보인다.
+- 런 엑셀 내보내기에도 같은 열이 실린다.</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>- [ ] 수행 화면에 사전조건 열이 보인다
+- [ ] 그 열은 읽기 전용이다. 수행 중 TC 원문이 고쳐지지 않는다
+- [ ] 참조 형태로 쓴 사전조건이 툴팁에서 펼쳐진다
+- [ ] 런 엑셀 내보내기에 사전조건 열이 실린다
+- [ ] 위를 검증하는 테스트가 있고, 일부러 깨뜨리면 실패한다</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>- 사전조건은 실행 직전에 갖춰야 하는 상태라 수행자가 봐야 하는 정보다. Steps 와 Expected 를 보여주면서 이것만 빼면 수행 중에 화면을 옮겨다녀야 한다.
+- 이 프로젝트는 사전조건을 비중 있게 다룬다. 전용 렌더러 PreconditionCell, 참조 풀이 precondition_service, TC 내보내기의 셀 메모까지 있는데 정작 가장 필요한 화면에만 없다.</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>- TestRunManager 의 columnDefs 에 precondition 이 없었다. 설정 문제도 회귀도 아니고 처음부터 없었다. API 응답에는 담겨 오고 있었다.
+- 수행 그리드에 읽기 전용 열을 넣고 PreconditionCell 을 재사용해 참조를 툴팁으로 펼쳤다. 색인은 런의 results 로 만든다.
+- 런 엑셀(routes/testruns.py)과 리포트 엑셀(routes/reports.py) 양쪽에 같은 열을 넣었다. 리포트는 QA2 가 빠진 것을 잡았다.
+- 부수 수정: 런 엑셀 col_widths 가 헤더보다 하나 적어 폭이 밀리던 것(QA1 지적), 리포트의 결과 색칠이 열 번호를 박아 쓰던 것.</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>- GridEditorContract.test.tsx 에 계약 7건. 이 파일은 '두 그리드 중 한쪽만 고쳐 온 이력' 을 막으려고 만든 자리다.
+- tests_unit/test_run_export_columns.py 13건. 두 엑셀의 TC 열 집합이 같은지 묶었다.
+- 이빨 확인에서 두 번 구멍을 찾아 메웠다. load_only 를 빼도 지연 로딩으로 값이 나와 못 잡던 것은 조회 횟수 비교로, col_widths 밀림은 openpyxl 이 기본 폭을 돌려줘 못 잡던 것을 폭의 성질 비교로 바꿨다.
+- test_export_formula_injection.py 픽스처에 precondition 을 태웠다. 값이 없으면 전 셀을 훑어도 그 열은 검사되지 않는다.
+- 하지 않을 것: 수행 화면에서 사전조건 편집, 셀 안 참조 펼침, 프로젝트 전체 TC 를 색인용으로 추가 조회.</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>- 수행 화면에 열 하나 추가(읽기 전용). 런 엑셀과 리포트 엑셀 열 하나 추가.
+- 되가져오기는 import_service 에 Precondition 매핑이 이미 있어 그대로 들어간다.
+- 잔여 누락은 SYM-109(Platform), SYM-110(Ctrl+D 거짓 성공), SYM-111(필드 표시 설정 미적용)로 분리했다.</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>System 1.6.1.0</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>FE 1.6.1.0 / BE 1.6.1.0 (System 1.6.2.0)</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>SYM-108</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ENH-052</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>테스트 수행 화면과 런 엑셀에 Platform(test_type) 열 추가</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>- test_type(Platform)이 TC 그리드에 있고(TestCaseGrid.tsx:395) TC 목록 엑셀에도 있고(export_service.py:87) 프로젝트 설정에 숨김 가능 필드로 등록돼 있는데(ProjectSettings.tsx:397), 수행 화면과 런 엑셀에는 없다.
+- SYM-108 의 사전조건과 정확히 같은 모양의 누락이다.
+- 함께 빠진 것은 TestCase.remarks 와 custom_fields 다. 수행 그리드의 Remarks 열은 TestResult.remarks 라 이름만 같고 다른 값이다. r1~r3 은 TC 그리드에도 없는 레거시라 제외한다.</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>- 수행자가 그 TC 가 Web 인지 Android 인지 화면에서 확인할 수 있다.
+- 런 엑셀과 리포트 엑셀에도 같은 열이 실린다.</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>- [ ] 수행 화면에 Platform 열이 보이고 읽기 전용이다
+- [ ] 런 엑셀과 리포트 엑셀에 같은 열이 실린다
+- [ ] GridEditorContract 에 계약 테스트가 있다
+- [ ] TestCase.remarks 를 넣을지 뺄지 결정하고 근거를 남긴다</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>- SYM-108 을 고치며 같은 유형의 누락이 남아 있음을 확인했다. 지금 적어 두지 않으면 다음에 또 제보로 발견된다.
+- 수행 플랫폼은 실행 방법을 가르는 정보라 사전조건만큼 수행에 직접 쓰인다.</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>- r1~r3 은 넣지 않는다. TC 그리드에도 없는 레거시 칼럼이다.</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>System 1.6.1.0</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>SYM-109</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>BUG-148</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>trivial</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Ctrl+D 가 읽기 전용 TC 열에서 채웠다고 알린다</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>- 수행 그리드에서 읽기 전용 TC 열(category, test_steps, precondition 등 8개)에 Ctrl+D 를 누르면 '몇 건 채웠다' 토스트가 뜨고 저장 요청이 나간다.
+- 실제로는 아무것도 바뀌지 않는다.</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>- 편집할 수 없는 열에서는 Ctrl+D 가 아무 일도 하지 않고 토스트도 뜨지 않아야 한다.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>- TestRunManager.tsx:459-476 에서 node.data[field] = sourceValue 를 하는데 field 가 'test_case.precondition' 같은 점 찍힌 경로다. 중첩 객체가 아니라 평평한 문자열 키가 새로 생겨 화면 값은 그대로다.
+- 저장 요청은 test_case_id/result/actual_result/issue_link/remarks/duration_sec 화이트리스트라 TC 원문이 새지는 않는다.</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>- 수행 그리드에 행이 둘 이상 있고 첫 행이 선택돼 있다.</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>1. 테스트 수행 화면에서 런을 연다.
+2. Category 나 Test Steps 열의 셀을 클릭한다.
+3. 아래 행까지 선택한 뒤 Ctrl+D 를 누른다.
+4. 토스트 문구와 화면 값을 비교한다.</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>- TestRunManager.tsx:459-476 의 node.data[field] 대입. field 는 columnDefs 의 field 값이라 test_case 로 시작하는 열은 점 표기다.
+- 저장 경로는 saveOneResult(:384)와 saveManyResults(:160)이고 둘 다 고정 화이트리스트다.</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰. SYM-108 교차 검증 중 QA2 가 지적</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>System 1.6.1.0</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SYM-110</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>ENH-053</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>수행 그리드가 프로젝트의 필드 표시 설정을 따르지 않는다</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>- 프로젝트 설정의 기본 필드 설정(표시 여부, 표시 이름)은 TC 그리드에만 적용된다. TestCaseGrid.tsx:344-348 의 fieldDisplay 가 그 일을 한다.
+- 수행 그리드는 field_config 를 읽지 않고 headerName 을 영문으로 박아 둔다.
+- 그래서 필드 이름을 '사전조건 / 테스트 데이터' 로 바꾼 프로젝트에서 두 화면의 헤더가 다르게 보이고, 숨긴 필드가 수행 화면에는 그대로 나온다.</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>- 두 그리드가 같은 설정을 따른다. 이름을 바꾸면 양쪽이 같이 바뀌고, 숨기면 양쪽에서 사라진다.</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>- [ ] 수행 그리드가 project.field_config 의 표시 이름을 반영한다
+- [ ] 숨김으로 둔 필드는 수행 그리드에서도 빠진다
+- [ ] test_steps 와 expected_result 는 canHide:false 라 숨겨지지 않는다
+- [ ] 두 그리드가 같은 설정을 본다는 계약 테스트가 있다</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>- SYM-108 로 숨김 가능 필드(precondition)를 수행 화면에 하나 더 얹었다. 설정과 어긋나는 면이 그만큼 넓어졌다.
+- 제보가 '설정에서 숨긴 것 아니냐' 로 시작했던 만큼 사용자도 두 화면이 같은 설정을 따를 것이라 기대한다.</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>- 수행 전용 열(Result, Actual Result, 첨부, 소요)은 이 설정의 대상이 아니다.</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>System 1.6.1.0</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SYM-111</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -18055,9 +18055,23 @@
 - 수행 플랫폼은 실행 방법을 가르는 정보라 사전조건만큼 수행에 직접 쓰인다.</t>
         </is>
       </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>- SYM-108 과 같은 유형의 누락이었다. TC 그리드와 TC 목록 엑셀에는 있는데 수행 화면과 두 엑셀에만 없었다.
+- 수행 그리드에 읽기 전용 Platform 열을 넣고, 런 엑셀과 리포트 엑셀에도 같은 열을 넣었다.
+- TestCase.remarks 는 넣지 않기로 했다. 수행 그리드에 이미 Remarks 열이 있는데 그것은 TestResult.remarks 라, 같은 이름의 열이 둘이 되면 수행자가 어느 칸에 적을지 헷갈린다. custom_fields 는 동적 컬럼 생성이 필요해 이번 범위를 넘는다. 근거는 TestRunManager.tsx 주석에 남겼다.</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>- r1~r3 은 넣지 않는다. TC 그리드에도 없는 레거시 칼럼이다.</t>
+          <t>- GridEditorContract 에 Platform 계약 3건. 열 제거 조작에서 4건이 실패하는 것을 확인했다.
+- 리포트 엑셀에도 N+1 회귀 테스트를 걸어 런 엑셀과 대칭을 맞췄다. load_only 에서 test_type 을 빼면 실패한다.
+- 하지 않을 것: r1~r3 은 TC 그리드에도 없는 레거시라 넣지 않았다.</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>- 수행 화면 열 하나, 런 엑셀과 리포트 엑셀 각 열 하나.</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
@@ -18065,9 +18079,14 @@
           <t>System 1.6.1.0</t>
         </is>
       </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>FE 1.6.2.0 / BE 1.6.2.0 (System 1.6.3.0)</t>
+        </is>
+      </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U220" t="inlineStr">
@@ -18153,14 +18172,38 @@
           <t>- 코드 리뷰. SYM-108 교차 검증 중 QA2 가 지적</t>
         </is>
       </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>- 원인: Ctrl+D 가 열을 가리지 않고 node.data[field] 에 대입했다. field 가 'test_case.precondition' 같은 점 찍힌 경로라 중첩이 아니라 평평한 키가 새로 생겨, 화면 값은 그대로인데 토스트가 뜨고 저장 요청이 나갔다.
+- 수정: 채워도 되는 열(result, actual_result, issue_link, remarks)만 통과시킨다.
+- ★처음에는 'editable 이 false 면 막는다' 로 고쳤다가 QA 에서 뒤집혔다. 판정이 반대로 걸린 것이었다. editable 을 아예 안 쓴 열 아홉은 undefined 라 통과하고, 정작 Ctrl+D 의 주 용도인 Result 는 커스텀 렌더러 때문에 editable:false 라서 막혔다.</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>- 테스트 5건. 읽기 전용 TC 열, editable 이 undefined 인 열, 소요(초), Result, 실제 결과를 각각 본다.
+- 테스트 헬퍼가 colDef 를 손으로 만들지 않고 실제 columnDefs 에서 찾아 쓴다. 손으로 만들면 구현과 테스트가 같은 가정을 공유해 undefined 경로를 영영 못 본다.
+- 이빨 확인: 틀린 가드로 되돌리면 3건, 가드를 빼면 3건, 소요(초)를 화이트리스트에 넣으면 1건이 실패한다.</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>- 소요(초) 열에서 Ctrl+D 가 동작하지 않게 됐다. 그 열은 저장 본문 화이트리스트에 있어, 그냥 뒀으면 타이머 측정값이 실제로 덮어써져 저장됐다.</t>
+        </is>
+      </c>
       <c r="R221" t="inlineStr">
         <is>
           <t>System 1.6.1.0</t>
         </is>
       </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>FE 1.6.2.0 / BE 1.6.2.0 (System 1.6.3.0)</t>
+        </is>
+      </c>
       <c r="T221" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U221" t="inlineStr">
@@ -18226,9 +18269,21 @@
 - 제보가 '설정에서 숨긴 것 아니냐' 로 시작했던 만큼 사용자도 두 화면이 같은 설정을 따를 것이라 기대한다.</t>
         </is>
       </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>- 원인: field_config 를 TestCaseGrid 만 읽었다. 수행 그리드는 headerName 을 영문으로 박아 두고 숨김도 반영하지 않았다.
+- 수정: TC 그리드와 같은 규칙(_key + fieldDisplay)을 수행 그리드에 적용했다. 대상은 TC 에서 오는 아홉 열이다.</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>- 수행 전용 열(Result, Actual Result, 첨부, 소요)은 이 설정의 대상이 아니다.</t>
+          <t>- 수행 전용 열에는 _key 를 붙이지 않는다. 특히 Remarks 가 위험하다. 이름만 같고 TestResult.remarks 라, 섞였으면 TC 비고를 숨긴 프로젝트에서 수행 결과 비고가 사라져 결과를 못 적는다. 그것을 잡는 테스트를 따로 넣었다.
+- 하지 않을 것: 수행 전용 열(Result, 실제 결과, 첨부, 소요)은 이 설정의 대상이 아니다.</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>- 필드 이름을 바꾼 프로젝트는 수행 화면 헤더도 같이 바뀐다. 숨긴 TC 열은 수행 화면에서도 빠진다. 내보내기 파일에는 그대로 실린다.</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
@@ -18236,9 +18291,14 @@
           <t>System 1.6.1.0</t>
         </is>
       </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>FE 1.6.2.0 / BE 1.6.2.0 (System 1.6.3.0)</t>
+        </is>
+      </c>
       <c r="T222" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U222" t="inlineStr">

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -11668,14 +11668,36 @@
           <t>- 코드 리뷰 (SYM-37 QA 교차검증, Codex)</t>
         </is>
       </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>- 이번 릴리즈에서 고친 것이 아니다. 확인해 보니 v1.5.4.0(커밋 37d6363)에서 이미 해결돼 있었고 이슈만 열려 있었다.
+- backend/services/schema_guard.py 의 assert_schema_is_current 가 stamp(head) 전에 표지 컬럼을 검사하고, 없으면 SchemaMismatch 로 기동을 멈춘다. 이슈가 요구한 '어긋난 것을 감지해 기동을 멈추고 알린다' 그대로다.</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_schema_guard.py 4건이 지킨다.
+- 말만 믿지 않고 구버전 스키마(test_runs.sheet_names 없음)를 흉내낸 인스펙터로 직접 호출해 실제로 막히는 것을 확인했다.</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>- 없음. 코드는 이미 들어가 있었다.</t>
+        </is>
+      </c>
       <c r="R153" t="inlineStr">
         <is>
           <t>BE 1.3.3.0</t>
         </is>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>BE 1.5.4.0 (커밋: 37d6363)</t>
+        </is>
+      </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U153" t="inlineStr">
@@ -13376,14 +13398,36 @@
           <t>- 코드 리뷰 (SYM-54 교차 검증 중 Codex 지적)</t>
         </is>
       </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>- 원인: 다크 --accent(#4B7BBE)에 흰 글자를 얹는 조합이 4.31:1 로 일반 텍스트 AA(4.5:1)에 못 미쳤다. 프로젝트 탭, 시트 탭, 대시보드 날짜 필터가 모두 이 조합이다.
+- 수정: #4876B6 으로 조정(4.62:1). 색상(H)과 채도(S)는 그대로 두고 명도(V)만 낮춰 원래 인상을 유지했다.</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>- cssTokens.test.ts 에 토큰 명암비 검사 추가. index.css 를 직접 읽어 WCAG 상대휘도로 잰다. jsdom 은 CSS 변수를 안 풀어 주므로 axe 기반 접근성 테스트로는 이 조합을 볼 수 없다.
+- 옛 값으로 되돌리면 실패하는 것을 확인했다.</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>- 다크 테마의 선택 상태 배경색. 전후 차이가 눈에 거의 안 띄는 수준이다.</t>
+        </is>
+      </c>
       <c r="R169" t="inlineStr">
         <is>
           <t>FE 1.5.1.1</t>
         </is>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>FE 1.6.2.1 (System 1.6.3.1)</t>
+        </is>
+      </c>
       <c r="T169" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U169" t="inlineStr">
@@ -13446,9 +13490,24 @@
 - SYM-54 가 추가한 미선언 토큰 검사는 폴백이 있는 참조를 잡지 않으므로 이 자리는 계속 남는다</t>
         </is>
       </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>- 착수해 보니 절반은 이미 돼 있었다. --danger 가 --text-danger 로 바뀌고 라이트/다크 둘 다 선언된 상태였다. 남아 있던 것은 완료 조건 2번(명암비 4.5:1)이다.
+- 다크 --text-danger 가 카드 4.42 입력 4.02 였다. #F87171 로 올렸다(6.01 / 5.46).
+- 교차 검증에서 두 곳이 더 나왔다. 다크 --color-fail 이 퇴출한 #EF4444 그대로였고(배지가 아니라 ReportView 의 FAIL 건수 등 본문 글자색이다), 라이트 --text-danger 가 연분홍 경고 배경에서 4.38 이었다. 둘 다 고쳤다.
+- 검사 목록을 만들다 --color-na 가 라이트에서 4.47 인 것도 찾아 함께 고쳤다.</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>- 폴백 있는 참조 전체를 금지하는 규칙 추가는 이번 범위가 아니다</t>
+          <t>- 명암비 검사에 더해 인벤토리 단언을 넣었다. --text-* / --color-* 토큰이 검사 목록에도 제외 목록에도 없으면 실패한다. 손목록만 두면 또 샌다. 실제로 넣자마자 13개가 샜고 그중 하나가 진짜 미달이었다.
+- 한계를 파일 첫머리에 적었다. 토큰 값이 #RRGGBB 인 것만 읽으므로 rgba() 배경과 하드코딩 색은 대상 밖이다.
+- 하지 않을 것: 폴백 있는 참조 전체를 금지하는 규칙은 이번에도 넣지 않았다.</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>- 라이트와 다크의 오류 문구, FAIL/N-A 건수 글자색.</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -13456,9 +13515,14 @@
           <t>FE 1.5.1.1</t>
         </is>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>FE 1.6.2.1 (System 1.6.3.1)</t>
+        </is>
+      </c>
       <c r="T170" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U170" t="inlineStr">

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U222"/>
+  <dimension ref="A1:U223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12931,7 +12931,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>minor</t>
+          <t>major</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -12956,7 +12956,8 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>- 파일에 같은 No 가 두 번 있으면 두 행 모두 같은 TC ID 로 계산된다. 첫 임포트에서는 TC-001 과 TC-001-2 로 갈라지지만, 두 번째 임포트에서는 둘 다 TC-001 을 찾는다</t>
+          <t>- 두 행이 모두 TC-001 을 찾아 앞 행을 두 번 덮는다. 뒤 행의 내용은 영영 반영되지 않는데 결과는 updated 2 로 보고된다.
+- 사용자가 엑셀에 적은 TC 내용이 조용히 사라지므로 전역 규칙의 데이터 이슈 하한(Major 이상)을 적용한다.</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -12982,14 +12983,41 @@
           <t>- 코드 리뷰</t>
         </is>
       </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>- 원인: TC ID 칸이 빈 행에 파일의 No 로 ID 를 만들어 주는데, 파일에 같은 No 가 둘이면 두 행이 같은 ID 로 계산된다. 첫 임포트는 채번(allocate_tc_id)이 -2 를 붙여 갈라 주지만, 채번 결과는 다음 임포트에서 파서가 재계산해 낼 수 없다. 그래서 재임포트에서 두 행이 모두 TC-001 을 찾아 앞 행을 두 번 덮는다.
+- 수정: 파일 안 중복을 파서가 직접 -2, -3 으로 가른다. 결정적이라 재임포트에서도 같은 값이 나온다.
+- 파일에 적힌 ID 와 No 로 만든 ID 를 한 이름공간(점유 집합)에서 관리한다. 나누면 명시 ID 가 파생 ID 와 부딪칠 때 같은 증상이 남는다.
+- ★세 번째 시도다. 앞선 두 번은 되돌렸다. 매칭 키를 읽은 차례로 바꾸거나 옛 규칙 호환 매칭을 붙이는 방향이었는데, 둘 다 기존 데이터를 못 찾거나 다중 시트에서 깨졌다.</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_tc_id_dedup.py 에 27건. 재임포트, 명시 ID 혼합, 명시 ID 와 파생 ID 충돌, No=0, CSV/MD 경로, dedupe_in_file 직접 호출.
+- ★라우트 차례(park_sheet_numbers -&gt; _parse_sheet -&gt; renumber_sheet)를 태우는 테스트를 넣었다. 단위 테스트만으로는 라우트가 하는 일의 절반만 재현해 증상을 오진했다.
+- 이빨 확인: 파일 안 중복 처리를 빼면 3건, 접미사 모양을 바꾸면 6건, 읽은 차례 방식으로 바꾸면 8건, 점유 집합을 파서끼리 공유하면 8건 실패.
+- 하지 않을 것: 시트를 가로지르는 매칭은 이번 범위가 아니다. SYM-112 로 분리했다.</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>- 임포트 세 경로(엑셀/CSV/Markdown) 전부. 만들어지는 TC ID 는 예전과 같아 이미 임포트해 둔 데이터의 재임포트가 그대로 이어진다.
+- 예외: 다른 시트가 이미 그 ID 를 쓰고 있으면 채번이 한 번 더 붙어 TC-001-2-2 가 된다(옛 코드는 TC-001-4). SYM-112 범위다.</t>
+        </is>
+      </c>
       <c r="R165" t="inlineStr">
         <is>
           <t>BE 1.5.0.0</t>
         </is>
       </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>BE 1.6.3.0 (System 1.6.4.0)</t>
+        </is>
+      </c>
       <c r="T165" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U165" t="inlineStr">
@@ -18371,6 +18399,101 @@
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>BUG-149</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>시트가 여럿인 파일을 다시 임포트하면 두 번째 시트부터 실패한다</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>- 시트마다 No 가 1 부터 시작하는 워크북을 임포트하면 두 번째 시트의 TC ID 에 접미사가 붙는다(TC-001-2).
+- 같은 파일을 다시 넣으면 파서는 여전히 TC-001 을 계산하는데 그 ID 는 그 시트에 없다. 기존 행을 못 찾아 새로 만든다.
+- 임포트할 때마다 행이 불어난다. 2건이 4건, 다시 넣으면 6건이 된다.</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>- 시트가 여럿이어도 재임포트가 각 시트의 기존 행을 찾아 갱신한다.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>- 2회차 두 번째 시트가 created 2, updated 0 으로 보고된다. 갱신이 아니라 추가다.
+- 실측: S1 No 1,2 / S2 No 1,2 인 워크북을 두 번 넣으면 최종 6행(기대 4). S2 에 TC-001-2 와 TC-001-3 이 같은 내용으로 남는다.</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>- 시트가 둘 이상이고 각 시트의 No 가 1 부터 시작하는 파일. TC ID 칸은 비어 있다.</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>1. 시트 S1(No 1,2)과 S2(No 1,2)를 담은 엑셀을 만든다. TC ID 칸은 비운다.
+2. 임포트한다. S1 은 TC-001,TC-002 / S2 는 TC-001-2,TC-002-2 가 된다.
+3. 같은 파일을 다시 임포트한다.</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>- 2026-09-18 실측. 라우트와 같은 차례(park_sheet_numbers -&gt; _parse_sheet -&gt; renumber_sheet)로 재현했다.
+- 처음에 이 이슈를 IntegrityError 로 적었는데 틀렸다. 그 예외는 park_sheet_numbers 를 뺀 단위 테스트에서만 난다. 라우트는 기존 번호를 음수로 비켜 두므로 유니크 제약에 안 걸리고 대신 조용히 행이 복제된다.
+- SYM-51 수정 전 코드(커밋 f9e1609)에서도 같은 결과다. 원래 있던 결함이다.
+- 원인: import_service.py 의 existing_map 은 시트 단위인데(:249) taken_tc_ids 는 프로젝트 전체다(:254).</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰. SYM-51 교차 검증 중 QA2 가 지적</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>BE 1.6.2.0</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>SYM-112</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -18478,14 +18478,41 @@
           <t>- 코드 리뷰. SYM-51 교차 검증 중 QA2 가 지적</t>
         </is>
       </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>- 원인: existing_map 은 시트 단위인데 채번(taken_tc_ids)은 프로젝트 전체를 본다. 그래서 두 번째 시트의 TC-001 은 첫 시트와 부딪쳐 TC-001-2 로 저장되는데, 다음 임포트에서 파서는 여전히 TC-001 을 계산한다. 기존 행을 못 찾아 새로 만들고 행이 불어난다. SYM-51 과 같은 뿌리다.
+- 수정: 조회가 실패하면 채번이 접미사를 붙여 저장한 행을 이 시트에서 되짚는다(find_parked_by_base).
+- 접미사를 2, 3 으로 세어 올라가지 않고 맵 키를 훑어 가장 작은 것을 고른다. 세 번째 시트의 파킹 ID 는 base-3 인데 base-2 는 다른 시트 소유라 세어 올라가면 첫 구멍에서 끊긴다.
+- 되짚기는 base 가 프로젝트에 실제로 있을 때만 한다. 접미사는 누가 base 를 쓰고 있어서 붙는 것이라, base 가 없으면 그 base-2 는 사람이 손으로 붙인 ID 다.</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>- 테스트 38건. 세 시트 반복 임포트, 사람이 붙인 ID 보호, CSV/MD 되짚기, 빈 시트 첫 임포트, 후보 연속, find_parked_by_base 단위 동작, 성능 상한.
+- ★작업 중 세 가지 회귀를 만들었다가 교차 검증에서 잡혔다. (1) 되짚기가 사람이 붙인 ID 를 덮었다 (2) explicit_ids 스캔이 max_row 까지 훑으며 셀마다 병합 범위를 봐서 임포트가 0.16초에서 109초가 됐다 (3) 세 번째 시트부터는 안 고쳐져 있었다.
+- 성능 회귀는 테스트로 막았다. 서식으로 max_row 가 부푼 병합 워크북을 3초 상한으로 잰다. 이 종류는 4행짜리 테스트로는 영영 안 잡힌다.
+- 하지 않을 것: 파서가 계산한 키를 행에 저장하는 근본 처방은 DB 축 변경이라 이번 범위가 아니다.</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>- 임포트 세 경로(엑셀/CSV/Markdown)의 재임포트 매칭. 첫 임포트 결과는 예전과 같다.
+- 남는 한계: base 를 쥔 행이 소프트 삭제된 뒤 재임포트하면 되짚지 못해 행이 하나 는다. 덮어쓰기보다 가벼운 실패라 이쪽을 택했다.</t>
+        </is>
+      </c>
       <c r="R223" t="inlineStr">
         <is>
           <t>BE 1.6.2.0</t>
         </is>
       </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>BE 1.6.4.0 (System 1.6.5.0)</t>
+        </is>
+      </c>
       <c r="T223" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U223" t="inlineStr">

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U223"/>
+  <dimension ref="A1:U224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -18521,6 +18521,89 @@
         </is>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>ENH-054</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>테스트 수행 화면에서 우선순위를 하나만 고를 수 있다</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>- 테스트 수행 화면의 Priority 필터가 단일 select 라 한 번에 한 값만 고른다
+- 핵심과 중요를 같이 보려면 값을 바꿔 가며 두 번 확인해야 한다
+- AG Grid 컬럼 필터는 꺼져 있고, 체크박스형 Set Filter 는 Enterprise 기능이라 community 35.1.0 에서는 쓸 수 없다</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>- 우선순위를 여러 개 함께 고른다. 고른 것 중 하나라도 맞는 행이 남는다
+- 버튼에 고른 값이, 둘 이상이면 개수가 표시된다
+- 우선순위를 비워 둔 TC 가 있으면 (미지정) 선택지가 생겨 그 행만 따로 볼 수 있다</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>- [ ] 우선순위를 여러 개 체크하면 OR 로 걸린다
+- [ ] Result, Category, 검색어와는 AND 로 합쳐진다
+- [ ] 값이 빈 행을 (미지정) 으로 골라낼 수 있다
+- [ ] 시트를 옮겨 고른 값이 그 시트에 없어도 체크를 풀 수 있다
+- [ ] 바깥 클릭과 Esc 로 닫힌다
+- [ ] 다크 테마에서 활성 버튼 명암비가 AA 를 넘는다</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>- 회귀 수행에서 핵심과 중요만 먼저 도는 일이 잦은데, 지금은 두 번 나눠 확인해야 한다
+- 우선순위가 빈 TC 는 어떤 값을 골라도 화면에서 사라지는데 그 사실을 알 방법이 없다</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>- Result 와 Category 의 멀티 선택. 이번 범위는 우선순위만
+- 드롭다운 포커스 트랩. 기존 결과 일괄입력 드롭다운도 없어 따로 다룬다</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>FE 1.6.2.1</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SYM-113</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U224"/>
+  <dimension ref="A1:U227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -18582,6 +18582,17 @@
 - 우선순위가 빈 TC 는 어떤 값을 골라도 화면에서 사라지는데 그 사실을 알 방법이 없다</t>
         </is>
       </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>* `useResultFilters` 의 `filterPriority`(string) 를 `filterPriorities`(string\[\]) 로 바꾸고 `togglePriority` 를 더했다. 빈 배열이 "전체"다
+* Priority 필터를 체크박스 드롭다운으로 교체했다. 버튼 라벨은 전체 / 고른 값 / 개수 순으로 바뀐다
+* 우선순위가 빈 행이 있을 때만 (미지정) 선택지가 생긴다. 실측으로 이 값이 있는 TC 가 162건 있었다(ymseo_test 160, 런시트범위\_tmp 2)
+* 고른 값이 현재 결과 집합에 없어도 목록에 남긴다. 시트별 우선순위 구성이 달라(stockradar 의 "표면 커버리지 보강" 시트는 중요 하나뿐) 시트를 옮기면 체크를 풀 수단이 사라지고 그리드가 빈 채로 잠겼다
+* 바깥 클릭과 Esc 로 닫고, 런이나 시트를 옮기면 열린 드롭다운을 닫는다
+* 활성 버튼을 accent 배경에 흰 글자로 칠했다. accent 를 글자색으로 쓰면 다크에서 3.27:1 로 AA(4.5:1) 에 못 미쳤다. 이 변수는 흰 글자를 얹는 배경 기준으로 보정된 값이다(4.62:1)
+* 완료 조건과 어긋난 것은 없다</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>- Result 와 Category 의 멀티 선택. 이번 범위는 우선순위만
@@ -18593,14 +18604,327 @@
           <t>FE 1.6.2.1</t>
         </is>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>FE 1.6.3.0 (System 1.6.6.0, 커밋 a35160f)</t>
+        </is>
+      </c>
       <c r="T224" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U224" t="inlineStr">
         <is>
           <t>SYM-113</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>ENH-055</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>테스트 수행 시트에서 셀 텍스트를 끌어서 복사할 수 없다</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>- 셀 안의 글자를 마우스로 끌어도 선택되지 않는다. AG Grid 가 user-select:none 을 걸기 때문이다.
+- 절차·기대 결과·사전조건은 읽기 전용 열인데도 복사가 막혀 있다. 편집도 안 되고 복사도 안 되는 상태다.</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>- 셀 안의 글자를 끌어 선택해 복사할 수 있다.
+- 읽기 전용 열과 편집 가능 열 모두에서 된다.</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>- [x] 두 그리드에서 셀 텍스트를 끌어 선택할 수 있다
+- [x] 읽기 전용 열에서도 선택된다
+- [x] 결과 드롭다운, Shift+클릭 범위 채우기, Ctrl+D 가 그대로 동작한다</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>- 수행자가 절차나 기대 결과를 다른 곳에 옮길 때마다 막힌다. 눈으로 읽고 손으로 옮기는 수밖에 없다.
+- 같은 화면을 매일 쓰는 작업이라 누적 비용이 크다.</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>- 두 그리드에 enableCellTextSelection 과 ensureDomOrder 를 켰다.
+- 브라우저에서 user-select 가 text 로 바뀐 것과 실제로 글자가 선택되는 것을 확인했다.</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>- AG Grid 범위 복사(Ctrl+C 로 여러 셀) 는 Enterprise 기능이라 넣지 않는다. Community 에는 없다.</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>FE 1.6.3.0</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>FE 1.6.4.0</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SYM-114</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>BUG-150</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>TC 그리드가 클릭 한 번에 편집 모드로 들어간다</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>- TC 관리 그리드에서 셀을 한 번 클릭하면 곧바로 편집기가 열린다.
+- 값을 고칠 생각 없이 내용만 확인하려 해도 편집 상태가 되어, 잘못 누르면 값이 바뀐다.
+- 편집기가 열린 칸은 글자를 끌어서 선택할 수 없다.</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>- 클릭 한 번은 셀 선택까지만 한다.
+- 편집은 더블클릭이나 F2 로 시작한다. 사용자 매뉴얼도 그렇게 안내하고 있다.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>- 클릭 즉시 인라인 편집기가 열렸다.</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>1. TC 관리 그리드를 연다.
+2. 아무 셀이나 한 번 클릭한다.
+3. 편집기가 열린 것을 확인한다.</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>- 매뉴얼 grid_li1 은 '셀을 더블 클릭하면 인라인 편집 모드로 진입합니다' 라고 적고 있었다(frontend/src/i18n/ko/manual.json:195). 문서가 맞고 구현이 달랐다.
+- 그리드 설정에 singleClickEdit={true} 가 있었다(TestCaseGrid.tsx, TestRunManager.tsx).</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>- 사용자</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>원인: - 두 그리드 모두 singleClickEdit 을 켜 두었다. 빠른 입력을 노린 설정으로 보이나 매뉴얼과 어긋났고, 편집기가 열리면 텍스트 선택이 막히는 부작용이 있었다.
+수정 내용: - 두 그리드에서 singleClickEdit 을 제거해 AG Grid 기본값인 더블클릭 편집으로 되돌렸다.
+- 셀 선택 후 바로 타이핑하는 진입은 그대로라 대량 입력의 타수는 늘지 않는다.</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>- 유닛 계약 테스트에 두 그리드의 singleClickEdit 이 true 가 아닌지 단언을 넣었다(GridEditorContract.test.tsx).
+- E2E 에 실제 DOM 기준 단일 클릭/더블클릭 검증을 넣었다. singleClickEdit 을 일부러 되살려 그 테스트가 실패하는 것까지 확인했다.</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>- TC 관리 그리드와 테스트 수행 그리드의 편집 진입 방식.</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>FE 1.6.3.0</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>FE 1.6.4.0</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SYM-115</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>BUG-151</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>trivial</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>매뉴얼이 구현되지 않은 Ctrl+C/V 셀 복사 기능을 안내한다</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>- 사용자 매뉴얼 단축키 표에 'Ctrl + C / V = 복사 / 붙여넣기, TC 관리 그리드' 항목이 있다.
+- 그런 기능이 구현되어 있지 않다. 안내를 보고 눌러도 아무 일도 일어나지 않는다.</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>- 매뉴얼은 실제로 되는 것만 적는다.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>- 되지 않는 조작을 표에 싣고 있었다.</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>1. 운영 매뉴얼의 단축키 표를 연다.
+2. TC 관리 그리드에서 셀을 선택하고 Ctrl+C 를 누른다.
+3. 다른 셀에서 Ctrl+V 를 누른다.</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>- AG Grid 의 셀 범위 복사·붙여넣기는 Enterprise 전용이다. 이 프로젝트는 ag-grid-community 만 쓰고 ClipboardModule 도 LicenseManager 도 없다(등록 모듈은 AllCommunityModule 하나).
+- 앱 코드에도 Ctrl+C 처리가 없다(grep 0건).
+- 브라우저에서 셀에 포커스만 준 채 복사를 시도하면 선택된 글자가 없어 아무것도 복사되지 않는 것을 확인했다.</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>원인: - 구현되지 않은 기능이 매뉴얼에 적혀 있었다. 언제 들어갔는지는 확인하지 못했다.
+수정 내용: - 단축키 표 문구를 '끌어서 선택한 글자 복사 / 편집 중 붙여넣기' 로 고치고 적용 위치를 두 그리드로 바로잡았다(ko/en).
+- 그리드 편집 설명에 한 번 클릭은 선택이고 그 상태에서 글자를 끌어 복사할 수 있다는 문장을 넣었다.</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>- 붙이지 못했다. 매뉴얼 문구가 실제 동작과 맞는지 기계로 확인할 방법이 없다. 단축키 표 항목마다 대응하는 E2E 를 두는 것이 근본 처방이나 이번 범위를 넘는다.</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>- 사용자 매뉴얼 단축키 표와 그리드 편집 설명(ko, en).</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>FE 1.6.3.0</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>FE 1.6.4.0</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>SYM-116</t>
         </is>
       </c>
     </row>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U227"/>
+  <dimension ref="A1:U228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -18928,6 +18928,114 @@
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>BUG-152</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>릴리즈 태그가 45개 빠져 있었다</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>- rules/release_process.md 가 커밋 뒤에 git tag 와 git push --tags 를 지시하는데 지켜지지 않았다.
+- 릴리즈 노트 절 52개 중 태그가 달린 것은 7개뿐이었다. v1.2.1.0 이후로 45개가 통째로 빠져 있었다.
+- 버전별 코드 상태를 되짚을 수단이 없었다.</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>- 릴리즈마다 태그가 남는다.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>- 2026-04-08 의 v1.2.1.0 이 마지막 태그였다.</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>1. git tag 목록을 뽑는다.
+2. Release_note.md 의 버전 절 목록과 대조한다.</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>- 태그 7개 대 릴리즈 노트 절 52개. GitHub 릴리즈 페이지도 v1.2.0.0 이 마지막이었다.</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>- 사용자</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>원인: - 절차 문서에만 적혀 있고 확인하는 장치가 없었다. 버전 사본이 어긋났던 것과 같은 유형이다.
+수정 내용: - 커밋 메시지의 (vX.X.X.X 표기로 릴리즈 커밋을 찾아 34개를 소급해 달고 푸시했다.
+- 남은 11개(v1.2.2.0 과 v0.x 초기 버전)는 커밋을 특정하지 못해 달지 않았다. 틀린 태그는 없는 태그보다 나쁘다.</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>- test_version_consistency.py 에 지난 릴리즈의 태그 존재를 확인하는 테스트를 넣었다. 최신 절 하나는 면제하므로 한 박자 늦게 잡는다.
+- 태그를 일부러 지워 그 테스트가 실패하는 것까지 확인했다.</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>- 릴리즈 절차와 태그 이력. 제품 동작은 바뀌지 않는다.</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>System 1.6.7.0</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>System 1.6.7.1</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SYM-117</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U228"/>
+  <dimension ref="A1:U234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -19036,6 +19036,600 @@
         </is>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>BUG-153</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>리포트에 BLOCK 결과의 상세가 빠진다</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>- BLOCK 건수는 요약 카드와 분류 표에 나오지만 어떤 TC 가 왜 막혔는지는 웹 리포트, PDF, 연관 이슈 목록 어디에도 없다
+- BLOCK 만 있는 수행은 '실패 항목이 없습니다' 로 나온다</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>- BLOCK 결과도 TC, 실제 결과, 이슈 링크와 함께 리포트 상세 목록에 실린다</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>- project 116 run 25(BLOCK 2건, 실제 결과 기재): /reports 응답의 top_failures 와 jira_issues 가 빈 배열</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>1. BLOCK 결과가 있고 FAIL 이 없는 수행을 고른다
+2. 리포트 탭에서 그 수행을 선택한다
+3. 주요 실패 항목과 PDF 를 본다</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>- run 25 리포트 JSON: summary.block=2, top_failures=[]</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>- 실서버 팩트체크(QA 2인)</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>원인: - routes/reports.py 의 _failed_items 가 result == FAIL 만 조회했다. 엑셀 Results 시트만 전 결과를 실어 BLOCK 상세가 거기에만 있었다
+수정 내용: - FAIL 과 BLOCK 을 함께 조회해 우선순위 높은 순으로 싣고 result 에 실제 값을 넣는다. 연관 이슈도 두 결과에서 모은다(순서 보존, 중복 제거)</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_report_content.py 에 BLOCK 만 있는 수행 테스트. ReportView.test.tsx 에 BLOCK 행 표시 테스트</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>- 웹 리포트, PDF 리포트, 연관 이슈 목록</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>BE 1.6.4.0</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>System 1.6.8.0 / BE 1.6.5.0 / FE 1.6.5.0</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>SYM-118</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>BUG-154</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>PDF 리포트 요약 표의 합격률 칸이 페이지 밖으로 잘린다</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>- PDF Summary 표의 Pass Rate 머리글이 'Pas', 값이 '9' 로 잘려 합격률을 읽을 수 없다</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>- 표가 본문 폭 안에 들어오고 합격률이 온전히 보인다</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>- 칸 27mm x 8 = 216mm 로 A4 본문 190mm 를 넘는다. 값이 x=590pt(페이지 폭 595pt)에서 시작한다</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>1. 아무 수행의 PDF 리포트를 받는다
+2. Summary 표 오른쪽 끝을 본다</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>- report_25.pdf 렌더 이미지, pypdf 좌표 x=590.2pt</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>- 실서버 팩트체크(QA 2인)</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>원인: - 칸 폭을 숫자로 박아 두고 칸을 늘리면서 합이 본문 폭을 넘었다
+수정 내용: - 칸 폭을 pdf.epw 에서 나눈다. 페이지를 넘는 표는 머리행을 다시 그린다. 굵은체 파일 등록, Version None -&gt; N/A, 날짜 표기, 말줄임 표시도 함께 고쳤다</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>- 합격률 값의 x 좌표가 여백선 안인지 보는 테스트. 옛 배치(27mm 고정)로 실패하는 것 확인</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>- PDF 리포트</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>BE 1.6.4.0</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>System 1.6.8.0 / BE 1.6.5.0 / FE 1.6.5.0</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SYM-119</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>BUG-155</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>한글 폰트가 없는 서버에서 PDF 리포트가 500 오류를 낸다</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>- 한글 폰트가 설치되지 않은 리눅스 서버와 CI 에서 PDF 리포트가 실패한다</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>- 서버 환경과 무관하게 한글이 든 PDF 가 만들어진다</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>- 폰트 탐색이 실패하면 Helvetica 로 떨어지고, 프로젝트명이나 수행명에 한글이 한 글자만 있어도 FPDFUnicodeEncodingException 이 난다</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>- 서버에 맑은 고딕과 나눔고딕이 없다</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>1. 한글 폰트가 없는 환경에서 백엔드를 띄운다
+2. 이름에 한글이 있는 수행의 PDF 리포트를 받는다</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>- FPDF Helvetica 에 한글 cell 출력 시 FPDFUnicodeEncodingException 재현</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(QA1 지적 후 재현)</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>원인: - 폰트를 시스템 경로에서만 찾았다. 맑은 고딕은 재배포가 안 돼 레포에 넣을 수 없었다
+수정 내용: - Pretendard(OFL-1.1) Regular/Bold TTF 와 OFL.txt 를 backend/fonts 에 넣고 첫 후보로 쓴다</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>- 한글 폰트가 없으면 skip 하던 PDF 테스트를 없애고, 레포 폰트가 실제로 잡히는지 단언한다. CI 에서도 PDF 테스트가 돈다</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>- PDF 리포트(리눅스 배포, CI)</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>BE 1.6.4.0</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>System 1.6.8.0 / BE 1.6.5.0 / FE 1.6.5.0</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>SYM-120</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>BUG-156</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>리포트 다운로드 파일 이름과 날짜, 이슈 링크 표기가 틀리다</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>- 다운로드 파일이 report_번호.pdf 로 저장된다
+- 수행일 칸에 생성일이 나온다
+- 이슈 키만 적은 링크가 href=# 로 걸린다
+- 엑셀 합격률이 문자열이다</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>- 파일 이름이 프로젝트명_Report_R라운드 이고, 생성일과 완료일이 따로 나오고, 이슈 키는 Jira Base URL 로 이어지고, 엑셀 합격률은 숫자다</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>- 브라우저 suggestedFilename 이 report_25.pdf. 엑셀 Summary I7 셀이 문자열 '92.0%'</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>1. 리포트 탭에서 PDF/Excel 을 받는다
+2. 파일 이름과 엑셀 합격률 셀을 본다</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>- Playwright 다운로드 이벤트 suggestedFilename, openpyxl 셀 타입 str</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>- 실서버 팩트체크(QA 2인)</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>원인: - 화면이 파일 이름을 직접 정했고, 엑셀에 f-string 으로 넣었고, 링크는 http 가 아니면 # 로 걸었다
+수정 내용: - Content-Disposition 을 읽어 파일 이름을 쓴다(CORS expose_headers 추가). 합격률을 숫자 + 0.0% 서식으로. resolveIssueUrl 로 이슈 키를 링크하고 못 만들면 글자로만 둔다</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>- 파일 이름, 날짜, 링크, 엑셀 숫자 셀 테스트 추가</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>- 리포트 화면, PDF/엑셀 다운로드</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>FE 1.6.4.0</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>System 1.6.8.0 / BE 1.6.5.0 / FE 1.6.5.0</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>SYM-121</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>ENH-056</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>리포트에 우선순위별 요약과 직전 수행 대비를 싣는다</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>- 리포트는 전체 요약과 분류별 건수만 싣는다. 우선순위별 결과와 직전 수행 대비 변화는 대시보드와 비교 화면에서 따로 봐야 한다</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>- 웹/PDF/엑셀 리포트에 우선순위별 요약, 분류별 PASS Rate, 직전 수행 대비 퇴보/개선, 수행자가 실린다</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>- [ ] 우선순위 높은 것부터 요약되고 빈 우선순위는 한 줄로 모인다
+- [ ] 퇴보/개선 판정이 비교 화면과 같다
+- [ ] 엑셀 Summary 에 같은 표가 있다</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>- 리포트는 밖으로 나가는 산출물이라 받는 사람이 다른 화면을 볼 수 없다. 출시 판단에 필요한 높은 우선순위 실패 수가 리포트에 없다</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>- 완료 조건 전부 충족. 변경 건수는 두 런 모두 수행한 TC 만 센다(직전 런이 진행 중이면 NS -&gt; PASS 잡음이 생겨서). 매뉴얼에 차이를 적었다</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>- 출시 판정(Go/No-Go) 기준. 기준을 정해야 해서 뺀다</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>BE 1.6.4.0</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>System 1.6.8.0 / BE 1.6.5.0 / FE 1.6.5.0</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SYM-122</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>BUG-157</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>테스트 수행 그리드의 이슈 키가 Jira 링크로 이어지지 않는다</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>- 매뉴얼은 이슈 키를 적으면 Jira Base URL 로 이동한다고 안내하지만 테스트 수행 그리드의 Issue Link 칸은 글자일 뿐이다</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>- 이슈 키 또는 http(s) 주소가 링크로 열린다</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>- TestCaseGrid 는 jiraBaseUrl 을 context 에 넣기만 하고 읽는 렌더러가 없다. TestRunManager 의 issue_link 칸에는 렌더러가 없다</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>1. 프로젝트 설정에 Jira Base URL 을 넣는다
+2. 테스트 수행에서 Issue Link 칸에 PROJ-1 을 적는다
+3. 그 칸을 누른다</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>- grep: jiraBaseUrl 소비 코드 0건. manual.json tcManage.field_issueLink, settings.pi_li2</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>- QA2 팩트체크</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>FE 1.6.5.0</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SYM-123</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U234"/>
+  <dimension ref="A1:U237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -19630,6 +19630,283 @@
         </is>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>BUG-158</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>시트가 여럿인 프로젝트에서 TC 관리를 열면 사이드바와 표의 시트가 다르다</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>- TC 관리를 누르면 사이드바는 첫 시트가 활성인데 표에는 전체 시트의 TC 가 나온다</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>- 사이드바에서 활성인 항목과 표의 데이터가 같은 범위다</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>- project 116: 사이드바 '인증/보안' 활성, 표 끝 행이 HOME-030, DET-072(다른 시트)</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>- 시트가 2개 이상인 프로젝트</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>1. 다른 탭에서 TC 관리 탭을 누른다
+2. 사이드바 활성 항목과 표의 TC ID 를 본다</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>- 간헐</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>- Playwright 에서 전체 요청 응답을 0.6초 늦추면 항상 재현. 전체 요청과 첫 시트 요청이 동시에 나가고 전체 응답이 뒤에 도착</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>- 사용자</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>원인: - 처음 열 때 전체로 조회하면서 동시에 첫 시트를 자동 선택해 두 요청이 겹쳤다. loadData 에 요청 순서 보호가 없어 늦게 온 응답이 표를 덮었다
+수정 내용: - 시트가 여럿이면 처음에 전체로 연다. 하나면 그 시트를 선택한다(시트를 지워 하나 남았을 때도). loadData 와 고급 필터 적용이 요청 순번을 공유해 옛 응답을 버린다</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>- TcNoDragGuard.test.tsx 에 옛 응답 무시, 전체로 열기, 시트 삭제 후 재선택 테스트. 가드를 빼면 실패하는 것 확인. QA2 브라우저 지연 주입 65회 불일치 0건</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>- TC 관리 화면. 시트가 여럿이면 처음에는 행 추가가 꺼져 있고 시트를 골라야 켜진다</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>FE 1.6.5.0</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>System 1.6.9.0 / FE 1.6.6.0</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>SYM-124</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ENH-057</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>테스트 수행 시트의 우선순위에 TC 시트와 같은 색을 넣는다</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>- TC 관리 그리드는 우선순위를 색으로 구분하지만 테스트 수행 그리드는 글자만 보인다. 선택지는 매우 낮음까지 5단계다</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>- 두 그리드가 같은 색과 표시 이름을 쓴다. 우선순위는 매우 높음/높음/보통/낮음 4단계다</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>- [ ] 수행 그리드 우선순위 칸이 TC 그리드와 같은 색이다
+- [ ] 색과 값 목록을 한 모듈이 가진다
+- [ ] 매우 낮음이 선택지, 매뉴얼, TC 작성 가이드에서 빠진다</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>- 수행 중에 높은 우선순위를 먼저 봐야 하는데 수행 시트에서는 구분되지 않는다</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>- 완료 조건 충족. utils/priority.ts 로 공용화. 영어 모드에서는 우선순위 필터 메뉴도 칸과 같은 표시 이름</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>- 목록에 없는 옛 값(중간, High 등)을 4단계로 바꾸는 데이터 정리</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>FE 1.6.5.0</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>System 1.6.9.0 / FE 1.6.6.0</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>SYM-125</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ENH-058</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>이슈 링크 설정을 Jira 전용이 아닌 이슈 관리 도구 주소로 바꾼다</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>- 설정 이름이 Jira Base URL 이고 이슈 키를 항상 주소/browse/키 로 만든다. 주소는 프로젝트를 만들 때만 입력할 수 있다</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>- 이름이 이슈 관리 도구 주소다. Linear 주소는 /issue/키, {key} 자리표시자도 받는다. 설정 탭에서 바꿀 수 있다</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>- [ ] 화면과 매뉴얼, 문서에 Jira Base URL 표기가 남지 않는다(Jira CSV 가져오기 제외)
+- [ ] Linear 워크스페이스 주소와 팀 화면 주소 모두 올바른 이슈 링크가 된다
+- [ ] 설정 탭에서 저장된다</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>- Linear 를 쓰는 프로젝트가 있는데 Jira 주소 형식으로만 링크가 만들어진다</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>- 완료 조건 충족</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>- DB 컬럼 이름(jira_base_url) 변경. 수행 그리드의 이슈 키 링크(SYM-123)</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>FE 1.6.5.0</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>System 1.6.9.0 / FE 1.6.6.0</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>SYM-126</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -19614,14 +19614,35 @@
           <t>- QA2 팩트체크</t>
         </is>
       </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>- 원인: 테스트 수행 그리드의 issue_link 칸에 렌더러가 없었고, TestCaseGrid 는 jiraBaseUrl 을 context 에 넣기만 하고 읽지 않았다. 매뉴얼만 기능을 약속했다
+- 수정: IssueLinkCell 렌더러가 이슈 키나 주소 옆에 ↗ 를 붙인다(resolveIssueUrl, 리포트와 같은 규칙). ↗ 는 포커스를 받지 않고, 더블클릭과 Enter 가 셀 편집으로 번지지 않게 브라우저 리스너로 막는다</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>- IssueLinkCell 단위 테스트 13건(브라우저 리스너 기준 전파, 포커스, 값 변경 뒤 리스너), GridEditorContract 에 렌더러와 trackerUrl 값 계약, E2E TC-RUN-023(↗ 더블클릭, 가운데 클릭 뒤 Enter, 링크 포커스 Enter). 각 테스트는 수정을 빼면 실패하는 것 확인</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>- 테스트 수행 그리드 Issue Link 칸. 매뉴얼과 docs 의 이슈 링크 설명</t>
+        </is>
+      </c>
       <c r="R234" t="inlineStr">
         <is>
           <t>FE 1.6.5.0</t>
         </is>
       </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>System 1.6.10.0 / FE 1.6.7.0</t>
+        </is>
+      </c>
       <c r="T234" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U234" t="inlineStr">

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U237"/>
+  <dimension ref="A1:U238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -19928,6 +19928,110 @@
         </is>
       </c>
     </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>BUG-159</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>E2E TC-TCM-007/008 이 새 행 자동 선택과 겹쳐 간헐 실패한다</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>- CI E2E 의 TC-TCM-007(삭제), TC-TCM-008(복제)이 'Clicking the checkbox did not change its state' 로 간헐 실패한다</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>- 행을 추가한 뒤 선택 상태 확인이 매번 같은 결과를 낸다</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>- v1.6.9.0, v1.6.10.0 CI 에서 두 테스트가 첫 시도에 실패. v1.6.10.0 은 재시도까지 실패해 E2E job 이 빨갛게 끝났다</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>1. 시트를 만들고 행을 하나 추가한다
+2. 행이 보이자마자 체크박스를 check() 한다</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>- 간헐</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>- CI run 35809668885(a0d7be3), ba9b9c7 의 E2E 로그. 로컬 실패 화면에서 체크박스는 비었는데 상태 표시줄은 '1개 행 선택'</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>- 배치 로그(CI)</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>원인: - TestCaseGrid addRows 가 행을 만든 뒤 setTimeout 100ms 로 새 행을 자동 선택한다. 테스트가 체크 상태를 읽은 직후 자동 선택이 끼어들면 테스트의 클릭이 선택을 풀었다. 제품 코드 변경과 무관하게 v1.6.8.0 에도 있던 경합이다(로컬 A/B 결과 차이 없음)
+수정 내용: - 두 테스트가 체크박스를 누르지 않고, 자동 선택이 끝나 선택 1건과 체크 상태가 되는 것을 기다린다</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>- 테스트 주석에 원인을 남겼다. 깨끗한 DB 에서 두 테스트 10회 반복 실패 0회, CI=1 조건 E2E 59건 통과</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>- E2E 테스트만. 제품 동작은 바뀌지 않는다</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>System 1.6.10.0</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>System 1.6.10.1</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SYM-127</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U238"/>
+  <dimension ref="A1:U239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -20032,6 +20032,90 @@
         </is>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>ENH-059</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>우선순위 옛 값 '중간' 을 '보통' 으로 일괄 변경한다</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>- ymseo_test 프로젝트 TC 98건의 우선순위가 4단계 목록에 없는 옛 값 '중간' 이라 TC 관리와 테스트 수행 그리드에서 색이 입혀지지 않는다</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>- 98건 모두 '보통' 이다. 4단계 목록 밖의 값이 없어진다</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>- [ ] priority='중간' 인 TC 가 0건이다
+- [ ] 바뀐 98건 모두 변경 이력이 남는다
+- [ ] 변경 전 DB 백업이 있다</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>- v1.6.9.0 에서 우선순위를 4단계로 정하면서 '중간' 이 목록 밖 값이 됐다. 사용자 지시</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>- 일괄 변경 API(PUT /testcases/bulk)로 98건 변경. 중간 98-&gt;0, 보통(p23) 0-&gt;98, 변경 이력 6091-&gt;6189(+98, 모두 priority 중간-&gt;보통). 백업 backend/tc_manager.db.bak_20260923_194029_priority</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>- 다른 목록 밖 값(High, Medium, 중요, 핵심 등)과 빈 우선순위 정리</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>System 1.6.10.1</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>System 1.6.10.2(데이터 정리, 코드 변경 없음)</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>SYM-128</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U239"/>
+  <dimension ref="A1:U241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -20116,6 +20116,214 @@
         </is>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>BUG-160</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>우선순위 글자색이 접근성 대비 기준(4.5:1)에 못 미친다</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>- TC 관리와 테스트 수행 그리드의 우선순위 글자색 일부가 배경과 대비가 낮다</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>- 12px 굵은 글씨라 라이트/다크 테마 모두 카드 배경, 행 hover, 선택 행에서 4.5:1 이상</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>- 고정색이라 다크 '보통' #2563EB 가 카드 위 3.22:1, 다크 '매우 높음' 3.44:1, 라이트 '낮음' 3.3:1</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>1. 다크 테마로 TC 관리를 연다
+2. 우선순위 칸 글자색과 배경색의 대비를 잰다</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>- QA2 측정(getComputedStyle, 픽셀 대비), cssTokens 대비 계산</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>- QA2 리뷰</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>원인: - 우선순위 색이 테마와 무관한 고정 hex 였다
+수정 내용: - --priority-* CSS 변수로 옮기고 라이트 #B91C1C/#B54200/#1D4ED8/#166534, 다크 #F87C7C/#FB923C/#60A5FA/#4ADE80. 라이트 '높음' 은 빨강과 구분되는 가장 밝은 주황</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>- cssTokens.test.ts 가 테마별 그리드 블록의 hover/선택 값으로 합성한 배경까지 4.5:1 을 검사. priority.test.ts 가 CSS 변수 사용을 고정. 옛 색으로 되돌리면 실패 확인</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>- TC 관리, 테스트 수행 그리드의 우선순위 칸</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>FE 1.6.7.1</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>System 1.6.10.5 / FE 1.6.7.2 / BE 1.6.5.1</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>SYM-129</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>BUG-161</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>trivial</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>리포트에서 분류와 우선순위가 비어 있는 TC 의 표기가 곳마다 다르다</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>- 분류 없는 TC 가 요약 표는 'Uncategorized', 실패·차단 목록은 '-'. 우선순위도 요약 표 '(미지정)', 목록 '-', 영어 화면에서 목록만 번역 안 됨</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>- 화면은 '(미분류)'/'(미지정)', PDF/엑셀은 '(none)' 로 통일되고 영어 화면은 번역된다</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>- 같은 TC 가 표마다 다른 이름으로 보인다</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>1. 분류나 우선순위가 빈 TC 가 FAIL 인 런의 리포트를 연다
+2. 요약 표와 실패·차단 목록의 표기를 비교한다</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>- QA2 리뷰: 요약 표 'Uncategorized' 대 목록 '-', EN 화면 목록 우선순위 '높음'</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>- QA2 리뷰</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>원인: - 백엔드가 분류 요약에서만 이름('Uncategorized')을 정했고, 화면 목록은 따로 '-' 로 대체했다
+수정 내용: - JSON 은 빈 값을 null 로 정규화(요약, 목록 모두). 화면은 i18n 으로 '(미분류)'/'(미지정)' 과 우선순위 번역, PDF/엑셀은 '(none)'</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>- ReportView 테스트(분류/우선순위 표기, 영어 번역), 백엔드 테스트(JSON null, 엑셀·PDF '(none)'). 수정을 빼면 실패 확인</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>- 리포트 화면, PDF, 엑셀 Summary</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>BE 1.6.5.0</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>System 1.6.10.5 / FE 1.6.7.2 / BE 1.6.5.1</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>SYM-130</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U241"/>
+  <dimension ref="A1:U244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -20324,6 +20324,316 @@
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>BUG-162</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>대시보드 전체 집계에서 미수행이 이전 실행 결과를 덮는다</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>- 대시보드 전체 버전 보기에서 최근 수행에 미수행(NS)으로 담긴 TC 는 이전 수행의 PASS/FAIL 대신 미수행으로 집계된다</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>- TC 별로 마지막으로 실제 판정된 결과(PASS/FAIL/BLOCK/NA)를 집계한다. 한 번도 판정되지 않은 TC 만 미수행으로 센다</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>- stockradar 프로젝트(TC 689): 7월 실측 수행에 PASS 504 가 있는데 9월 21일 만든 수행 '테스트'(689건 전부 NS) 때문에 대시보드가 PASS 0, 미수행 689 로 표시된다</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>- 같은 TC 를 담은 수행이 둘 이상이고, 나중 수행에서 그 TC 가 아직 NS 다</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>1. 수행 A 를 만들고 TC 전부 PASS 로 기록한다
+2. 같은 TC 로 수행 B 를 만들고 결과를 기록하지 않는다
+3. 대시보드를 전체 버전, 수행 전체로 연다</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>- GET /api/projects/30/dashboard/summary -&gt; pass 0, not_started 689. test_results 의 run 27 은 PASS 504 / NS 185</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>- 기타 (v1.10.1.0 업데이트 뒤 데이터 점검)</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>원인: - backend/routes/dashboard.py 의 _latest_run_subquery 가 TC 별 max(test_run_id) 를 NS 행까지 포함해 골랐다. 새 수행에 NS 로 담긴 TC 는 그 수행이 최신이 되어 앞 수행의 판정이 집계에서 빠졌다
+수정 내용: - 서브쿼리에 result != NS 조건. 요약 · 우선순위 · 카테고리 · 히트맵이 함께 바뀐다. 나중의 기준은 수행 생성 순서(run id)로 유지하고 매뉴얼 · 화면 부제에 적었다</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_dashboard_latest_executed.py 9건(수정 전 7건 실패 확인). 기간 필터와 수행 순서 기준도 고정
+- test_dashboard_version.py 의 옛 기대값 (0,1,2) 를 (2,1,0) 으로</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>- 대시보드 전체 보기(요약 카드, 우선순위 · 카테고리 표, 히트맵). 수행을 고른 보기와 라운드 비교 · 추이 · 안정성은 그대로</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>BE 1.10.1.0</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>System 1.10.2.0 / FE 1.10.1.1 / BE 1.10.2.0</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>SYM-131</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>BUG-163</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>E2E 찾기/바꾸기 테스트 2건이 화면에 없는 버튼 이름을 찾아 실패한다</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>- CI E2E job 이 v1.7.0.0 이후 매번 빨간불이다. 실패는 두 건으로 같다</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>- `TC-TCM-018` 과 `모두 바꾸기가 거부돼도 값이 되돌아간다` 가 화면의 찾기/바꾸기 버튼을 눌러 통과한다</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>- `getByRole("button", { name: "변경하기" })` 가 요소를 못 찾아 `toBeVisible` 실패, 두 번째는 클릭 30초 타임아웃</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>- 빈 DB 로 기동한 백엔드와 admin/test1234 시드</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>1. `npx playwright test e2e/regression-full.spec.ts e2e/tc-management.spec.ts -g "TC-TCM-018|모두"`
+2. 실패 스크린샷에서 툴바 버튼 글자를 본다</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>- CI run (v1.10.1.0, e4887c6) E2E job: `TC-TCM-018` 2회, `tc-management.spec.ts:145` 2회 실패
+- 스크린샷의 버튼 글자는 `바꾸기`, 입력칸은 `바꿀 내용...`</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>- 기타 (SYM-131 릴리즈 게이트에서 로컬 E2E)</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>원인: - v1.7.0.0 의 용어 일괄 치환(바뀐다 -&gt; 변경된다)이 E2E 의 버튼 · 입력칸 이름(바꾸기, 바꿀 내용...)까지 바꿨다. 화면 문구(ko/testcase.json)는 그대로라 셀렉터가 없는 요소를 찾았다
+수정 내용: - regression-full.spec.ts, tc-management.spec.ts 의 셀렉터와 테스트 이름을 화면 문구로 복구. 주석의 동사 치환은 유지</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>- 없음. CI E2E job 이 이미 잡고 있었다(빨간불이 9/30 부터 방치). 릴리즈 전 CI 상태 확인으로 대응</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>- E2E 2건(TC-TCM-018, 모두 바꾸기 거부 복구). 제품 동작 변화 없음</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>FE 1.7.0.0</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>System 1.10.2.0 / FE 1.10.1.1 / BE 1.10.2.0</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>SYM-132</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>BUG-164</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>프로젝트 목록 합격률이 판정 없는 새 수행에서 0% 로 보인다</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>- 프로젝트 목록의 진행률과 합격률은 프로젝트의 가장 최근 수행 하나로 계산한다. 그 수행에 판정이 하나도 없으면 합격률이 0% 로 나온다</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>- 판정이 없으면 0% 가 아니라 값 없음(-)으로 보이거나, 기준이 화면에 적혀 있다</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>- 앞 수행에 PASS 가 있어도 미수행뿐인 새 수행을 만들면 목록 합격률이 0% 다. 같은 프로젝트의 대시보드 전체 집계(SYM-131 이후)는 앞 수행의 PASS 를 그대로 센다</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>- 판정이 있는 수행이 하나 이상 있는 프로젝트</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>1. 판정이 있는 수행을 둔 프로젝트에서 새 수행을 만든다(결과는 입력하지 않는다)
+2. 프로젝트 목록을 연다
+3. 그 프로젝트의 합격률을 본다</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>- `backend/routes/overview.py` 의 `latest_run_sq` 는 `max(TestRun.id)` 이고 `pass_rate` 는 `p / (p+f+b)`, 분모 0 이면 `0.0`</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>- QA (SYM-131 교차 검증의 QA2)</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>BE 1.10.1.0</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SYM-133</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -20618,14 +20618,36 @@
           <t>- QA (SYM-131 교차 검증의 QA2)</t>
         </is>
       </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>원인: - backend/routes/overview.py 가 판정(PASS/FAIL/BLOCK)이 없을 때 pass_rate 를 0.0 으로 냈다. 최근 수행 기준이라 새 회차를 만들면 앞 회차와 무관하게 0% 가 됐다
+수정 내용: - 판정이 없으면 pass_rate 를 None(프로젝트 행, 전체 요약, 프로젝트 0개). ProjectListPage 는 null 을 - 로, 보조 글자색으로 표시. 진행률 기준은 유지하고 매뉴얼에 기준 설명</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_overview_pass_rate.py 9건(수정 전 코드로 5건 실패 확인). 합계 대 평균, FAIL/BLOCK 만 0%, 전체 값 없음 포함
+- ProjectListPage.test.tsx 2건(행 · 요약 카드 -, 색, 프로젝트 0개)</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>- 프로젝트 목록 표와 요약 카드의 Pass Rate. /api/dashboard/overview 응답의 pass_rate 가 null 일 수 있다</t>
+        </is>
+      </c>
       <c r="R244" t="inlineStr">
         <is>
           <t>BE 1.10.1.0</t>
         </is>
       </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>System 1.10.3.0 / FE 1.10.2.0 / BE 1.10.3.0</t>
+        </is>
+      </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U244"/>
+  <dimension ref="A1:U245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -20656,6 +20656,94 @@
         </is>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>ENH-060</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>릴리즈 노트 제목이 형식 규격과 다르고 강제하는 검사가 없다</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>- Release_note.md 제목 74건이 '## v1.10.3.0 (2026-10-02) - [fix] 요약' 꼴이다. 전역 규격은 '## &lt;컴포넌트&gt; &lt;버전&gt; - [유형] &lt;요약&gt; (YYYY-MM-DD)'
+- 새 절이 규격을 지키는지 커밋 전에 보는 장치가 없다</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>- 과거 제목 73건을 'System &lt;버전&gt; - [유형] &lt;요약&gt; (날짜)' 로 통일. 날짜 근거가 없는 v0.1.0.0 1건은 그대로
+- 노트 머리에 작성 규칙 절, pre-commit 훅이 새 절을 검사</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>- [ ] 규격 밖 제목 1건(v0.1.0.0)만 남음
+- [ ] test_version_consistency 가 새 형식을 읽고, 절을 못 읽으면 실패
+- [ ] pre-commit 훅이 규격 밖 새 절을 막음</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>- 13개 레포 노트를 모아 보는 ym-wiki 릴리즈 페이지에서 제목 형식이 레포마다 달라 한 화면에서 읽기 어렵다</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>- 과거 제목 73건을 System &lt;버전&gt; - [유형] &lt;요약&gt; (날짜) 로 통일, 날짜 근거 없는 v0.1.0.0 은 그대로
+- 노트 머리 작성 규칙 절, rules/ 노트 안내 갱신, pre-commit 훅(release-lint) 설치
+- test_version_consistency 가 새 제목을 읽고 버전 절을 1개 이하로 읽으면 실패</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>- 하지 않은 것: 과거 절 본문 재작성, v0.1.0.0 날짜 추정</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>System 1.10.3.0</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>System 1.10.3.1</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>SYM-134</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U245"/>
+  <dimension ref="A1:U255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -20744,6 +20744,1040 @@
         </is>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SEC-021</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>동시에 가입하면 첫 관리자가 여러 명 생긴다</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>- 사용자가 없는 DB 에 가입 요청을 동시에 보내면 관리자 계정이 2명 이상 생긴다</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>- 첫 가입자 한 명만 관리자, 나머지는 일반 사용자</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>- 동시 가입 8건 중 관리자 2~5명</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>1. 빈 DB 로 서버를 띄운다
+2. 서로 다른 아이디로 가입 요청 8개를 동시에 보낸다
+3. role=admin 인 사용자 수를 센다</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>- 항상(동시 요청 수 4~8 에서)</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_first_admin_concurrent.py</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(설계 QA 2인) 후 PostgreSQL 에서 동시 요청 테스트로 재현</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>원인: - '사용자 수가 0 이면 관리자' 판정과 INSERT 사이에 잠금이 없다. SQLite 는 쓰기를 직렬화해 드러나지 않았다
+수정 내용: - 판정과 INSERT 를 트랜잭션 범위 advisory lock(FIRST_ADMIN) 안에서 한다. 해시 계산은 잠금 밖</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>- 동시 가입 테스트(잠금을 빼면 실패하는 것 확인)</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>- 새 설치의 첫 가입</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>BE 1.10.3.0 (PostgreSQL 전환 브랜치)</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>- System 2.0.0.0 / BE 2.0.0.0 (브랜치 feat/postgresql)</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>SYM-136</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>SEC-022</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>1회용 코드를 동시 요청으로 여러 번 쓸 수 있다</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>- 계정 찾기·비밀번호 재설정 1회용 코드를 동시에 보내면 여러 요청이 성공한다</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>- 한 요청만 성공, 나머지는 401</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>- 동시 8건 중 4건 성공</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>1. 관리자가 요청을 승인해 코드를 발급한다
+2. 같은 코드로 재설정 요청 8개를 동시에 보낸다</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>- 항상(동시 요청 수 4~8 에서)</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>- test_account_requests 의 동시 사용 테스트 결과 [200]*4</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(설계 QA 2인) 후 PostgreSQL 에서 동시 요청 테스트로 재현</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>원인: - 코드 행을 읽고 사용 처리하는 사이에 행 잠금이 없다
+수정 내용: - 코드 행을 SELECT ... FOR UPDATE 로 읽는다. 승인·거절도 같은 행 잠금</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>- 동시 사용 테스트가 [200]+[401]*7 을 단언</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>- 계정 찾기, 비밀번호 재설정</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>BE 1.10.3.0 (PostgreSQL 전환 브랜치)</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>- System 2.0.0.0 / BE 2.0.0.0 (브랜치 feat/postgresql)</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SYM-137</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>SEC-023</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>로그인 실패 제한을 동시 요청으로 넘을 수 있다</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>- 실패 횟수 확인과 기록 사이에 다른 요청이 끼어들어 제한보다 많이 시도할 수 있다</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>- 제한 횟수를 넘는 시도는 429</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>- 동시 요청에서 제한을 넘는 시도가 401 로 처리됨</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>1. 같은 아이디로 틀린 비밀번호 로그인을 제한 수보다 많이 동시에 보낸다</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>- 항상(동시 요청 수 4~8 에서)</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_rate_limit.py</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(설계 QA 2인) 후 PostgreSQL 에서 동시 요청 테스트로 재현</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>원인: - 실패 기록이 프로세스 메모리에 있어 서버리스 인스턴스끼리 공유되지 않고, 확인과 기록이 원자적이지 않다
+수정 내용: - rate_limit_events 테이블로 옮기고 키 단위 advisory lock 안에서 확인·기록</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>- 동시 실패 테스트</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>- 로그인, 계정 요청 제출</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>BE 1.10.3.0 (PostgreSQL 전환 브랜치)</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>- System 2.0.0.0 / BE 2.0.0.0 (브랜치 feat/postgresql)</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SYM-138</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>BUG-165</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>같은 수행 결과를 동시에 저장하면 한쪽이 조용히 덮어쓴다</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>- 두 사람이 같은 결과 행을 거의 동시에 저장하면 둘 다 성공하고 먼저 저장한 값이 사라진다</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>- 늦은 저장은 충돌(409)로 알리거나 순서대로 반영</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>- 동시 저장 전부 성공, 마지막 값만 남음</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>1. 같은 수행의 같은 결과 행에 저장 요청 여러 개를 동시에 보낸다</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>- 항상(동시 요청 수 4~8 에서)</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_result_conflict_concurrent.py</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(설계 QA 2인) 후 PostgreSQL 에서 동시 요청 테스트로 재현</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>원인: - 기존 행을 읽고 쓰는 사이에 잠금이 없다
+수정 내용: - 수행 단위 advisory lock(RUN_RESULTS) + 기존 행 FOR UPDATE. 결과 가져오기와 동기화도 같은 잠금</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>- 동시 저장 테스트, 잠금 범위 테스트(test_run_results_lock)</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>- 테스트 수행 결과 저장, 결과 가져오기</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>BE 1.10.3.0 (PostgreSQL 전환 브랜치)</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>- System 2.0.0.0 / BE 2.0.0.0 (브랜치 feat/postgresql)</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>SYM-139</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>BUG-166</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>동시에 TC 를 복제하면 일부가 409 로 실패한다</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>- 같은 프로젝트에서 TC 복제나 시트 이동이 동시에 들어오면 일부 요청이 409</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>- 모두 성공하고 TC 번호가 겹치지 않는다</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>- 동시 복제 8건 중 일부 409</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>1. TC 가 있는 프로젝트에서 복제 요청 8개를 동시에 보낸다</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>- 항상(동시 요청 수 4~8 에서)</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>- test_tc_clone_concurrent.py</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(설계 QA 2인) 후 PostgreSQL 에서 동시 요청 테스트로 재현</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>원인: - 번호 다시 매기기가 프로젝트 단위로 직렬화되지 않는다
+수정 내용: - 구조를 바꾸는 라우트에 프로젝트 쓰기 잠금. 대기 상한(LOCK_WAIT_TIMEOUT_MS)을 넘으면 409 와 안내 문구</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>- 동시 복제 테스트(배리어로 동시 출발), 잠금 범위 테스트</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>- TC 생성·복제·삭제·정렬, 시트 생성·이동·삭제</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>BE 1.10.3.0 (PostgreSQL 전환 브랜치)</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>- System 2.0.0.0 / BE 2.0.0.0 (브랜치 feat/postgresql)</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SYM-140</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>BUG-167</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>TC 번호 다시 매기기가 SQLite 전용 임시 테이블에 의존한다</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>- PostgreSQL 에서 번호 다시 매기기가 임시 테이블 문법 차이로 실패하거나 트랜잭션 풀러에서 세션 상태가 깨진다</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>- 두 DB 모두에서 같은 결과</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>- PostgreSQL 전환 시 동작하지 않는 경로</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>1. PostgreSQL 에서 시트의 TC 순서를 바꾼다</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>- 항상(동시 요청 수 4~8 에서)</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>- services/tc_numbering.py 의 옛 구현</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(설계 QA 2인) 후 PostgreSQL 에서 동시 요청 테스트로 재현</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>원인: - 고유 제약을 피하려고 임시 테이블에 번호를 계산해 두었다
+수정 내용: - UPDATE 두 번(음수로 비켜 두기 -&gt; 최종 번호)으로 바꿔 세션 상태 없이 처리</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>- 재번호 테스트, SQLite 전용 문법 검사 테스트(test_no_sqlite_in_tests)</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>- TC 정렬, 삭제 후 번호</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>BE 1.10.3.0 (PostgreSQL 전환 브랜치)</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>- System 2.0.0.0 / BE 2.0.0.0 (브랜치 feat/postgresql)</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SYM-141</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>BUG-168</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>고급 필터 조건 타입이 다르면 500 이 난다</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>- 숫자 칸(no) 조건에 문자열, in 조건에 목록이 아닌 값을 보내면 500</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>- 400 과 이유</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>- 500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>1. 필터 API 에 {field: no, operator: eq, value: "abc"} 를 보낸다</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>- 항상(동시 요청 수 4~8 에서)</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_filter_types.py</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(설계 QA 2인) 후 PostgreSQL 에서 동시 요청 테스트로 재현</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>원인: - SQLite 는 타입이 달라도 비교하지만 PostgreSQL 은 타입 오류를 낸다
+수정 내용: - 숫자 칸은 ASCII 숫자와 정수 범위만 받고, in 은 목록만 받는다. 어기면 400</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>- 타입별 경계 테스트</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>- 고급 필터, 저장된 필터</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>BE 1.10.3.0 (PostgreSQL 전환 브랜치)</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>- System 2.0.0.0 / BE 2.0.0.0 (브랜치 feat/postgresql)</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>SYM-142</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>BUG-169</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>백엔드 테스트가 개발 DB 를 건드리는지 판정이 SQLite 파일 기준이다</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>- PostgreSQL 로 바꾸면 테스트가 개발 DB 를 쓰는지 판정하지 못해 개발 데이터를 지울 수 있다</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>- 테스트는 세션마다 임시 DB 를 만들고 지운다. 개발 DB 에는 닿지 않는다</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>- 판정이 tc_manager.db 경로 비교라 PostgreSQL 에서는 무력</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>1. DATABASE_URL 을 PostgreSQL 개발 DB 로 두고 백엔드 테스트를 실행한다</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>- 항상(동시 요청 수 4~8 에서)</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>- 옛 conftest.py, dev_db_guard.py</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(설계 QA 2인) 후 PostgreSQL 에서 동시 요청 테스트로 재현</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>원인: - 테스트 격리가 SQLite 파일 복사에 기대고 있었다
+수정 내용: - testing_db 가 세션 임시 DB(로컬 호스트만, 쿼리 옵션 거부)를 만들고 지운다. .env 의 DATABASE_URL_DIRECT 재주입도 막음</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>- test_db_isolation, test_testing_db</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>- 백엔드 테스트 전체</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>BE 1.10.3.0 (PostgreSQL 전환 브랜치)</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>- System 2.0.0.0 / BE 2.0.0.0 (브랜치 feat/postgresql)</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>SYM-143</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>BUG-170</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>API 문서(Swagger) 화면이 빈 화면이다</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>- /docs (이제 /api/docs) 를 열면 아무것도 나오지 않는다</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>- API 목록이 보인다</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>- 빈 화면, 콘솔에 CSP 위반</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>1. 서버를 띄우고 브라우저로 /api/docs 를 연다</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>- 백엔드 CSP script-src 'self' 가 jsdelivr 스크립트와 인라인 초기화 스크립트를 막음</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(QA2)</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>원인: - 전역 보안 헤더가 문서 페이지에도 같은 CSP 를 준다
+수정 내용: - /api/docs 에만 CDN 과 인라인 스크립트를 허용하는 CSP. 다른 경로는 그대로</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>- 페이지가 부르는 출처와 CSP 를 대조하는 테스트(test_docs_csp), 브라우저 캡처 확인</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>- API 문서 화면, 관리자 매뉴얼의 Swagger 링크</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>BE 1.10.3.0 (PostgreSQL 전환 브랜치)</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>- System 2.0.0.0 / BE 2.0.0.0 (브랜치 feat/postgresql)</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SYM-144</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>BUG-171</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>파일을 올린 직후 미리보기가 409 로 실패할 수 있다</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>- 로컬 저장소 구성에서 TC 가져오기 파일을 고르면 가끔 '같은 업로드를 처리하는 중입니다' 로 실패한다</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>- 미리보기가 시트 목록을 보여주고 가져오기가 끝난다</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>- CI E2E 에서 '1개 가져옴' 이 끝내 나오지 않음(재시도 포함 2회 연속)</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>1. 로컬 저장소로 서버를 띄운다
+2. TC 가져오기로 CSV 를 고른다(PUT 직후 미리보기 요청)</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>- 간헐(로컬 8회 0건, CI 2회 연속)</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>- GitHub Actions run 37815839247, 37818104306 의 e2e/uploads.spec.ts:58 실패. 라우트 함수를 직접 불러 반환 시점에 행이 잠겨 있음을 확인(test_upload_hardening)</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>- CI(E2E)</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>원인: - 업로드 PUT 이 NOWAIT 행 잠금을 잡고 커밋·롤백 없이 반환한다. FastAPI 는 get_db 정리를 응답 뒤에 해서 잠금이 응답 뒤까지 남는다
+수정 내용: - PUT 이 반환 전에 롤백해 잠금을 푼다. 미리보기와 dry run 도 같은 이유로 반환 전에 롤백</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>- 반환 시점 잠금 해제 테스트 3건, CI 에 E2E 실패 스크린샷 보관 단계</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>- 로컬 저장소 구성의 TC 가져오기, 결과 가져오기 미리보기</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>BE 1.10.3.0 (PostgreSQL 전환 브랜치)</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>- System 2.0.0.0 / BE 2.0.0.0 (브랜치 feat/postgresql)</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>SYM-145</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -1850,7 +1850,15 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>SQLite 동시성 한계, 프로덕션 환경 대비</t>
+          <t>- SQLite 동시성 한계, 프로덕션 환경 대비
+- 결과: DB 를 PostgreSQL 로 단일화, Vercel + Supabase 배포 구성, SQLite 이관 스크립트(사전 점검·검증·첨부 해시 대조) 추가
+- SQLite 버전은 sqlite-legacy 브랜치(v1.10.3.1)로 동결</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>- 회사 계정 인증(Google 로그인, 가입 승인)은 후속 작업
+- Supabase 컷오버는 인증 작업 뒤</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1858,9 +1866,14 @@
           <t>0.3.0.0</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>System 2.0.0.0</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U255"/>
+  <dimension ref="A1:U256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -21791,6 +21791,115 @@
         </is>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>BUG-172</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>TC 가져오기 E2E 가 CI 에서 간헐로 실패한다</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>- main 푸시 CI 에서 E2E uploads.spec.ts 의 TC 가져오기 테스트가 재시도까지 실패했다
+- 같은 커밋이 브랜치 CI 와 다음 커밋 CI 에서는 통과했다</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>- 빈 프로젝트에서 CSV 를 고르면 '1개 가져옴' 알림이 뜨고 TC 1건이 생긴다</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>- 15초 동안 알림이 없고 화면은 빈 프로젝트 상태 그대로였다</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>1. main 에 c6e1393 을 푸시해 CI E2E 를 돌린다
+2. uploads.spec.ts 의 TC 가져오기 테스트 결과를 본다</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>- 간헐(CI 4회 중 1회, 로컬 격리 환경 25회 반복 0회)</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>- CI run 37865609420 의 e2e-test-results 아티팩트(빈 프로젝트 화면 캡처)
+- 실패 화면에 API 응답 기록이 없어 어느 요청이 실패했는지 남지 않았다</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>- CI(main 머지 직후 푸시 확인)</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>원인: - 확정하지 못했다
+- 후보: 화면 로딩 중에는 툴바의 파일 입력이 있다가 빈 프로젝트 화면의 입력으로 바뀌는데, 테스트가 로딩 완료를 기다리지 않고 파일을 골랐다
+수정 내용: - 빈 프로젝트 화면이 뜬 뒤에 파일을 고른다
+- 실패하면 4xx/5xx API 응답, 실패한 요청, 콘솔 오류를 api-and-console-problems.txt 로 남긴다(CI 아티팩트에 포함)</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>- 실패 기록 파일. 재발하면 기록으로 원인을 확정한다
+- 기록 동작은 /api/uploads 에 500 을 주입해 남는 것을 확인했다</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>- CI E2E 만. 제품 동작 변경 없음</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>System 2.0.0.0</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>- System 2.0.0.1</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>SYM-146</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U256"/>
+  <dimension ref="A1:U267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -21900,6 +21900,1135 @@
         </is>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>SEC-024</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>회사 계정만 쓰도록 로그인과 가입을 환경변수로 제한하는 기능이 없다</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>- 누구나 아이디로 가입해 바로 쓴다
+- 로그인은 아이디와 비밀번호뿐이고 회사 계정인지 확인할 방법이 없다</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>- Google 로그인(서버 측 인가 코드 흐름)과 이메일 가입
+- AUTH_COMPANY_DOMAINS, AUTH_ALLOW_PERSONAL, AUTH_APPROVAL 로 '누구나', '회사 계정만', '회사 계정은 바로, 나머지는 승인 후' 를 고른다
+- 관리자 승인, 사용 중지, 이메일 해제, 본인의 Google 계정 연결</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>- [x] 환경변수 세 개로 정책을 고른다(.env.example 에 선택지, 기본값만 켬)
+- [x] Google 로그인과 계정 연결, 해제
+- [x] 승인 대기, 사용 중지(JWT, API 키 즉시 무효), 마지막 관리자 보호
+- [x] 첫 관리자 보호(운영은 BOOTSTRAP_TOKEN)
+- [x] QA 2인 통과, E2E 와 CI 반영</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>- 회사 팀에 인터넷으로 배포하기 전에 들어올 수 있는 사람을 막아야 한다(Supabase 컷오버의 선행 조건)</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>- 설계: docs/superpowers/specs/2026-10-09-org-account-auth-design.md
+- 마이그레이션 0007(email, email_verified, google_sub, status)</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>- 메일 발송과 이메일 인증, 다른 IdP, Workspace 그룹 기반 역할, 이메일 자동 연결, 초대 코드
+- Supabase 컷오버(하위 프로젝트 3)</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>BE 2.0.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>- System 2.1.0.0 / BE 2.1.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>SYM-147</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>SEC-025</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>계정 복구와 Google 연결이 겹치면 공격자가 연결한 Google 계정이 남는다</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>- 관리자 초기화나 비밀번호 찾기가 사용자를 읽은 뒤 다른 요청이 Google 연결을 커밋하면, 초기화가 옛 값을 보고 연결 해제를 빠뜨린다</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>- 계정을 되찾으면 Google 연결도 끊긴다</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>- 연결이 남아 탈취한 쪽이 Google 로 다시 들어온다</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>1. 초기화가 사용자를 읽는다
+2. 다른 세션이 google_sub 를 커밋한다
+3. 초기화가 끝난 뒤 google_sub 를 본다</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>- 항상(재현 테스트 기준)</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_auth_qa_fixes.py::test_관리자_초기화는_잠금_전에_붙은_Google_연결도_끊는다</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>- QA 2인(Codex, 자체 리뷰) 코드 검토, 릴리즈 전</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>원인: - 초기화와 복구가 계정 잠금 없이 읽었고, 잠금 뒤 조회도 이미 읽은 ORM 객체의 옛 값을 돌려줬다(populate_existing 없음)
+수정 내용: - 초기화·복구·연결을 계정 잠금 안에서 최신 값으로 다시 읽는다. 연결은 잠금 안에서 세션 버전과 상태를 다시 확인한다</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>- 잠금 직전에 다른 세션이 값을 바꾸는 재현 테스트 3건</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>- 관리자 초기화, 비밀번호 찾기, Google 연결(릴리즈 전 발견)</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>BE 2.0.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>- System 2.1.0.0 / BE 2.1.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>SYM-148</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>BUG-173</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>사용 중지와 비밀번호 변경이 겹치면 행 잠금 교착이 날 수 있다</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>- 사용 중지는 사용자 행 다음 API 키 행을, 비밀번호 변경·복구는 API 키 행 다음 사용자 행을 잠근다</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>- 같은 사용자에 대한 두 요청이 순서대로 처리된다</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>- PostgreSQL 이 한쪽을 교착으로 중단해 500 이 날 수 있다</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>1. API 키가 있는 사용자에 대해 사용 중지와 비밀번호 변경을 동시에 보낸다</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>- 항상(재현 테스트 기준)</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>- 코드 정적 분석(Codex), tests_unit/test_auth_qa_fixes.py::test_비밀번호_변경은_계정_잠금을_잡는다</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>- QA 2인(Codex, 자체 리뷰) 코드 검토, 릴리즈 전</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>원인: - 비밀번호 변경·복구가 계정 잠금을 거치지 않았다
+수정 내용: - 계정을 바꾸는 모든 경로를 계정 잠금 하나로 줄 세운다(횟수 제한 키 -&gt; 계정 잠금 -&gt; 사용자 행 -&gt; API 키 행)</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>- 계정 잠금을 쥔 상태에서 비밀번호 변경이 409 로 기다림을 확인하는 테스트</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>- 비밀번호 변경, 관리자 초기화, 비밀번호 찾기, 사용 중지(릴리즈 전 발견)</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>BE 2.0.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>- System 2.1.0.0 / BE 2.1.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>SYM-149</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>BUG-174</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>첫 관리자 아이디에 골뱅이와 대문자가 섞이면 로그인할 수 없다</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>- 빈 DB 에서 아이디를 Admin@Corp.com 으로 만들면 그 관리자가 로그인하지 못한다</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>- 만든 아이디로 로그인된다</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>- 항상 401, 유일한 관리자가 잠긴다</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>1. 빈 DB 에서 아이디 Admin@Corp.com 으로 첫 관리자를 만든다
+2. 같은 값으로 로그인한다</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>- 항상(재현 테스트 기준)</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_auth_qa_fixes.py::test_첫_관리자_아이디에_골뱅이와_대문자가_있어도_로그인된다</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>- QA 2인(Codex, 자체 리뷰) 코드 검토, 릴리즈 전</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>원인: - 로그인은 '@' 가 든 입력을 소문자로 찾는데 첫 관리자 아이디는 원문으로 저장했다
+수정 내용: - 첫 관리자 아이디도 로그인과 같은 규칙으로 정규화해 저장</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>- 재현 테스트</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>- 첫 설치(릴리즈 전 발견)</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>BE 2.0.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>- System 2.1.0.0 / BE 2.1.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>SYM-150</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>SEC-026</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>가입 횟수 제한이 bcrypt 계산 뒤에 걸려 비용을 막지 못한다</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>- 한도를 넘긴 가입 요청도 bcrypt 를 다 계산한 뒤 429 를 받는다</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>- 한도를 넘긴 요청은 bcrypt 전에 거절된다</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>- 요청마다 약 250ms CPU 를 쓴다</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>1. REGISTER_MAX_PER_HOUR=1 로 두고 같은 IP 에서 두 번 가입한다
+2. 두 번째 요청에서 hash_password 호출 여부를 본다</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>- 항상(재현 테스트 기준)</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_auth_qa_fixes.py::test_한도를_넘긴_가입은_bcrypt_를_돌리지_않는다</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>- QA 2인(Codex, 자체 리뷰) 코드 검토, 릴리즈 전</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>원인: - register 가 해시를 먼저 계산하고 횟수 제한을 나중에 봤다
+수정 내용: - 횟수 제한 -&gt; bcrypt -&gt; 계정 잠금 순서로 바꿈</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>- 재현 테스트</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>- 이메일 가입(릴리즈 전 발견)</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>BE 2.0.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>- System 2.1.0.0 / BE 2.1.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>SYM-151</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>SEC-027</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Google 확인값이나 설치 토큰에 한글이 오면 500 이 난다</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>- state 나 bootstrap_token 에 ASCII 가 아닌 문자가 오면 서버 오류</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>- 일반 거절(google_state, 403)</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>- 500(TypeError: comparing strings with non-ASCII characters is not supported)</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>1. /api/auth/google/callback?state=한글 을 연다</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>- 항상(재현 테스트 기준)</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_auth_qa_fixes.py 의 두 테스트</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>- QA 2인(Codex, 자체 리뷰) 코드 검토, 릴리즈 전</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>원인: - hmac.compare_digest 에 str 을 넘겼다
+수정 내용: - 양쪽을 UTF-8 bytes 로 바꿔 비교</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>- 재현 테스트 2건</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>- Google 콜백, 첫 관리자 만들기(릴리즈 전 발견)</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>BE 2.0.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>- System 2.1.0.0 / BE 2.1.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SYM-152</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>BUG-175</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Google 이메일이 100자를 넘으면 계정 생성에서 500 이 난다</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>- 확인된 Google 이메일이 100자를 넘으면 저장 중 오류</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>- 검증 실패 안내(google_verify)</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>- 500(StringDataRightTruncation)</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>1. 100자를 넘는 이메일의 Google 신원으로 콜백한다</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>- 항상(재현 테스트 기준)</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_auth_qa_fixes.py::test_긴_Google_이메일은_500_이_아니다</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>- QA 2인(Codex, 자체 리뷰) 코드 검토, 릴리즈 전</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>원인: - users.email 이 100자인데 Google 이메일 길이를 확인하지 않았다
+수정 내용: - 100자를 넘으면 google_verify 로 돌려보냄</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>- 재현 테스트</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>- Google 로그인(릴리즈 전 발견)</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>BE 2.0.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>- System 2.1.0.0 / BE 2.1.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>SYM-153</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>BUG-176</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>첫 관리자 동시 가입 테스트가 같은 IP 라서 계정 잠금 결함을 가린다</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>- 계정 잠금 줄을 지워도 동시 가입 테스트가 통과한다</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>- 계정 잠금이 없으면 테스트가 실패한다</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>- 같은 IP 의 가입 횟수 제한 잠금이 요청을 줄 세워 테스트가 결함을 못 잡는다</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>1. register 의 lock_accounts 를 지운다
+2. 동시 가입 테스트를 돌린다</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>- 항상(재현 테스트 기준)</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>- QA2 지적, IP 를 가른 테스트는 잠금 제거 시 실패함을 확인</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>- QA 2인(Codex, 자체 리뷰) 코드 검토, 릴리즈 전</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>원인: - 테스트 요청이 모두 127.0.0.1 이었다
+수정 내용: - 요청마다 다른 IP 를 준다</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>- 잠금을 빼서 테스트가 실패하는지 확인함</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>- 테스트만</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>BE 2.0.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>- System 2.1.0.0 / BE 2.1.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>SYM-154</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>SEC-028</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>비밀번호 변경과 Google 연결 해제가 잠금을 기다리는 사이 중지된 계정에서도 진행된다</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>- 인증을 통과한 뒤 계정 잠금을 기다리는 사이 관리자가 사용 중지해도 비밀번호 변경과 연결 해제가 끝까지 진행된다</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>- 잠금 안에서 세션을 다시 확인해 거절한다</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>- 중지된 계정의 비밀번호가 바뀌거나 연결이 풀린다</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>1. 비밀번호 변경 요청이 인증을 통과한다
+2. 다른 세션이 그 계정을 사용 중지한다
+3. 변경 요청이 잠금을 얻는다</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>- 항상(재현 테스트 기준)</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_auth_qa2_fixes.py 의 두 테스트</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>- QA 2인(Codex, 자체 리뷰) 코드 검토, 릴리즈 전</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>원인: - 잠금 뒤 재확인이 비밀번호 해시 비교뿐이었다
+수정 내용: - 잠금 안에서 상태와 token_version 을 다시 확인하고 다르면 401</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>- 잠금 직전에 다른 세션이 계정을 중지하는 재현 테스트</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>- 비밀번호 변경, Google 연결 해제(릴리즈 전 발견)</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>BE 2.0.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>- System 2.1.0.0 / BE 2.1.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>SYM-155</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>BUG-177</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>비밀번호 찾기 완료 API 가 전역 계정 잠금 안에서 bcrypt 를 돌려 다른 계정 작업을 막는다</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>- 로그인 없이 부르는 코드 확인 API 가 계정 잠금을 잡은 채 bcrypt 를 돌린다</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>- 확인과 bcrypt 는 잠금 밖에서 하고 반영할 때만 잠근다</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>- 아이디를 바꿔 가며 보내는 요청이 가입, Google 로그인, 관리자 조작을 줄 세워 409 가 난다</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>1. 다른 세션이 계정 잠금을 쥔다
+2. 없는 아이디로 코드 확인을 보낸다</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>- 항상(재현 테스트 기준)</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_auth_qa2_fixes.py::test_비밀번호_찾기_실패는_계정_잠금을_기다리지_않는다</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>- QA 2인(Codex, 자체 리뷰) 코드 검토, 릴리즈 전</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>원인: - 직전 수정(계정 잠금 일원화)에서 잠금을 조회 앞에 넣었다
+수정 내용: - 확인과 bcrypt 를 잠금 밖으로 옮기고, 반영 직전에 잠금 안에서 사용자 상태와 요청 행을 다시 확인</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>- 계정 잠금을 쥔 상태에서 실패 요청이 바로 401 인지 보는 테스트, 동시 이중 사용 테스트 유지</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>- 비밀번호 찾기(릴리즈 전 발견)</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>BE 2.0.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>- System 2.1.0.0 / BE 2.1.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>SYM-156</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>BUG-178</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>영어 화면에서 새 인증 오류 문구가 한국어로 나온다</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>- 관리자 409(마지막 관리자 등), 비밀번호 없는 계정 해제, 검증 오류가 영어 화면에 한국어나 영어 원문으로 나온다</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>- 화면 언어로 번역된 문구</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>- 백엔드 원문 노출</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>1. 영어 화면에서 마지막 관리자를 사용 중지한다</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>- 항상(재현 테스트 기준)</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>- frontend/src/test/errorMessage-auth.test.ts</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>- QA 2인(Codex, 자체 리뷰) 코드 검토, 릴리즈 전</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>원인: - 번역 표(ERROR_MAP)에 새 문구가 없고, 검증 오류 배열의 msg 를 그대로 썼다
+수정 내용: - 번역 표에 15개 문구 추가, 검증 오류 배열은 화면 언어의 대체 문구, 콜백 코드는 허용 목록으로 변환</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>- 문구표 전체의 영어 번역 테스트</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>- 관리자 화면, 가입, 로그인(릴리즈 전 발견)</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>BE 2.0.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>- System 2.1.0.0 / BE 2.1.0.0 (브랜치 feat/auth)</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>SYM-157</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U267"/>
+  <dimension ref="A1:U271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23029,6 +23029,375 @@
         </is>
       </c>
     </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>BUG-179</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>배포 환경에서 서명 업로드 주소 발급이 400 으로 막혀 파일 업로드가 전부 실패한다</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>- Vercel + Supabase 시험 배포에서 첨부 업로드, TC 가져오기, 결과 가져오기가 모두 실패한다
+- 업로드 시작 API(POST /api/uploads)가 503 '파일 저장소에 연결할 수 없습니다' 를 낸다</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>- 서명 업로드 주소를 받아 브라우저가 Supabase Storage 에 직접 올린다</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>- Supabase Storage 가 서명 업로드 주소 발급 요청을 400 으로 거절한다</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>- STORAGE_BACKEND=supabase 로 배포된 서버</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>1. 로그인한다
+2. POST /api/uploads 에 purpose=attachment 로 업로드를 요청한다</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>- Vercel 함수 로그: Storage unavailable on POST /api/uploads: storage POST failed: HTTP 400
+- Storage 응답 본문: Body cannot be empty when content-type is set to 'application/json'</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>- 기타(운영 시험 배포 점검)</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>원인: - SupabaseStorage._json 이 payload 가 없으면 본문 없이 content-type: application/json 만 보냈다. 서명 업로드 주소 발급(upload_target)이 payload 없이 불렀다
+- 테스트의 가짜 Supabase 서버가 빈 JSON 본문을 받아 줘서 단위 테스트를 통과했다
+수정 내용: - _json 이 payload 가 없으면 {} 를 보낸다</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>- 가짜 Supabase 서버(POST, DELETE, 목록)가 실제처럼 JSON + 빈 본문을 400 으로 거절한다. 옛 코드에서 직접 업로드 주소 테스트가 실패함을 확인
+- 시험 배포에서 발급, 직접 업로드, 첨부 등록, 다운로드, 삭제 왕복 실측</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>- 배포 환경(STORAGE_BACKEND=supabase)의 모든 직접 업로드. 로컬 저장소는 영향 없음. 운영 컷오버 전에 발견</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>BE 2.0.0.0</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>- System 2.1.1.0 / BE 2.1.1.0</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>SYM-158</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>BUG-180</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>관리 화면의 전체 배정 조회 API 가 422 를 내 배정 칸이 미배정으로 보인다</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>- GET /api/projects/all-assignments 가 422(project_id 정수 변환 실패)를 낸다
+- 관리 화면이 실패를 삼켜 프로젝트에 배정된 일반 사용자도 '미배정' 으로 보인다</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>- 사용자별 프로젝트 배정 목록을 돌려준다</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>- 422. 화면 콘솔에 AxiosError 422</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>1. 관리자로 로그인한다
+2. 관리 화면을 열거나 GET /api/projects/all-assignments 를 부른다</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>- 시험 배포와 로컬 서버 모두 422, detail: int_parsing loc=[path, project_id] input=all-assignments</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>- 기타(운영 시험 배포 화면 점검의 콘솔 오류)</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>원인: - main.py 가 project_routes.router(GET /api/projects/{project_id})를 member_routes.assign_all_router 보다 먼저 등록해 고정 경로가 경로 변수에 먹혔다
+수정 내용: - assign_all_router 를 project_routes.router 앞에 등록</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>- 앞 라우트의 실제 정규식이 뒤 라우트 주소를 잡는지와 중복 등록을 전수 점검하는 테스트
+- 배정 조회 응답과 권한(비로그인 401, 일반 사용자 403) 테스트. 옛 순서에서 실패함을 확인</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>- 관리 화면 '프로젝트 배정' 칸(v0.7.0 부터). 현재 데이터는 배정이 모두 관리자 것이라 화면 차이는 없었다</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>v0.7.0</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>- System 2.1.1.0 / BE 2.1.1.0</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SYM-159</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>ENH-061</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>관리 화면이 프로젝트와 배정 조회 실패를 삼켜 빈 값처럼 보인다</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>- AdminPage 의 loadProjects, loadAllAssignments, openAssignModal 이 실패하면 console.error 만 남긴다
+- 배정 조회가 실패해도 '미배정', 프로젝트 조회가 실패해도 빈 드롭다운으로 보인다</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>- 조회가 실패하면 알림을 띄우고 배정 칸에 '조회 실패' 를 표시한다
+- 배정 모달은 프로젝트 수만큼의 순차 호출 대신 전체 배정 조회 결과를 쓴다</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>- [ ] 세 조회의 실패가 화면에 보인다
+- [ ] 실패 경로 목 테스트
+- [ ] 화면 캡처 확인</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>- 전체 배정 조회 422 가 이 패턴 때문에 7개월 동안 드러나지 않았다</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>- 다른 화면의 오류 처리 일괄 정비</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>BE 2.1.1.0</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SYM-160</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>ENH-062</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>로컬 전용 업로드 PUT 라우트가 배포 모드 판정에 서명 주소 발급 호출을 쓴다</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>- PUT /api/uploads/{id}/content 가 storage.upload_target() 결과로 배포 모드인지 판정한다
+- Supabase 모드에서는 이 판정만으로 서명 업로드 주소를 하나 발급한다. 행 잠금(FOR UPDATE NOWAIT)을 쥔 채 최대 30초 네트워크 호출</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>- 저장소 종류나 속성으로 판정해 네트워크 호출 없이 400 을 낸다</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>- [ ] Supabase 모드에서 이 라우트가 저장소를 호출하지 않고 400
+- [ ] 테스트</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>- 배포 환경에서 잘못 불린 요청이 잠금을 쥔 채 외부 호출을 기다린다</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>- 업로드 흐름 재설계</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>BE 2.1.1.0</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SYM-161</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U271"/>
+  <dimension ref="A1:U275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23398,6 +23398,339 @@
         </is>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>ENH-063</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>실수로 생긴 빈 계정을 관리자가 정리할 수 없고 Google 연결 뒤에도 빈 계정이 남는다</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>- Google 로그인을 잘못 눌러 생긴 빈 계정을 지울 방법이 없다. 관리자는 승인 대기 계정만 거절(삭제)할 수 있다
+- 그 빈 계정이 Google 계정을 쥐고 있으면 본 계정에 연결할 수 없고(already_linked), 초기화·중지로 우회해 연결해도 빈 계정이 목록에 남고 이메일을 옮겨 오지 못한다</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>- 관리자 '삭제': 작업 기록이 하나도 없는 계정만 지운다. 본인, 승인 대기, 마지막 관리자는 제외
+- Google 연결 때 같은 Google 계정을 쥔 빈 Google 전용 계정(비밀번호 없음, 기록 없음)은 정리하고 연결한다(account=merged). 현재 계정에 이메일이 없으면 이메일도 옮긴다</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>- [x] DELETE /api/auth/users/{id}, 기록(모든 사용자 외래키, API 키 포함)이 있으면 409
+- [x] 연결 시 빈 Google 전용 계정 정리, 기록·비밀번호·마지막 관리자면 거절
+- [x] 관리 화면 삭제 버튼, 매뉴얼, 체크리스트
+- [x] QA 2인 통과</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>- 시험 배포에서 사용자가 admin 연결을 잊고 Google 로그인해 빈 계정이 생겼고, 화면에서 풀 수 없었다</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>- 삭제와 정리는 계정 잠금과 사용자 행 FOR UPDATE 안에서 기록을 세고 지운다. 배정 저장과 겹치면 삭제가 기다렸다가 409
+- QA 지적으로 비밀번호 초기화 뒤 표 갱신, 테스트 목(렌더마다 새 사용자 객체)이 목록 갱신 누락을 가리던 문제를 함께 고침</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>- 기록이 있는 계정끼리의 병합(기록 이전)
+- 이메일이 같다는 이유의 자동 병합(탈취 방지 원칙 유지)</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>System 2.1.1.0</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>- System 2.2.0.0 / BE 2.2.0.0 / FE 1.13.0.0 / DB 1.2.0.0</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>SYM-162</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>ENH-064</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>사용자 관리 표에서 연결된 Google 계정을 확인할 수 없다</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>- 로그인 방식 칸은 '비밀번호 + Google' 만 보여 준다
+- 이메일 칸은 다른 계정이 그 주소를 쥐고 있으면 비어 있어, 어느 Google 계정이 연결됐는지 알 수 없다</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>- users.google_email(0008)에 연결된 Google 주소를 남긴다(가입, 로그인, 연결 때 갱신, 해제·초기화·복구 때 삭제)
+- 표의 로그인 방식 칸과 계정 연결 창에 'Google: 주소' 를 보여 준다. 기능 전에 연결된 계정은 '주소 미기록' 이고 다음 Google 로그인 때 채워진다</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>- [x] 마이그레이션 0008 과 왕복 테스트
+- [x] 표와 연결 창 표시, 화면 캡처 확인
+- [x] QA 2인 통과</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>- 사용자가 admin 에 Google 을 연결했는데 표에서 확인할 수 없다고 지적했다</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>- 시험 배포의 admin 은 다음 Google 로그인 때 주소가 채워진다</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>- 이메일 칸 자체의 의미 변경</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>System 2.1.1.0</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>- System 2.2.0.0 / BE 2.2.0.0 / FE 1.13.0.0 / DB 1.2.0.0</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>SYM-163</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>BUG-181</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>프로젝트 배정과 계정 삭제가 겹치면 배정 요청이 500 을 낸다</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>- 계정 삭제가 먼저 커밋되면 배정 요청은 존재 확인을 이미 통과해 외래키 오류(IntegrityError)를 처리하지 못한다</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>- 404(사용자를 찾을 수 없음)</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>- 500. 데이터는 손상되지 않는다</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>1. 배정 요청이 사용자 존재 확인을 통과한다
+2. 그 사이 관리자가 그 계정을 삭제하고 커밋한다
+3. 배정 요청이 커밋한다</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>- 미확인(경합)</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>- QA2 코드 검토: routes/members.py 의 멤버 추가와 일괄 배정이 commit 을 IntegrityError 로 감싸지 않는다. 승인 대기 거절(reject_user)도 같은 모양</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>- QA</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>BE 2.2.0.0</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>SYM-164</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>ENH-065</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>프론트 테스트의 로그인 사용자 목이 렌더마다 새 객체를 만들어 목록 갱신 누락을 가린다</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>- accessibility, AccountLinkModal, Header, ProjectListPage, ProjectPage 테스트의 useAuth 목이 호출마다 새 user 객체를 돌려준다
+- [currentUser] 에 걸린 effect 가 렌더마다 다시 돌아, 실제 앱에서는 일어나지 않는 재조회가 테스트에서 일어난다</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>- 목이 실제 AuthContext 처럼 같은 객체를 돌려준다(AdminPage 테스트는 이번에 고침)</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>- [ ] 다섯 파일의 목을 고정 객체로 바꾼다
+- [ ] 바꾼 뒤 드러나는 실패를 결함으로 분류해 고친다</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>- AdminPage 에서 이 목이 '비밀번호 초기화 뒤 목록 갱신 누락' 을 가린 것이 확인됐다</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>- 테스트 도우미 공통화 이상의 구조 변경</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>FE 1.13.0.0</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>SYM-165</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U275"/>
+  <dimension ref="A1:U278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23731,6 +23731,267 @@
         </is>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>BUG-182</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>사용자·운영 매뉴얼이 Google 로그인과 가입 승인을 다루지 않고 로그인 유지 시간을 틀리게 안내한다</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>- 사용자 매뉴얼(앱 안, docs md)에 Google 로그인, 이메일 가입과 승인 대기, 계정 연결 절이 없다. md 에는 계정 복구 절도 없다
+- 운영 매뉴얼의 환경변수 표, 보안 표, API 표에 인증 기능(2.1.0.0, 2.2.0.0)이 없다
+- 매뉴얼 그림(로그인, 가입, 사용자 관리, 계정 요청)이 인증 기능 전 화면이다</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>- 매뉴얼이 현재 화면과 코드 동작(세션 시간, 승인 정책, 연결 조건)을 그대로 안내한다</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>- 앱 사용자 매뉴얼: 로그인 유지가 '서버가 재시작되기 전까지'
+- 운영 매뉴얼(앱, md): TOKEN_EXPIRE_HOURS 기본 2시간. 코드는 72시간, 로그인 유지 30일(backend/auth.py)
+- 사용자 md: '최초 가입 사용자는 Admin', 가입 항목이 아이디(현재는 이메일)</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>1. 앱에서 도움말과 운영 매뉴얼을 연다
+2. 로그인 절과 환경변수 표, 보안 설정 표를 backend/auth.py, services/auth_config.py 와 비교한다</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>- backend/auth.py:33 TOKEN_EXPIRE_HOURS 기본 72, :35 REMEMBER_ME_DAYS 기본 30
+- adminManual.json security.authTokenSetting '기본 2시간', manual.json login.info1 '서버가 재시작되기 전까지'</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>- 사용자 요청(매뉴얼 갱신) 중 코드 대조</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>원인: - 인증 기능(2.1.0.0)과 계정 정리(2.2.0.0) 릴리즈 때 운영 매뉴얼 5-4-1 절만 갱신. 사용자 매뉴얼, 환경변수·보안·API 표, 그림은 갱신 대상에서 빠짐
+- 세션 시간 서술은 그 이전부터 코드와 불일치
+수정 내용: - 사용자 매뉴얼: Google 로그인, 이메일 가입, 계정 연결 절 추가, 세션 시간 수정, md 에 계정 복구 절 추가
+- 운영 매뉴얼: 인증 환경변수 10개, Google 로그인 켜기 절, 보안·API·트러블슈팅 행 추가, 세션 시간 수정. API 표 제목의 고정 개수(84개, 실제 115) 제거
+- 그림 01, 02, 22, 25, 39, 40 재촬영, 44(계정 연결 창) 추가. 예약 도메인 주소만 사용
+- 매뉴얼 꼬리말은 화면 푸터 버전(common:version)을 쓴다</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>- 꼬리말 버전을 고정 문자열에서 common:version 으로 변경(릴리즈마다 따로 고칠 필요 없음)
+- 그림 재촬영 스펙(e2e/capture-auth-manual.spec.ts)과 격리 설정(playwright/vite e2e-local) 커밋. 그림 재촬영을 재현 가능
+- 수치 서술과 코드의 자동 대조는 미적용(문장 안 수치를 기계로 뽑기 어려움)</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>- 앱 안 사용자 매뉴얼, 운영 매뉴얼, docs/manual_user_confluence.md, docs/manual_admin_confluence.md, 매뉴얼 그림 7장</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>System 2.2.0.0 / FE 1.13.0.0</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>- System 2.2.0.1 / FE 1.13.0.1</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>SYM-166</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>ENH-066</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>trivial</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>사내 업무 가이드 초안(docs/confluence_draft.md)이 인증 기능 전 내용으로 남아 있다</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>- 2026-03 초안이다. '최초 가입 사용자 Admin', TOKEN_EXPIRE_HOURS 기본 2 등 지금 코드와 다른 서술이 있다(68, 379행 부근)</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>- 초안을 현재 매뉴얼과 맞추거나, 쓰지 않는 문서면 정리한다</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>- [ ] 문서를 계속 쓸지 결정
+- [ ] 쓰면 인증·세션 서술을 현재 매뉴얼과 맞춘다</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>- 매뉴얼 갱신(System 2.2.0.1) QA 에서 같은 유형의 낡은 수치가 이 파일에 남은 것을 확인. 공개 레포라 외부에서 읽힘</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>- 매뉴얼 본문 재구성</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>System 2.2.0.1 / FE 1.13.0.1</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>SYM-167</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>ENH-067</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>trivial</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>운영 매뉴얼의 비밀번호 초기화 그림(25)이 사용자 관리 그림(22)과 같은 화면이다</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>- 25_admin_page_with_reset.png 가 22_admin_page.png 와 같은 화면이다(main 에서도 바이트 동일). 임시 비밀번호가 표시된 화면을 보여 주지 않는다</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>- 25 번 그림이 초기화 뒤 임시 비밀번호가 표시된 화면을 보여 준다</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>- [ ] capture-auth-manual.spec.ts 에 초기화 확인 뒤 화면 캡처 추가
+- [ ] 25 번 재촬영</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>- 매뉴얼 갱신 QA 에서 확인. 운영 매뉴얼 5-3 절의 설명과 그림이 불일치</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>- 다른 그림 재촬영</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>System 2.2.0.1 / FE 1.13.0.1</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>SYM-168</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U278"/>
+  <dimension ref="A1:U279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23992,6 +23992,91 @@
         </is>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>BUG-183</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>사용 중지 E2E 가 reload 도중 401 리다이렉트와 겹쳐 간헐 실패한다</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>- e2e/account-approval.spec.ts 의 '사용 중지하면 그 사용자의 다음 화면 이동이 로그인 화면으로 간다' 가 CI 에서 간헐 실패한다</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>- 사용 중지 뒤 화면을 다시 읽으면 /login 으로 가고 테스트가 통과한다</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>- page.reload: net::ERR_ABORTED; maybe frame was detached? (72행). 재시도까지 실패, 잡 재실행에서는 통과</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>1. 이메일 가입 계정을 승인하고 그 계정으로 로그인한다
+2. 관리자 API 로 그 계정을 사용 중지한다
+3. page.reload() 를 부른다</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>- 간헐</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>- CI run 37944275264 첫 시도(커밋 377c05f): 본 시도와 retry #1 모두 ERR_ABORTED, 같은 잡 재실행은 통과
+- frontend/src/api/client.ts:42 가 401 을 받으면 window.location.href='/login' 으로 이동한다. reload 는 load 이벤트까지 기다리므로 새 페이지의 /api/auth/me 401 이 load 보다 먼저 오면 이동이 reload 를 끊는다</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>- CI(매뉴얼 갱신 브랜치)</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>System 2.2.0.1</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>SYM-169</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U279"/>
+  <dimension ref="A1:U281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23898,19 +23898,34 @@
           <t>- 매뉴얼 갱신(System 2.2.0.1) QA 에서 같은 유형의 낡은 수치가 이 파일에 남은 것을 확인. 공개 레포라 외부에서 읽힘</t>
         </is>
       </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>- 초안을 지우지 않고 현재 기준으로 갱신: 계정 발급(Google·이메일·승인), 권한 표, 사용자 관리, PostgreSQL·Alembic, 환경변수, pg_dump 백업, 트러블슈팅(Google, 승인 대기, PDF 폰트), FAQ(포트 8008, 계정 도움 요청, 가져오기 형식·헤더 19행·70여 변형), 변경 이력</t>
+        </is>
+      </c>
       <c r="P277" t="inlineStr">
         <is>
           <t>- 매뉴얼 본문 재구성</t>
         </is>
       </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>- docs/confluence_draft.md</t>
+        </is>
+      </c>
       <c r="R277" t="inlineStr">
         <is>
           <t>System 2.2.0.1 / FE 1.13.0.1</t>
         </is>
       </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>- System 2.2.0.4 / FE 1.13.0.3</t>
+        </is>
+      </c>
       <c r="T277" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U277" t="inlineStr">
@@ -23971,19 +23986,36 @@
           <t>- 매뉴얼 갱신 QA 에서 확인. 운영 매뉴얼 5-3 절의 설명과 그림이 불일치</t>
         </is>
       </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>- 25 번을 '비밀번호 초기화 완료' 창으로 재촬영(capture-auth-manual.spec.ts)
+- 같은 그림을 22 와 같은 화면으로 덮어쓰던 capture-all-manual, capture-readme 의 01/02/22/25 저장 제거
+- md 운영 매뉴얼에 5-5-2 계정 복구 요청 승인 절과 그림 25/39/40 연결</t>
+        </is>
+      </c>
       <c r="P278" t="inlineStr">
         <is>
           <t>- 다른 그림 재촬영</t>
         </is>
       </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>- 운영 매뉴얼 그림 25, 캡처 스크립트 3개, docs/manual_admin_confluence.md</t>
+        </is>
+      </c>
       <c r="R278" t="inlineStr">
         <is>
           <t>System 2.2.0.1 / FE 1.13.0.1</t>
         </is>
       </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>- System 2.2.0.4 / FE 1.13.0.3</t>
+        </is>
+      </c>
       <c r="T278" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U278" t="inlineStr">
@@ -24061,19 +24093,252 @@
           <t>- CI(매뉴얼 갱신 브랜치)</t>
         </is>
       </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>- 원인: 앱의 401 인터셉터(src/api/client.ts)가 window.location 으로 /login 을 연다. reload/goto 의 기본 대기(load)는 외부 폰트까지 기다려서, 401 이 load 보다 먼저 오면 그 이동이 대기 중인 탐색을 끊는다
+- 수정: e2e/nav.ts 도우미가 응답 도착(commit)까지만 기다리고 ERR_ABORTED 만 삼킨다. 사용 중지 테스트, 미로그인 리다이렉트 테스트 2곳(auth, regression-full)에 적용. 사용 중지 테스트에 재로그인 시 '사용이 중지된 계정입니다.' 단언 추가</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>- 같은 패턴을 도우미 하나로 모음. 로컬 격리 환경에서 세 테스트 5회 반복 15/15 통과
+- 결정적 재현은 못 함(폰트 지연 주입으로 옛 코드 실패 2회 관측)</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>- E2E 3개 테스트</t>
+        </is>
+      </c>
       <c r="R279" t="inlineStr">
         <is>
           <t>System 2.2.0.1</t>
         </is>
       </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>- System 2.2.0.3</t>
+        </is>
+      </c>
       <c r="T279" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U279" t="inlineStr">
         <is>
           <t>SYM-169</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>BUG-184</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Excel 97-2003(.xls) 파일을 가져오면 이유 없이 'Failed to read Excel file' 로 실패한다</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>- TC 가져오기 파일 선택기와 서버가 .xls 를 받지만, 실제 97-2003 형식 파일은 읽지 못하고 일반 오류만 낸다</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>- 읽을 수 없는 형식이면 이유와 해결 방법(.xlsx 로 다시 저장)을 안내한다</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>- 400 'Failed to read Excel file'</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>1. Excel 97-2003 통합 문서(.xls)를 준비한다
+2. TC 관리에서 가져오기로 그 파일을 고른다</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>- services/import_service.py 가 openpyxl.load_workbook 만 쓰고 xlrd 의존이 없다
+- OLE2 서명으로 시작하는 바이트를 load_workbook 에 넣으면 BadZipFile</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>- QA(매뉴얼 후속 수정의 Codex·QA2 지적)</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>원인: - openpyxl 은 OOXML(zip)만 읽는다. 97-2003 형식(OLE2/BIFF)과 암호가 걸린 .xlsx(OLE2 EncryptedPackage)는 읽기에서 예외가 나고 일반 문구로 바뀌었다
+수정 내용: - 내용 첫 8바이트가 OLE2 서명이면 안내 문구(XLS_NOT_SUPPORTED)로 400. 판정은 이름이 아니라 내용으로 해서 이름만 .xls 인 xlsx 는 그대로 읽힌다
+- 확장자 판정을 대소문자 무시로 변경(TC.XLSX 허용)
+- 안내 문구 ko/en 번역 추가</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_import_xls.py 5건(옛 형식 거절, 이름만 .xls 인 xlsx 읽기, 이름이 .xlsx 인 OLE2 거절, 대문자 확장자, 그 외 확장자)
+- errorMessage-upload.test.ts 에 문구 번역 확인 추가</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>- TC 가져오기 미리보기와 가져오기(직접 업로드, upload_id 모두)</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>BE 2.2.0.0</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>- System 2.2.0.2 / BE 2.2.0.1 / FE 1.13.0.2</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>SYM-170</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>BUG-185</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>trivial</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>DB 설정 단위 테스트가 Windows 에서 하위 프로세스 한글 출력이 깨져 실패한다</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_db_config.py 의 원격 직결 주소 거절 테스트가 Windows 로컬에서만 실패한다(CI 리눅스는 통과)</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>- 운영체제와 무관하게 통과한다</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>- 오류 문구의 한글이 U+FFFD 로 깨져 '원격' 포함 단언이 실패</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>1. Windows 에서 PYTHONUTF8 없이 python -m pytest tests_unit/test_db_config.py 를 실행한다</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>- 항상(Windows)</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>- PYTHONUTF8=1 이면 6건 통과, 없으면 1건 실패</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>- 로컬 전체 테스트 실행</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>원인: - 부모는 UTF-8 로 디코딩하는데 자식 파이썬은 Windows 기본 코드페이지(cp949)로 stderr 를 쓴다
+수정 내용: - 두 하위 프로세스 환경에 PYTHONIOENCODING=utf-8</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>- 없음(테스트 자체의 수정). 다른 하위 프로세스 테스트는 같은 패턴이 없음을 확인</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>- 로컬 테스트만</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>System 2.2.0.1</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>- System 2.2.0.3</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>SYM-171</t>
         </is>
       </c>
     </row>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U281"/>
+  <dimension ref="A1:U283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23377,19 +23377,35 @@
           <t>- 배포 환경에서 잘못 불린 요청이 잠금을 쥔 채 외부 호출을 기다린다</t>
         </is>
       </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>* 저장소에 direct_upload 속성(Local False, Supabase True)을 두고 PUT 라우트가 행 잠금 전에 이 값으로 판정해 400 을 낸다. 서명 주소 발급 호출이 없어졌다
+* 409(이미 올림)와 413(상한 초과) 응답 전에도 롤백해 행 잠금을 바로 푼다</t>
+        </is>
+      </c>
       <c r="P271" t="inlineStr">
         <is>
           <t>- 업로드 흐름 재설계</t>
         </is>
       </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>* 로컬 저장소 업로드 PUT 라우트. 테스트 tests_unit/test_upload_put_direct_mode.py</t>
+        </is>
+      </c>
       <c r="R271" t="inlineStr">
         <is>
           <t>BE 2.1.1.0</t>
         </is>
       </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>* BE 2.2.1.0</t>
+        </is>
+      </c>
       <c r="T271" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U271" t="inlineStr">
@@ -23641,14 +23657,35 @@
           <t>- QA</t>
         </is>
       </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>원인: * 존재 확인과 커밋 사이에 계정이 지워지면 외래키 오류가 난다. 실제 응답은 500 이 아니라 전역 IntegrityError 핸들러의 409 '데이터 제약 조건에 걸렸습니다' 였다(재현 테스트로 확인)
+수정 내용: * routes/members.py \_commit_assignment: 커밋 실패 시 롤백 후 계정이 없으면 404, 프로젝트가 없으면 404, 이미 멤버면 400, 그 밖은 409 '다른 요청과 겹쳤습니다'. 멤버 추가와 전체 배정에 적용</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>* tests_unit/test_member_assign_race.py: 커밋 직전 다른 연결로 계정을 지우는 경합 2건, 같은 사용자 동시 추가 1건(수정 전 코드에서 3건 실패)</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>* 프로젝트 멤버 추가, 전체 프로젝트 일괄 배정</t>
+        </is>
+      </c>
       <c r="R274" t="inlineStr">
         <is>
           <t>BE 2.2.0.0</t>
         </is>
       </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>* BE 2.2.1.0</t>
+        </is>
+      </c>
       <c r="T274" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U274" t="inlineStr">
@@ -24339,6 +24376,216 @@
       <c r="U281" t="inlineStr">
         <is>
           <t>SYM-171</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>SEC-029</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>관리자 API 키로 계정 승인과 역할 변경을 할 수 있다</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>- 계정 관리 라우트 7개(approve, reject, disable, enable, release-email, delete, role)와 복구 요청 거절이 role_required("admin") 만 보고 세션 전용 검사가 없다</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>- API 키로 부르면 403. 계정 관리는 관리자 로그인 세션으로만 한다</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>- 관리자 키로 대기 계정을 승인하고 role 을 admin 으로 올릴 수 있다. 키를 폐기해도 올린 관리자 계정은 남는다</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>1. 관리자 세션으로 API 키를 발급한다
+2. 그 키로 POST /api/auth/users/{id}/approve, PUT /api/auth/users/{id}/role {"role":"admin"} 을 보낸다
+3. 200 이 오고 대상 계정이 관리자가 된다</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_api_keys.py::test_관리자_키로는_계정을_관리하지_못한다 8건이 수정 전 코드에서 전부 실패</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 보안 감사)</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>원인: - 비밀번호 초기화와 복구 승인만 get_session_user 를 거쳤다. 나머지 계정 관리 라우트는 키 인증을 그대로 받았다
+수정 내용: - auth.admin_session_required(관리자 + 세션 전용) 를 만들어 8개 라우트에 건다</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>- 8개 경로를 키로 호출하면 403 인지 보는 표 테스트</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>- 계정 관리 API. 웹 화면 동작은 그대로</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>BE 2.2.0.1</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>BE 2.2.1.0</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>SYM-172</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>BUG-186</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>긴 비밀번호와 잘못된 대시보드 날짜가 500 을 낸다</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>- bcrypt 5.0 이 72바이트 초과 입력에 ValueError 를 낸다
+- 대시보드 date_from/date_to 파싱 실패가 ValueError 로 남는다</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>- 로그인은 401(실패 횟수 기록), 가입·변경은 400 안내, 날짜는 400</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>- 로그인(ASCII 73자, 한글 25자), 가입, 비밀번호 변경, 코드 초기화, 대시보드 6개 API 가 500</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>1. 로그인에 한글 25자 비밀번호를 넣는다
+2. GET 대시보드 summary 에 date_to=2026-10-01T00:00 을 준다</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_password_bytes.py, test_dashboard_date_params.py 가 수정 전 코드에서 실패</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사)</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>원인: - 비밀번호 바이트 상한과 날짜 형식을 검증하지 않았다
+수정 내용: - verify_password 는 초과를 틀린 비밀번호로(더미 대조로 응답 시간 유지), 새 비밀번호는 ensure_password_fits 로 400. 대시보드 날짜는 400</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>- 경계값(정확히 72바이트) 포함 테스트</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>- 로그인, 가입, 비밀번호 변경, 계정 복구, 대시보드</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>BE 2.2.0.1</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>BE 2.2.1.0</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>SYM-173</t>
         </is>
       </c>
     </row>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U283"/>
+  <dimension ref="A1:U301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23303,19 +23303,35 @@
           <t>- 전체 배정 조회 422 가 이 패턴 때문에 7개월 동안 드러나지 않았다</t>
         </is>
       </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>* 프로젝트·배정 조회가 실패하면 알림을 띄우고 배정 칸에 '조회 실패' 를 보인다. 배정 모달은 프로젝트마다 멤버를 부르지 않고 전체 배정 조회 한 번으로 채우며, 실패하면 '배정된 프로젝트가 없습니다' 대신 실패 문구를 보인다
+* 완료 조건: 세 조회의 실패 표시(완료), 실패 경로 목 테스트 4건(완료), 격리 환경 화면 캡처 확인(완료)</t>
+        </is>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>- 다른 화면의 오류 처리 일괄 정비</t>
         </is>
       </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>* 관리 화면 사용자 표와 프로젝트 배정 모달</t>
+        </is>
+      </c>
       <c r="R270" t="inlineStr">
         <is>
           <t>BE 2.1.1.0</t>
         </is>
       </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>* FE 1.13.2.0</t>
+        </is>
+      </c>
       <c r="T270" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U270" t="inlineStr">
@@ -24586,6 +24602,1838 @@
       <c r="U283" t="inlineStr">
         <is>
           <t>SYM-173</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>BUG-187</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>다음 회차가 지운 TC 와 범위 밖 TC 를 넘긴다</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>- _clone_run 이 원본 수행의 결과를 거르지 않고 그대로 복사한다</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>- 새 수행 만들기와 같은 조건(지우지 않았고 범위 안)의 TC 만 넘어간다</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>- 지운 TC 가 NS 로 남아 리포트 전체·미수행이 부풀고 진행률이 100% 가 되지 않는다. 다음 회차마다 계속 넘어간다</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>1. R1 에서 TC 10건 중 2건을 지운다
+2. R1 을 완료하고 다음 회차를 만든다
+3. R2 에 지운 TC 2건이 NS 로 있다</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_run_clone_scope.py 4건이 수정 전 코드에서 실패</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사)</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>원인: - 다음 회차, 복제, CI 이름 가져오기가 쓰는 _clone_run 에 _new_run 의 거르기 조건이 없었다
+수정 내용: - _new_run 과 같은 조건(deleted_at 없음, 범위가 있으면 그 시트)으로 거른다</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>- 지운 TC, 범위 밖 TC, 범위 없는 수행 회귀 테스트</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>- 다음 회차, 수행 복제, CI 결과 가져오기</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>BE 2.2.0.1</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>BE 2.2.2.0</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>SYM-174</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>BUG-188</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>칸 길이 초과 입력과 가져오기가 500 으로 실패한다</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>- PostgreSQL 은 VARCHAR 길이 초과를 DataError 로 내는데 IntegrityError 만 처리해 500 이 된다. 스키마에 길이 제한이 없다</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>- 400 과 어느 칸이 넘었는지 알려 준다</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>- 엑셀 R1 칸에 'Not Applicable'(14자) 한 행만 있어도 수천 행 가져오기 전체가 'Internal server error' 로 롤백된다</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>1. R1 칸에 14자 값이 있는 엑셀을 가져온다</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_length_limits.py 가 수정 전 코드에서 TC 생성, 엑셀·CSV·마크다운 가져오기 모두 500</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사, QA 두 갈래 모두 지적)</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>원인: - SQLite 시절에는 길이를 무시해 드러나지 않았다. PostgreSQL 전환 뒤 회귀
+수정 내용: - DataError 핸들러 400. 요청 스키마에 컬럼과 같은 max_length. 가져오기는 넘는 칸을 '시트 행 칸(글자 수/상한)' 으로 모아 400</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>- 스키마와 모델 길이를 대조하는 계약 테스트(UserCreate.email 254 대 100 불일치를 찾아 맞춤)</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>- TC, 수행, 플랜, 프로젝트, 커스텀 필드, 필터, 시트 API 와 가져오기</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>BE 2.2.0.1</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>BE 2.2.2.0</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>SYM-175</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>BUG-189</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>가져오기가 대소문자 다른 헤더를 버리고 짧은 CSV 행에서 500</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>* 'Expected result', 'Test steps' 처럼 대소문자나 공백만 다른 헤더를 매핑하지 못한다
+* 헤더보다 칸이 적은 CSV 행은 None 에 strip 을 불러 500</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>* 대소문자와 앞뒤 공백을 무시해 매핑하고, 모자란 칸은 빈 칸으로 읽는다</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>* 그 열이 경고 없이 빠져 기대 결과가 빈 TC 가 생긴다. 엑셀은 헤더 행 자체를 못 찾는다</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>1. 헤더가 'Expected result' 인 엑셀을 가져온다
+2. 헤더 'TC ID,Priority', 행 'TC-001' 인 CSV 를 가져온다</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>* 항상</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>* tests_unit/test_import_header_case.py, test_length_limits.py 의 CSV 짧은 행 테스트가 수정 전 코드에서 실패</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>* 코드 리뷰(사내 도입 전 감사)</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>원인: * 헤더 매핑이 정확한 문자열 일치만 봤다. CSV 행 값이 None 일 때를 다루지 않았다
+수정 내용: * map_header: 정확히 일치를 먼저 보고 없으면 대소문자·공백을 무시해 찾는다. 행 값은 (값 or "").strip()</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>* 엑셀·CSV·마크다운 헤더 대소문자 테스트, 짧은 CSV 행 테스트</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>* TC 가져오기</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>BE 2.2.0.1</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>BE 2.2.2.0</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>SYM-176</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>BUG-190</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>시트를 옮긴 TC 가 진행 중 수행에 들어가지 않는다</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>- 단건·일괄 TC 수정이 시트를 바꿔도 진행 중 수행 동기화를 부르지 않는다</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>- 생성, 복제, 복원, 가져오기처럼 바로 진행 중 수행에 NS 로 들어간다</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>- 수행 상세를 다시 열기 전까지 빠져 있고, 그 전에 완료하면 빠진 채로 남는다</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>- 시트 B 만 담은 진행 중 수행 R</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>1. 시트 A 의 TC 를 시트 B 로 옮긴다
+2. R 을 다시 열지 않고 완료하거나 리포트를 본다</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_tc_update_sync.py 2건이 수정 전 코드에서 실패</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사, QA 두 갈래 모두 지적)</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>원인: - 수정 라우트만 sync_project_in_progress_runs 호출이 빠져 있었다
+수정 내용: - 시트를 옮겼을 때 커밋 뒤 동기화. 일괄 수정은 지운 TC 를 건너뛰고 빈 TC ID 를 거절</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>- 단건·일괄 이동 동기화 테스트, 지운 TC 일괄 수정 테스트</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>- TC 수정, 진행 중 수행, 리포트</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>BE 2.2.0.1</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>BE 2.2.2.0</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>SYM-177</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>BUG-191</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>완료와 겹친 결과 저장이 완료된 수행에 써진다</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>- 결과 저장은 잠금 전에 상태를 보고, 완료와 재오픈은 결과 저장과 같은 잠금을 잡지 않는다</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>- 완료된 뒤 도착한 저장은 거절된다</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>- 완료된 수행의 결과가 재오픈 없이 바뀐다. 이미 완료된 수행을 다시 완료하면 completed_at 이 덮인다</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>1. A 의 결과 저장이 진행 중 상태 확인을 통과한다
+2. B 가 완료를 커밋한다
+3. A 가 결과를 커밋한다</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>- 미확인(경합)</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_run_complete_race.py 5건(스레드 재현 포함)이 수정 전 코드에서 실패</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사, QA 두 갈래 모두 지적)</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>원인: - 상태 확인과 잠금의 순서가 거꾸로였고 완료 경로가 잠금을 잡지 않았다
+수정 내용: - 완료·재오픈이 RUN_RESULTS 잠금을 잡는다. 저장과 결과 가져오기는 잠금 뒤 상태를 다시 읽어 완료면 400. 완료된 수행 재완료는 그대로 반환</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>- 잠금 대기, 스레드 경합, 재완료 테스트</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>- 결과 저장, 결과 가져오기, 완료, 재오픈</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>BE 2.2.0.1</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>BE 2.2.2.0</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>SYM-178</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>BUG-192</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>삭제가 실패해도 첨부 파일은 먼저 지워진다</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>- 저장소 객체를 DB 커밋보다 먼저 지운다</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>- DB 삭제가 확정된 뒤에만 파일을 지운다</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>- 커밋 실패나 함수 시간 초과(Vercel 60초)로 DB 는 남는데 첨부만 사라져 깨진다</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>1. 첨부가 있는 수행을 지운다
+2. 커밋이 실패한다</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>- 미확인(실패나 시간 초과 때)</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_delete_storage_order.py 가 수정 전 코드에서 프로젝트, 수행, 첨부 단건 삭제 모두 실패</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사)</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>원인: - delete_attachment_objects 가 커밋 전에 저장소를 바로 지웠다
+수정 내용: - 커밋 전에 지울 키를 같은 트랜잭션에서 storage_deletions 에 예약하고, 커밋 뒤 지운다. 실패하면 예약이 남아 일일 정리가 다시 지운다</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>- 커밋 실패 시 파일이 남는지 보는 테스트</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>- 프로젝트, 수행, 첨부 삭제</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>BE 2.2.0.1</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>BE 2.2.2.0</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>SYM-179</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>ENH-068</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>큰 응답을 압축하지 않아 Vercel 응답 한도에 걸릴 수 있다</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>- 응답 압축이 없다. 수행 상세는 TC 본문을 모두 싣는다(실데이터 643건 수행이 저장 크기 약 1MB)</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>- 1KB 이상 응답을 gzip 으로 보낸다</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>- [x] 큰 목록 응답에 content-encoding gzip
+- [x] 미들웨어를 빼면 실패하는 테스트</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>- Vercel 함수 응답 상한이 4.5MB 라 TC 수천 건 수행은 열리지 않는다. 사내 프로젝트 규모를 모른다</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>- GZipMiddleware(minimum_size=1024) 추가</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>- 수행 상세 응답 구조를 나누는 일(페이지 조회)</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>- 모든 API 응답</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>BE 2.2.0.1</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>BE 2.2.2.0</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>SYM-180</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>BUG-193</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>다른 시트가 쓴 TC ID 와 겹쳐 행 추가가 실패한다</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>- 행 추가의 새 TC ID 를 지금 보는 시트의 행만으로 계산한다. TC ID 유일 제약은 프로젝트 전체다</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>- 프로젝트에서 안 쓰는 다음 번호로 행이 추가된다</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>- 409 로 실패하고 '행 추가 실패' 만 뜬다. 새로 만든 빈 시트는 늘 TC-001 이 계산돼 매번 실패한다</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>- 시트 A 에 TC-001~030, 시트 B 에 TC-031~060 이 있다</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>1. 시트 A 를 연다
+2. + 행 추가를 누른다</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사)</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>원인: - addRows 가 rowData(현재 시트, 필터 결과)만 보고 최대 번호를 정했다
+수정 내용: - 프로젝트 전체 TC 목록을 받아 nextNewTcIds 로 계산(접두사는 지금 시트, 번호는 프로젝트 전체, 이미 쓴 값은 건너뜀). 실패 사유를 함께 표시</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>- nextNewTcIds 단위 테스트, 다른 시트 번호를 피하는 화면 테스트(수정 전 코드에서 실패 확인)</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>- TC 관리 행 추가</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>FE 1.13.0.3</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>FE 1.13.1.0</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>SYM-181</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>BUG-194</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>TC 자동저장이 다른 사람이 고친 칸을 되돌린다</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>- 셀 하나를 고쳐도 행 전체를 PUT 으로 보낸다. 서버는 보낸 칸을 모두 덮는다</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>- 내가 고친 칸만 바뀌고 다른 사람이 고친 칸은 남는다</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>- A 가 고친 절차가 B 의 화면에 있던 옛 값으로 알림 없이 돌아간다</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>- 두 사람이 같은 TC 를 연 상태</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>1. A 가 TC-010 의 절차를 고친다
+2. 다시 불러오지 않은 B 가 같은 행의 우선순위를 고친다
+3. A 의 절차가 원래 값으로 돌아간다</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사, QA 두 갈래 모두 지적)</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>원인: - autoSaveRow 가 행 객체 전체를 보냈다. 같은 행의 저장도 앞 요청을 기다리지 않아 순서가 뒤바뀔 수 있었다
+수정 내용: - 마지막 저장 스냅샷 대비 바뀐 칸만 보낸다(서버는 exclude_unset). 같은 행 저장은 앞 요청이 끝난 뒤 보낸다</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>- 바뀐 칸만 보내는지, 앞 요청을 기다리는지 화면 테스트(수정 전 코드에서 실패 확인)</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>- TC 관리 자동저장. 같은 칸을 동시에 고치면 여전히 늦게 저장한 쪽이 남는다</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>FE 1.13.0.3</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>FE 1.13.1.0</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>SYM-182</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>BUG-195</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>프로젝트를 바꾸면 이전 시트 선택이 남아 표가 빈다</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>- 같은 라우트라 TC 그리드가 다시 마운트되지 않아 시트 선택, 필터, 펼친 폴더가 남는다</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>- 새 프로젝트를 처음 연 것과 같은 상태로 보인다</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>- 새 프로젝트를 옛 시트 이름으로 조회해 표가 비고, 새 프로젝트를 못 불러오면 옛 프로젝트 이름 아래 새 데이터가 보인다</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>1. 프로젝트 A 에서 '로그인' 시트를 연다
+2. 헤더 검색이나 목록으로 프로젝트 B 로 간다</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사)</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>원인: - ProjectPage 가 projectId 가 바뀌어도 같은 인스턴스를 유지했다. 검색 강조는 onGridReady 에서만 처리했다
+수정 내용: - 프로젝트 id 를 key 로 화면 전체를 다시 띄운다. 검색 강조를 effect 로 옮기고 지금 시트에 없으면 전체 보기로 넓힌다</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>- 프로젝트 전환 시 그리드 재마운트, 불러오기 실패 시 옛 이름 미표시 테스트</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>- 프로젝트 화면 전환, 전역 검색 이동</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>FE 1.13.0.3</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>FE 1.13.1.0</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>SYM-183</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>BUG-196</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>시트 목록 조회 실패 시 빈 프로젝트 화면이 뜬다</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>- listSheets 실패를 삼키고 시트 0개로 본다</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>- 조회 실패와 다시 시도를 보여 준다</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>- '폴더나 시트를 추가하여...' 빈 프로젝트 안내와 시트 추가 버튼이 뜬다</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>1. 시트 목록 API 가 500 이나 네트워크 오류를 내는 상태에서 TC 탭을 연다</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>- 미확인(일시 장애 때)</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>- SheetsLoadFailed.test.tsx 가 수정 전 코드에서 실패</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사)</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>원인: - loadSheets 의 catch 가 '기존 호환' 이라며 아무것도 하지 않았다
+수정 내용: - 실패 상태를 따로 두고 오류 문구와 다시 시도 버튼을 보인다</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>- 실패 후 다시 시도까지 보는 화면 테스트</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>- TC 관리 첫 화면</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>FE 1.13.0.3</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>FE 1.13.1.0</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>SYM-184</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>BUG-197</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>TC 목록이 5,000건에서 안내 없이 잘린다</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>- 목록 API 는 한 번에 최대 5,000건을 주는데 프론트가 다음 구간을 요청하지 않는다</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>- 모든 TC 가 보인다</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>- 5,000건 뒤가 빠진다. 정렬이 no 뿐이라 어느 TC 가 빠지는지도 요청마다 달라질 수 있다</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>- 살아 있는 TC 가 5,000건을 넘는 프로젝트</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>1. 전체 보기로 TC 탭을 연다</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>- 항상(해당 규모에서)</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사, QA 두 갈래 모두 지적)</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>원인: - testCasesApi.list 가 한 번만 불렀다
+수정 내용: - 1,000건씩 끝까지 이어 받는다(한 응답을 Vercel 4.5MB 한도 아래로 둔다). 서버 정렬에 id 동점 깨기</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>- 여러 구간을 이어 받는 API 단위 테스트</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>- TC 관리, 행 추가의 번호 계산</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>FE 1.13.0.3</t>
+        </is>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>FE 1.13.1.0</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>SYM-185</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>BUG-198</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>행 수 선택, Ctrl+D, 필터 중 드래그가 상태를 무시한다</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>- 행 수 선택 상자가 5 로 고정돼 5행 추가를 고를 수 없다
+- 편집 권한이 없어도 Ctrl+D 가 화면 값을 바꾼 뒤 403 으로 되돌아간다
+- 고급 필터 적용 중에도 드래그 정렬이 켜져 있다</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>- 고를 수 있는 선택지만 보이고, 권한과 상태에 맞지 않는 조작은 처음부터 막힌다</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>- 위 증상 그대로. 필터 중 드래그는 서버가 400 으로 거절하고 필터가 풀린다</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>1. 행 수 선택에서 5행을 고른다
+2. viewer 로 셀을 고르고 Ctrl+D
+3. 고급 필터를 적용하고 행을 끈다</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사)</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>원인: - 비제어 select(defaultValue 5), Ctrl+D 에 canEditTC 검사 없음, rowDrag 조건에 필터 상태 없음
+수정 내용: - 자리표시 선택지가 있는 제어 select, Ctrl+D 권한 검사, 필터 적용 중 rowDrag 끔</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>- 없음. 단순 조건 추가라 화면 확인으로 갈음</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>- TC 관리 도구 모음과 키보드 조작</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>FE 1.13.0.3</t>
+        </is>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>FE 1.13.1.0</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>SYM-186</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>BUG-199</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>보기 전용과 완료 수행에서 결과 편집이 열려 있다</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>- 완료/편집 권한 검사가 버튼 몇 개에만 있다. 결과 드롭다운, 셀 편집, P/F/B/N, 일괄 입력, 첨부, 타이머는 열려 있다</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>- viewer 와 완료된 수행은 읽기만 된다</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>- 바꾼 뒤 서버가 거절하고 화면이 다시 읽힌다. 타이머가 켜진 채 완료 수행을 열면 행을 옮길 때마다 오류가 뜨고 스크롤이 맨 위로 간다</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>1. 타이머를 켠다
+2. 완료된 수행을 연다
+3. 행을 차례로 클릭한다</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>- TestRunReadOnly.test.tsx 가 수정 전 코드에서 실패</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사)</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>원인: - canManageRun 과 완료 여부를 그리드 편집 경로에 반영하지 않았다
+수정 내용: - readOnly(viewer 또는 완료)면 편집 칸, 결과 select, 단축키, Ctrl+D, Shift 채우기, 일괄 입력, 첨부 추가/삭제, 타이머를 막는다. 저장 오류 문구를 번역한다</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>- viewer, 완료 수행 두 경우 화면 테스트</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>- 테스트 수행 화면</t>
+        </is>
+      </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>FE 1.13.0.3</t>
+        </is>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>FE 1.13.2.0</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>SYM-187</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>BUG-200</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>수행 화면 Ctrl+Z 가 다른 행의 결과를 되돌린다</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>- 되돌리기 기록에 단축키와 셀 편집만 들어가고 드롭다운, 일괄 입력, Shift 채우기, Ctrl+D 는 빠진다</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>- 직전 조작 하나가 되돌아간다</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>- 한참 전 단축키로 입력한 다른 행의 결과가 지워진 채 저장되고 '되돌리기 완료' 가 뜬다</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>1. 행 5 에서 P 를 누른다
+2. 행 40 을 드롭다운으로 FAIL 로 바꾼다
+3. Ctrl+Z 를 누른다</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사)</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>원인: - 결과를 바꾸는 경로마다 기록 여부가 달랐다. 편집기 안 Ctrl+Z 도 가로챘다
+수정 내용: - 조작 하나를 묶음으로 기록하고 묶음 단위로 되돌린다. 편집 중에는 가로채지 않고, 수행을 바꾸면 기록을 비운다</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>- 일괄 입력 뒤 되돌리기, 편집기 안 Ctrl+Z 화면 테스트</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>- 테스트 수행 화면 되돌리기</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>FE 1.13.0.3</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>FE 1.13.2.0</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>SYM-188</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>BUG-201</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>수행 칸을 고친 직후 탭을 옮기면 저장되지 않는다</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>- 셀 편집은 0.3초 뒤에 저장하는데 화면을 떠나면 그 타이머를 취소만 한다</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>- 떠나기 전에 저장 요청을 보낸다</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>- 저장 요청이 나가지 않아 편집이 알림 없이 사라진다</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>1. 실제 결과 칸을 고치고 Enter
+2. 0.3초 안에 대시보드 탭을 누른다</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>- 항상(0.3초 안에 옮길 때)</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사, Codex 지적)</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>원인: - 언마운트 정리가 clearTimeout 만 했다
+수정 내용: - 대기 중인 저장을 기억해 두고 언마운트 때 즉시 보낸다</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>- 편집 직후 언마운트해도 저장되는지 화면 테스트(수정 전 코드에서 실패 확인)</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>- 테스트 수행 화면 셀 편집</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>FE 1.13.0.3</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>FE 1.13.2.0</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>SYM-189</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>BUG-202</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>리포트 수행을 빠르게 바꾸면 이전 리포트가 남는다</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>- 리포트 조회에 순번 가드가 없다</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>- 지금 고른 수행의 리포트만 보인다</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>- 선택 상자는 B 인데 화면은 늦게 도착한 A 의 리포트다</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>1. 큰 수행 A 를 고른다
+2. 응답 전에 작은 수행 B 를 고른다</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>- 간헐(응답 지연이 있을 때)</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>- ReportView.test.tsx 경합 테스트가 수정 전 코드에서 실패</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 감사)</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>원인: - loadReport 와 refreshReport 가 늦은 응답을 걸러내지 않았다
+수정 내용: - 세대 번호로 늦은 응답을 버린다. 대시보드도 같은 가드(방어)</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>- 늦은 응답 경합 화면 테스트</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>- 리포트, 대시보드</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>FE 1.13.0.3</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>FE 1.13.2.0</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>SYM-190</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>ENH-069</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>로그인 뒤 원래 보던 화면으로 돌아오지 못한다</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>- 세션이 끊기거나 공유받은 링크로 들어오면 로그인 화면으로 가고, 로그인 뒤 늘 프로젝트 목록으로 간다</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>- 로그인 화면 주소에 원래 경로(next)를 싣고 로그인(비밀번호, Google) 뒤 그 화면으로 돌아간다. 사이트 밖 경로는 받지 않는다</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>- [x] 401 리다이렉트와 보호 라우트가 next 를 싣는다
+- [x] 로그인 화면이 safeNextPath 로 이동한다
+- [x] 열린 리디렉션 차단 테스트</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>- 사내 도입 뒤 Slack 에 수행 링크를 공유하면 로그인한 사람마다 다시 찾아 들어가야 한다</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>- utils/nextPath.ts 추가, client.ts, App.tsx, LoginPage 연결. 서버 safe_next 와 같은 규칙</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>- 만료 전 토큰 자동 연장</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>- 로그인 흐름</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>FE 1.13.0.3</t>
+        </is>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>FE 1.13.2.0</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>SYM-191</t>
         </is>
       </c>
     </row>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U301"/>
+  <dimension ref="A1:U305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -26437,6 +26437,410 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>SEC-030</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>강등된 생성자가 멤버 역할과 무관하게 프로젝트 admin 으로 남는다</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>- 역할 판정이 멤버 표와 별도로 created_by 를 봐서 생성자는 늘 admin 이다
+- 생성자는 프로젝트 멤버에서 뺄 수도 없다</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>- 프로젝트 역할은 멤버 표를 따른다. 시스템 관리자는 생성자를 멤버에서 뺄 수 있다</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>- qa_manager 를 user 로 강등하고 그 사람의 멤버 역할을 tester 로 낮춰도 프로젝트 삭제(204)와 멤버 관리가 된다</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>1. qa_manager 가 비공개 프로젝트를 만든다
+2. 관리자가 그 사람을 user 로 강등하고 멤버 역할을 tester 로 바꾼다
+3. 그 사람이 DELETE /api/projects/{id} 를 보낸다</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_creator_role.py 2건이 수정 전 코드에서 실패(삭제 204, 생성자 제거 400)</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 보안 감사)</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>원인: - 생성자는 만들 때 admin 멤버로 자동 등록되는데 역할 판정 네 곳(auth, 목록, 개요, 검색)이 created_by 를 따로 봤다
+수정 내용: - created_by 우회 판정을 지우고 멤버 표만 본다. 생성자의 역할 변경과 제거는 시스템 admin/qa_manager 만 허용(서버와 프로젝트 설정 화면 같은 규칙). 매뉴얼·문서 서술 정정</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>- 강등 후 역할 낮추기, 시스템 관리자의 생성자 제거, 프로젝트 admin 의 생성자 제거·역할 변경 거절 테스트. 옛 규칙을 못박은 test_security 3건 정정. 실데이터에 생성자 판정에만 기대는 프로젝트 0건 확인</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>- 프로젝트 권한 판정, 목록, 개요, 검색, 멤버 관리</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>BE 2.2.2.0</t>
+        </is>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>BE 2.2.3.0</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>SYM-192</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>SEC-031</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>임시 비밀번호 상태에서도 서버가 다른 API 를 막지 않는다</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>- 관리자 초기화 뒤 비밀번호 강제 변경을 화면만 하고 서버는 검사하지 않는다</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>- 비밀번호를 바꾸기 전에는 변경 창이 쓰는 경로(me, change-password, logout)만 열린다</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>- 전달 과정에서 임시 비밀번호를 본 사람이 화면을 거치지 않고 API 로 프로젝트를 읽고 쓸 수 있다</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>1. 관리자가 비밀번호를 초기화한다
+2. 임시 비밀번호로 로그인한다
+3. GET /api/projects 를 보낸다</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>- tests_unit/test_must_change_password.py 가 수정 전 코드에서 실패(200)</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰(사내 도입 전 보안 감사)</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>원인: - must_change_password 를 로그인 응답에 싣기만 하고 인증 의존성에서 보지 않았다
+수정 내용: - get_current_user 가 세션 경로에서 이 상태면 세 경로 밖은 403 '비밀번호를 먼저 변경해 주세요.'. 문구 번역 추가</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>- 403, 변경 뒤 재로그인, 로그아웃 테스트</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>- 관리자 초기화를 받은 계정</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>BE 2.2.2.0</t>
+        </is>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>BE 2.2.3.0</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>SYM-193</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>ENH-070</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>이메일 가입 횟수 기본 상한이 IP 당 시간당 10건이라 사무실 일괄 가입이 막힌다</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>- REGISTER_MAX_PER_HOUR 기본값 10. 같은 사무실(NAT 하나)에서 11번째 가입부터 429</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>- 기본값 30</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>- [x] 환경변수가 없으면 30건까지 201, 31번째 429
+- [x] .env.example, 운영 매뉴얼(화면, docs) 기본값 갱신</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>- 다음 주 팀 단위 사내 도입에서 이메일 가입이 한꺼번에 몰린다(사용자 결정)</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>- 기본값 30, 문서 4곳 갱신</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>- 제한 방식(IP 기준) 변경</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>- 이메일 가입</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>BE 2.2.2.0</t>
+        </is>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>BE 2.2.3.0</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>SYM-194</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>BUG-203</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>TC 저장이 거부되면 그 사이 고친 다른 칸까지 되돌아가 저장되지 않는다</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>- 저장 거부 때 행 전체를 마지막 저장 상태로 되돌린다</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>- 거부된 요청이 보낸 칸만 되돌리고, 그 사이 고친 칸은 남아 다음 저장으로 나간다</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>- 앞 요청이 오가는 사이 고친 칸도 지워지고, 줄 서 있던 다음 저장은 바뀐 칸이 없다며 보내지지 않는다</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>1. 우선순위를 고친다(저장 요청 진행 중)
+2. 비고를 고친다
+3. 첫 저장이 거부된다</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>- 간헐(거부와 연속 편집이 겹칠 때)</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>- TcAutoSavePartial.test.tsx 의 거부 테스트가 수정 전 코드에서 실패(두 번째 저장 없음)</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>- QA(2차 검증 지적)</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>원인: - restoreRow 가 Object.assign 으로 행 전체를 덮었다
+수정 내용: - 거부된 요청이 보낸 칸 가운데 지금 값이 보낸 값 그대로인 칸만 되돌린다. custom_fields 는 복사해 싣고 칸 단위로 비교</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>- 거부와 연속 편집이 겹치는 화면 테스트</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>- TC 관리 자동저장</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>FE 1.13.2.0</t>
+        </is>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>FE 1.13.3.0</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>SYM-195</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U305"/>
+  <dimension ref="A1:U306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -26841,6 +26841,101 @@
         </is>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>ENH-071</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>배포 절차가 README 한 절에 몰려 있어 공개 배포와 회사 배포를 따라 하기 어렵다</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>- README 의 배포 절 하나에 Supabase, Vercel, GitHub Actions 설정이 표 위주로 적혀 있다
+- 함수 리전, 첫 관리자 만들기, 배포 뒤 확인, 업데이트 순서가 없다
+- 회사(비공개 레포 + Actions) 경로만 있고 fork 해 개인 계정에 올리는 경로가 없다
+- .vercel 폴더가 .gitignore 에 없어 vercel link 결과가 커밋될 수 있다</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>- docs/deploy_public.md, docs/deploy_company.md 두 가이드를 순서대로 따르면 배포가 끝난다
+- README 배포 절은 두 가이드로 안내한다</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>- [x] 공개 배포 가이드: Supabase, PC 마이그레이션, Vercel Git 연동, 첫 관리자, 가입 정책, 확인, 업데이트, 백업
+- [x] 회사 배포 가이드: 비공개 레포, Supabase, Vercel CLI 연결, Google 내부 OAuth, Actions 비밀값, 첫 배포, 확인, 업데이트, 운영
+- [x] 정책 조합 서술을 account_policy.initial_status 와 대조
+- [x] .gitignore 에 .vercel/</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>- 다음 주 사내 도입에서 회사 배포를 처음 만든다. 리전(icn1), TRUSTED_PROXY_HEADER, AUTH_* 를 빠뜨리면 느리거나 외부에 열린다</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>- 두 가이드 추가, README 배포 절을 안내로 축소, Google OAuth 내부 대상 안내 추가, .gitignore 에 .vercel/</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>- 로컬 PostgreSQL 설치에서 Supabase 로 데이터를 옮기는 스크립트
+- 배포 자동화 코드 변경</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>- 문서(README, docs), .gitignore</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>System 2.2.5.0</t>
+        </is>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>System 2.2.5.1</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>SYM-196</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U306"/>
+  <dimension ref="A1:U309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -26936,6 +26936,273 @@
         </is>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>ENH-072</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Claude 스타트업 프로그램 지원용 회사소개 페이지 추가</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>- 제품 소개 자료는 portfolio/YM_TestCase.html, PDF, PPTX 와 README 뿐이다
+- 비로그인 라우트는 /login, /register, /account-help, /reset-password 뿐이고 / 는 /projects 로 보낸다. 외부에 보여줄 회사/제품 소개 페이지가 없다</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>- ym-testcase 에서 회사(팀)와 제품을 소개하는 공개 페이지에 접근할 수 있다
+- Claude 스타트업 프로그램 지원서에 이 페이지 URL 을 적을 수 있다</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>- [ ] 로그인 없이 접근 가능한 회사소개 페이지가 배포 URL 에 있다
+- [ ] 제품 개요, 주요 기능, 스크린샷, 팀/연락처가 들어간다
+- [ ] 프로그램 지원 요건(웹사이트 항목 등)을 확인하고 그에 맞춘다
+- [ ] 페이지 문구가 deslop 검사를 통과한다
+- [ ] QA 2인 검증과 스크린샷 확인을 마친다</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>- 지금 착수하지 않는다. Claude 스타트업 프로그램 지원 시점에 착수한다(백로그)
+- 지원서에 회사/제품 웹사이트를 요구할 때 보여줄 페이지가 없다</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>- 지원서 작성과 제출 자체
+- 기존 앱 화면 레이아웃 변경</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>System 2.2.5.1</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>SYM-197</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>SEC-032</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>일반 사용자가 프로젝트를 만들 수 없다</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>- 프로젝트 생성 API 가 시스템 역할 qa_manager 이상만 허용한다(POST /api/projects 403)
+- 프로젝트 목록 화면의 '+ 새 프로젝트' 버튼이 qa_manager 이상에게만 보인다</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>- 로그인한 사용자는 누구나 프로젝트를 만든다
+- 만든 사람은 그 프로젝트의 admin 멤버로 등록된다(기존 규칙 유지)
+- 프로젝트 일괄 삭제 체크박스는 지금처럼 qa_manager 이상에게만 보인다</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>- [ ] role=user 계정의 POST /api/projects 가 201 이고 생성자가 admin 멤버로 들어간다
+- [ ] 일반 사용자 화면에 '+ 새 프로젝트' 버튼이 보이고 일괄 삭제 체크박스는 안 보인다
+- [ ] 매뉴얼의 '생성은 Admin 만' 문구와 권한 표가 바뀐 규칙과 맞다</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>- 사용자 요청. 팀원이 자기 업무용 프로젝트를 만들 때마다 관리자에게 부탁해야 한다</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>* `POST /api/projects` 를 로그인 사용자 전체에 허용. 만든 사람은 Project Admin 멤버로 등록
+* 프로젝트 목록의 '+ 새 프로젝트' 버튼을 모든 사용자에게 표시. 일괄 삭제 체크박스는 QA Manager 이상 유지
+* 생성 허용으로 멤버 후보 목록이 사실상 전원에게 열리므로 `available-users` 를 사용 중 계정의 id, 아이디, 표시 이름으로 축소
+* 시스템 관리자가 아니면 사용 중이 아닌 계정의 멤버 추가를 404 로 거절(id 를 넣어 보며 숨긴 계정을 알아내는 경로 차단)
+* 사용자·운영 매뉴얼의 생성 권한 경고문, 권한 표, 역할 요약, API 목록 갱신
+* 완료 조건 3개 충족. 남은 정책 결정: 일반 사용자가 만든 프로젝트의 공개 기본값, 이메일 가입 계정은 아이디가 이메일이라 후보 목록에 보임</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>- 생성 권한을 끄는 환경변수 스위치
+- 사용자별 프로젝트 개수 상한</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>System 2.2.5.1 / BE 2.2.3.0 / FE 1.13.3.0</t>
+        </is>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>* System 2.2.6.0 / BE 2.2.4.0 / FE 1.13.4.0 (커밋: 533c34c)</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>SYM-198</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>ENH-073</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>시트를 통째로 복사하는 기능이 없다</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>- 시트는 추가, 이름 변경, 이동, 삭제만 된다
+- 같은 구성의 시트가 필요하면 TC 를 전부 골라 복제한 뒤 시트를 옮기거나 엑셀로 내보내 다시 가져와야 한다</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>- 시트 트리의 시트 행에 복사 버튼이 생긴다
+- 누르면 같은 부모 아래, 원본 바로 다음에 '&lt;원본&gt; (복사)' 시트가 생기고 원본의 살아 있는 TC 가 같은 순서로 들어간다
+- 복사한 TC 는 새 TC ID(&lt;원본 ID&gt;-copy)를 받는다. 수행 결과, 변경 이력, 첨부는 복사하지 않는다</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>- [ ] POST /sheets/{id}/copy 가 새 시트와 TC 를 만들고 번호가 1 부터 이어진다
+- [ ] 이름이 겹치면 (복사 2), (복사 3) 으로 비어 있는 이름을 찾는다. 100자 상한을 넘지 않는다
+- [ ] 폴더는 복사를 거부한다(400). 프로젝트 admin 이 아니면 403
+- [ ] 진행 중인 전체 범위 수행에 복사한 TC 가 NS 로 들어간다
+- [ ] 시트 트리에 복사 버튼이 보이고 누르면 새 시트가 선택된다</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>- 사용자 요청. 회차별·플랫폼별로 같은 TC 묶음을 따로 관리하려는 수요</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>* `POST /api/projects/{id}/testcases/sheets/{sheet_id}/copy` 와 시트 트리 복사 버튼(키보드 Enter/Space 가능) 추가
+* 원본 바로 다음 자리에 `&lt;원본&gt; (복사)`, 겹치면 `(복사 N)`. 시트 행 없이 TC 만 남은 이름도 피함. 100자 상한
+* 살아 있는 TC 를 No 1 부터 복제, TC ID 는 TC 복제와 같은 `-copy` 규칙. 수행 결과, 변경 이력, 첨부는 복사하지 않음
+* 진행 중인 전체 범위 수행 동기화까지 한 트랜잭션. 동기화가 실패하면 복사 전체 취소
+* 완료 조건 5개 충족. '기본' 시트 하나뿐인 프로젝트는 원래 사이드바가 없어 복사 버튼도 보이지 않음(기존 호환 모드, 범위 밖)</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>- 폴더(하위 시트 포함) 복사
+- 다른 프로젝트로 복사</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>System 2.2.5.1 / BE 2.2.3.0 / FE 1.13.3.0</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>* System 2.2.6.0 / BE 2.2.4.0 / FE 1.13.4.0 (커밋: 533c34c)</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>SYM-199</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U309"/>
+  <dimension ref="A1:U310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -27203,6 +27203,118 @@
         </is>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>PERF-011</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>30분 이상 쓰지 않다가 접속하면 첫 화면이 느리다</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>- 30분 이상 아무도 쓰지 않다가 접속하면 첫 화면의 데이터가 늦게 뜬다. 그 뒤로는 빠르다</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>- 유휴 뒤 첫 접속도 평소와 큰 차이 없이 뜬다</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>- 새 함수 인스턴스의 첫 API 응답 1.5~3.4초(따뜻할 때 0.07~0.13초)
+- 따뜻한 인스턴스가 있어도 동시 요청 3건 중 1건이 새 인스턴스로 가서 1.5~2초</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>1. 시험 배포(Vercel Hobby)를 30분 이상 호출하지 않는다
+2. 로그인 화면을 열고 로그인한다
+3. 프로젝트 목록과 프로젝트 화면의 API 응답 시간을 본다</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>- 항상(유휴 뒤 첫 접속)</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>- 2026-10-20 실측: 첫 /api 호출 3.4초, 프로젝트 화면 진입 중 /api/projects 1.9~2.0초, /testcases/sheets 1.5초. 같은 요청의 런타임 로그에 새 인스턴스 기동 흔적(alembic 플러그인 로그)
+- 로컬 앱 임포트 1.35~1.67초 중 openpyxl 0.26초, 모듈 로드 시 bcrypt 0.16초, 첫 요청 alembic 0.16초</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>- 사용자</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>원인: - Hobby 플랜은 유휴 시 함수 인스턴스를 0개로 내린다(프로덕션 인스턴스 1개 유지는 Pro/Enterprise 만). 새 인스턴스가 엑셀 라이브러리 임포트, 모듈 로드 시 bcrypt 해시, 첫 요청의 alembic 임포트를 사용자 요청 안에서 치렀다
+- 프론트가 같은 목록을 중복 요청해(프로젝트 목록 2회, TC 목록 2회) 동시 요청이 새 인스턴스로 갈라질 기회를 늘렸다
+수정 내용: - openpyxl 은 쓰는 함수 안에서 임포트, 더미 해시는 미리 만든 상수, 스키마 판정은 리비전 상수로(alembic 미임포트). 로컬 앱 임포트 0.85초
+- 프로젝트 목록은 진행 중 요청 공유, TC 관리는 시트 목록 뒤 TC 목록 1회
+- /assets 1년 immutable 캐시, 없는 자산은 SPA 폴백 대신 404</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>- test_cold_start.py: 앱 임포트 중 openpyxl/alembic 미로드와 bcrypt 0회, 첫 요청 스키마 판정의 alembic 미로드, 더미 해시 비용 일치
+- 리비전 상수와 alembic 이력 대조 테스트
+- TcInitialLoadOnce.test.tsx, api-index.test.ts 진행 중 요청 테스트</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>- 새 인스턴스의 첫 API 응답, 프로젝트 목록, TC 관리 첫 로딩, 정적 자산 캐시</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>System 2.2.6.0 / BE 2.2.4.0 / FE 1.13.4.0</t>
+        </is>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>System 2.2.6.1 / BE 2.2.4.1 / FE 1.13.4.1</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>SYM-200</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
